--- a/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
+++ b/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\land\BLAPE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\land\BLAPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A78EC5D-9081-450D-8FFB-1B527D472B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C994E1-3E4F-43E0-A513-39717EA92B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="48" r:id="rId14"/>
+    <pivotCache cacheId="11" r:id="rId14"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -641,12 +641,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
     <numFmt numFmtId="166" formatCode="0.0E+00"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000E+00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -771,7 +772,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -827,6 +828,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1256,6 +1258,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1263,7 +1266,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9245,7 +9247,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9616E194-24DA-4C46-8097-71C6F2CA831B}" name="PivotTable2" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9616E194-24DA-4C46-8097-71C6F2CA831B}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:F16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -9668,18 +9670,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="2" width="51.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.1796875" customWidth="1"/>
+    <col min="2" max="2" width="51.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -9687,62 +9689,62 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B5" s="4">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B7" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B10" s="26" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B11" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B12" s="4">
         <v>2024</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -9750,7 +9752,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -9758,27 +9760,27 @@
         <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>145</v>
       </c>
@@ -9795,22 +9797,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AH15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="63.28515625" customWidth="1"/>
+    <col min="1" max="1" width="63.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.75">
       <c r="B3" s="6">
         <v>2020</v>
       </c>
@@ -9905,7 +9907,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -10034,7 +10036,7 @@
         <v>-954.08424242424235</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -10163,7 +10165,7 @@
         <v>71.351515151515173</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -10292,29 +10294,29 @@
         <v>15.475757575757598</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.75">
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.75">
       <c r="AG11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="AH11" s="7"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -10418,7 +10420,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -10555,7 +10557,7 @@
         <v>-921.8</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -10692,7 +10694,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -10838,18 +10840,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="33" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="255.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="33" width="6.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -10953,7 +10955,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -11057,7 +11059,7 @@
         <v>-771.7</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -11161,7 +11163,7 @@
         <v>-787</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -11265,7 +11267,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -11369,7 +11371,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -11473,7 +11475,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -11577,7 +11579,7 @@
         <v>-100.3</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -11681,7 +11683,7 @@
         <v>-100.3</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -11785,7 +11787,7 @@
         <v>-31.7</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -11889,7 +11891,7 @@
         <v>-31.7</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -11993,7 +11995,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -12097,7 +12099,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -12201,7 +12203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -12305,7 +12307,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -12409,7 +12411,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -12513,7 +12515,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -12617,7 +12619,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -12721,7 +12723,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -12825,7 +12827,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -12929,7 +12931,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -13033,7 +13035,7 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -13137,7 +13139,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -13241,7 +13243,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -13345,7 +13347,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -13449,7 +13451,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -13553,7 +13555,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -13657,7 +13659,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -13761,7 +13763,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -13865,7 +13867,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>53</v>
       </c>
@@ -13969,7 +13971,7 @@
         <v>-132.30000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -14073,7 +14075,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -14177,7 +14179,7 @@
         <v>-138.5</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -14281,7 +14283,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>57</v>
       </c>
@@ -14385,7 +14387,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>58</v>
       </c>
@@ -14489,7 +14491,7 @@
         <v>68.2</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -14593,7 +14595,7 @@
         <v>68.2</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>59</v>
       </c>
@@ -14697,7 +14699,7 @@
         <v>67.599999999999994</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -14801,7 +14803,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -14905,7 +14907,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>60</v>
       </c>
@@ -15009,7 +15011,7 @@
         <v>-921.8</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -15113,67 +15115,67 @@
         <v>-854.2</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -15188,27 +15190,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D41D2ED-A995-4355-B1B7-DFF537DF2BE3}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AE602"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="4" width="11.42578125" style="20"/>
-    <col min="5" max="5" width="18.28515625" style="20" customWidth="1"/>
-    <col min="6" max="16384" width="11.42578125" style="20"/>
+    <col min="1" max="4" width="11.453125" style="20"/>
+    <col min="5" max="5" width="18.26953125" style="20" customWidth="1"/>
+    <col min="6" max="16384" width="11.453125" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A2" s="20" t="s">
         <v>104</v>
       </c>
@@ -15240,7 +15242,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A3" s="20" t="s">
         <v>114</v>
       </c>
@@ -15273,7 +15275,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A4" s="20" t="s">
         <v>114</v>
       </c>
@@ -15306,7 +15308,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A5" s="20" t="s">
         <v>114</v>
       </c>
@@ -15339,7 +15341,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A6" s="20" t="s">
         <v>114</v>
       </c>
@@ -15372,7 +15374,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A7" s="20" t="s">
         <v>114</v>
       </c>
@@ -15401,7 +15403,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A8" s="20" t="s">
         <v>114</v>
       </c>
@@ -15430,7 +15432,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A9" s="20" t="s">
         <v>114</v>
       </c>
@@ -15459,7 +15461,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A10" s="20" t="s">
         <v>114</v>
       </c>
@@ -15488,7 +15490,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A11" s="20" t="s">
         <v>114</v>
       </c>
@@ -15521,7 +15523,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A12" s="20" t="s">
         <v>114</v>
       </c>
@@ -15554,7 +15556,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A13" s="20" t="s">
         <v>114</v>
       </c>
@@ -15587,7 +15589,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A14" s="20" t="s">
         <v>114</v>
       </c>
@@ -15620,7 +15622,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A15" s="20" t="s">
         <v>114</v>
       </c>
@@ -15653,7 +15655,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A16" s="20" t="s">
         <v>114</v>
       </c>
@@ -15686,7 +15688,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A17" s="20" t="s">
         <v>114</v>
       </c>
@@ -15715,7 +15717,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A18" s="20" t="s">
         <v>114</v>
       </c>
@@ -15744,7 +15746,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A19" s="20" t="s">
         <v>114</v>
       </c>
@@ -15773,7 +15775,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A20" s="20" t="s">
         <v>114</v>
       </c>
@@ -15802,7 +15804,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A21" s="20" t="s">
         <v>114</v>
       </c>
@@ -15835,7 +15837,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A22" s="20" t="s">
         <v>114</v>
       </c>
@@ -15868,7 +15870,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A23" s="20" t="s">
         <v>114</v>
       </c>
@@ -15901,7 +15903,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A24" s="20" t="s">
         <v>114</v>
       </c>
@@ -15934,7 +15936,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A25" s="20" t="s">
         <v>114</v>
       </c>
@@ -15967,7 +15969,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A26" s="20" t="s">
         <v>114</v>
       </c>
@@ -16000,7 +16002,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A27" s="20" t="s">
         <v>114</v>
       </c>
@@ -16029,7 +16031,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A28" s="20" t="s">
         <v>114</v>
       </c>
@@ -16058,7 +16060,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A29" s="20" t="s">
         <v>114</v>
       </c>
@@ -16087,7 +16089,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A30" s="20" t="s">
         <v>114</v>
       </c>
@@ -16116,7 +16118,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A31" s="20" t="s">
         <v>114</v>
       </c>
@@ -16149,7 +16151,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A32" s="20" t="s">
         <v>114</v>
       </c>
@@ -16182,7 +16184,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A33" s="20" t="s">
         <v>114</v>
       </c>
@@ -16215,7 +16217,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A34" s="20" t="s">
         <v>114</v>
       </c>
@@ -16248,7 +16250,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A35" s="20" t="s">
         <v>114</v>
       </c>
@@ -16281,7 +16283,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A36" s="20" t="s">
         <v>114</v>
       </c>
@@ -16314,7 +16316,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="37" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A37" s="20" t="s">
         <v>114</v>
       </c>
@@ -16343,7 +16345,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A38" s="20" t="s">
         <v>114</v>
       </c>
@@ -16372,7 +16374,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A39" s="20" t="s">
         <v>114</v>
       </c>
@@ -16401,7 +16403,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A40" s="20" t="s">
         <v>114</v>
       </c>
@@ -16430,7 +16432,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A41" s="20" t="s">
         <v>114</v>
       </c>
@@ -16463,7 +16465,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A42" s="20" t="s">
         <v>114</v>
       </c>
@@ -16496,7 +16498,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A43" s="20" t="s">
         <v>114</v>
       </c>
@@ -16526,7 +16528,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A44" s="20" t="s">
         <v>114</v>
       </c>
@@ -16631,7 +16633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A45" s="20" t="s">
         <v>114</v>
       </c>
@@ -16664,7 +16666,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A46" s="20" t="s">
         <v>114</v>
       </c>
@@ -16697,7 +16699,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="47" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A47" s="20" t="s">
         <v>114</v>
       </c>
@@ -16723,7 +16725,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A48" s="20" t="s">
         <v>114</v>
       </c>
@@ -16752,7 +16754,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A49" s="20" t="s">
         <v>114</v>
       </c>
@@ -16781,7 +16783,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A50" s="20" t="s">
         <v>114</v>
       </c>
@@ -16810,7 +16812,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A51" s="20" t="s">
         <v>114</v>
       </c>
@@ -16840,7 +16842,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A52" s="20" t="s">
         <v>114</v>
       </c>
@@ -16873,7 +16875,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A53" s="20" t="s">
         <v>114</v>
       </c>
@@ -16906,7 +16908,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A54" s="20" t="s">
         <v>114</v>
       </c>
@@ -16939,7 +16941,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A55" s="20" t="s">
         <v>114</v>
       </c>
@@ -16972,7 +16974,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A56" s="20" t="s">
         <v>114</v>
       </c>
@@ -17005,7 +17007,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A57" s="20" t="s">
         <v>114</v>
       </c>
@@ -17034,7 +17036,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A58" s="20" t="s">
         <v>114</v>
       </c>
@@ -17063,7 +17065,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A59" s="20" t="s">
         <v>114</v>
       </c>
@@ -17092,7 +17094,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A60" s="20" t="s">
         <v>114</v>
       </c>
@@ -17121,7 +17123,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A61" s="20" t="s">
         <v>114</v>
       </c>
@@ -17154,7 +17156,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A62" s="20" t="s">
         <v>114</v>
       </c>
@@ -17187,7 +17189,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A63" s="20" t="s">
         <v>114</v>
       </c>
@@ -17220,7 +17222,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A64" s="20" t="s">
         <v>114</v>
       </c>
@@ -17253,7 +17255,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A65" s="20" t="s">
         <v>114</v>
       </c>
@@ -17286,7 +17288,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A66" s="20" t="s">
         <v>114</v>
       </c>
@@ -17319,7 +17321,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A67" s="20" t="s">
         <v>114</v>
       </c>
@@ -17348,7 +17350,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A68" s="20" t="s">
         <v>114</v>
       </c>
@@ -17377,7 +17379,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A69" s="20" t="s">
         <v>114</v>
       </c>
@@ -17406,7 +17408,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A70" s="20" t="s">
         <v>114</v>
       </c>
@@ -17435,7 +17437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A71" s="20" t="s">
         <v>114</v>
       </c>
@@ -17468,7 +17470,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A72" s="20" t="s">
         <v>114</v>
       </c>
@@ -17501,7 +17503,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A73" s="20" t="s">
         <v>114</v>
       </c>
@@ -17534,7 +17536,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A74" s="20" t="s">
         <v>114</v>
       </c>
@@ -17567,7 +17569,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A75" s="20" t="s">
         <v>114</v>
       </c>
@@ -17600,7 +17602,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A76" s="20" t="s">
         <v>114</v>
       </c>
@@ -17633,7 +17635,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A77" s="20" t="s">
         <v>114</v>
       </c>
@@ -17662,7 +17664,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A78" s="20" t="s">
         <v>114</v>
       </c>
@@ -17691,7 +17693,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A79" s="20" t="s">
         <v>114</v>
       </c>
@@ -17720,7 +17722,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A80" s="20" t="s">
         <v>114</v>
       </c>
@@ -17749,7 +17751,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A81" s="20" t="s">
         <v>114</v>
       </c>
@@ -17782,7 +17784,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A82" s="20" t="s">
         <v>114</v>
       </c>
@@ -17815,7 +17817,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A83" s="20" t="s">
         <v>114</v>
       </c>
@@ -17844,7 +17846,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A84" s="20" t="s">
         <v>114</v>
       </c>
@@ -17873,7 +17875,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A85" s="20" t="s">
         <v>114</v>
       </c>
@@ -17902,7 +17904,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A86" s="20" t="s">
         <v>114</v>
       </c>
@@ -17931,7 +17933,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A87" s="20" t="s">
         <v>114</v>
       </c>
@@ -17960,7 +17962,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A88" s="20" t="s">
         <v>114</v>
       </c>
@@ -17993,7 +17995,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A89" s="20" t="s">
         <v>114</v>
       </c>
@@ -18026,7 +18028,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A90" s="20" t="s">
         <v>114</v>
       </c>
@@ -18059,7 +18061,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A91" s="20" t="s">
         <v>114</v>
       </c>
@@ -18092,7 +18094,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A92" s="20" t="s">
         <v>114</v>
       </c>
@@ -18125,7 +18127,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A93" s="20" t="s">
         <v>114</v>
       </c>
@@ -18154,7 +18156,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A94" s="20" t="s">
         <v>114</v>
       </c>
@@ -18183,7 +18185,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A95" s="20" t="s">
         <v>114</v>
       </c>
@@ -18212,7 +18214,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A96" s="20" t="s">
         <v>114</v>
       </c>
@@ -18241,7 +18243,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A97" s="20" t="s">
         <v>114</v>
       </c>
@@ -18270,7 +18272,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A98" s="20" t="s">
         <v>114</v>
       </c>
@@ -18299,7 +18301,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A99" s="20" t="s">
         <v>114</v>
       </c>
@@ -18328,7 +18330,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A100" s="20" t="s">
         <v>114</v>
       </c>
@@ -18357,7 +18359,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A101" s="20" t="s">
         <v>114</v>
       </c>
@@ -18386,7 +18388,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A102" s="20" t="s">
         <v>114</v>
       </c>
@@ -18415,7 +18417,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A103" s="20" t="s">
         <v>114</v>
       </c>
@@ -18444,7 +18446,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A104" s="20" t="s">
         <v>114</v>
       </c>
@@ -18473,7 +18475,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A105" s="20" t="s">
         <v>114</v>
       </c>
@@ -18502,7 +18504,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A106" s="20" t="s">
         <v>114</v>
       </c>
@@ -18531,7 +18533,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A107" s="20" t="s">
         <v>114</v>
       </c>
@@ -18560,7 +18562,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A108" s="20" t="s">
         <v>114</v>
       </c>
@@ -18589,7 +18591,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A109" s="20" t="s">
         <v>114</v>
       </c>
@@ -18618,7 +18620,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A110" s="20" t="s">
         <v>114</v>
       </c>
@@ -18647,7 +18649,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A111" s="20" t="s">
         <v>114</v>
       </c>
@@ -18676,7 +18678,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A112" s="20" t="s">
         <v>114</v>
       </c>
@@ -18705,7 +18707,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A113" s="20" t="s">
         <v>114</v>
       </c>
@@ -18734,7 +18736,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A114" s="20" t="s">
         <v>114</v>
       </c>
@@ -18763,7 +18765,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A115" s="20" t="s">
         <v>114</v>
       </c>
@@ -18792,7 +18794,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A116" s="20" t="s">
         <v>114</v>
       </c>
@@ -18821,7 +18823,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A117" s="20" t="s">
         <v>114</v>
       </c>
@@ -18850,7 +18852,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A118" s="20" t="s">
         <v>114</v>
       </c>
@@ -18879,7 +18881,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A119" s="20" t="s">
         <v>114</v>
       </c>
@@ -18908,7 +18910,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A120" s="20" t="s">
         <v>114</v>
       </c>
@@ -18937,7 +18939,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A121" s="20" t="s">
         <v>114</v>
       </c>
@@ -18966,7 +18968,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A122" s="20" t="s">
         <v>114</v>
       </c>
@@ -18995,7 +18997,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A123" s="20" t="s">
         <v>114</v>
       </c>
@@ -19024,7 +19026,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A124" s="20" t="s">
         <v>114</v>
       </c>
@@ -19053,7 +19055,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A125" s="20" t="s">
         <v>114</v>
       </c>
@@ -19082,7 +19084,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A126" s="20" t="s">
         <v>114</v>
       </c>
@@ -19111,7 +19113,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A127" s="20" t="s">
         <v>114</v>
       </c>
@@ -19140,7 +19142,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A128" s="20" t="s">
         <v>114</v>
       </c>
@@ -19169,7 +19171,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A129" s="20" t="s">
         <v>114</v>
       </c>
@@ -19198,7 +19200,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A130" s="20" t="s">
         <v>114</v>
       </c>
@@ -19227,7 +19229,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A131" s="20" t="s">
         <v>114</v>
       </c>
@@ -19256,7 +19258,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A132" s="20" t="s">
         <v>114</v>
       </c>
@@ -19285,7 +19287,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A133" s="20" t="s">
         <v>114</v>
       </c>
@@ -19314,7 +19316,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A134" s="20" t="s">
         <v>114</v>
       </c>
@@ -19343,7 +19345,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A135" s="20" t="s">
         <v>114</v>
       </c>
@@ -19372,7 +19374,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A136" s="20" t="s">
         <v>114</v>
       </c>
@@ -19401,7 +19403,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A137" s="20" t="s">
         <v>114</v>
       </c>
@@ -19430,7 +19432,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A138" s="20" t="s">
         <v>114</v>
       </c>
@@ -19459,7 +19461,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A139" s="20" t="s">
         <v>114</v>
       </c>
@@ -19488,7 +19490,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A140" s="20" t="s">
         <v>114</v>
       </c>
@@ -19517,7 +19519,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A141" s="20" t="s">
         <v>114</v>
       </c>
@@ -19546,7 +19548,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A142" s="20" t="s">
         <v>114</v>
       </c>
@@ -19575,7 +19577,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A143" s="20" t="s">
         <v>114</v>
       </c>
@@ -19604,7 +19606,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A144" s="20" t="s">
         <v>114</v>
       </c>
@@ -19633,7 +19635,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A145" s="20" t="s">
         <v>114</v>
       </c>
@@ -19662,7 +19664,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A146" s="20" t="s">
         <v>114</v>
       </c>
@@ -19691,7 +19693,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A147" s="20" t="s">
         <v>114</v>
       </c>
@@ -19720,7 +19722,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A148" s="20" t="s">
         <v>114</v>
       </c>
@@ -19749,7 +19751,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A149" s="20" t="s">
         <v>114</v>
       </c>
@@ -19778,7 +19780,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A150" s="20" t="s">
         <v>114</v>
       </c>
@@ -19807,7 +19809,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A151" s="20" t="s">
         <v>114</v>
       </c>
@@ -19836,7 +19838,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A152" s="20" t="s">
         <v>114</v>
       </c>
@@ -19865,7 +19867,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A153" s="20" t="s">
         <v>114</v>
       </c>
@@ -19898,7 +19900,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A154" s="20" t="s">
         <v>114</v>
       </c>
@@ -19931,7 +19933,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A155" s="20" t="s">
         <v>114</v>
       </c>
@@ -19960,7 +19962,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A156" s="20" t="s">
         <v>114</v>
       </c>
@@ -19989,7 +19991,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A157" s="20" t="s">
         <v>114</v>
       </c>
@@ -20018,7 +20020,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A158" s="20" t="s">
         <v>114</v>
       </c>
@@ -20047,7 +20049,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A159" s="20" t="s">
         <v>114</v>
       </c>
@@ -20080,7 +20082,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A160" s="20" t="s">
         <v>114</v>
       </c>
@@ -20113,7 +20115,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A161" s="20" t="s">
         <v>114</v>
       </c>
@@ -20146,7 +20148,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A162" s="20" t="s">
         <v>114</v>
       </c>
@@ -20179,7 +20181,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A163" s="20" t="s">
         <v>114</v>
       </c>
@@ -20212,7 +20214,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A164" s="20" t="s">
         <v>114</v>
       </c>
@@ -20245,7 +20247,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A165" s="20" t="s">
         <v>114</v>
       </c>
@@ -20274,7 +20276,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A166" s="20" t="s">
         <v>114</v>
       </c>
@@ -20303,7 +20305,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A167" s="20" t="s">
         <v>114</v>
       </c>
@@ -20332,7 +20334,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A168" s="20" t="s">
         <v>114</v>
       </c>
@@ -20361,7 +20363,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A169" s="20" t="s">
         <v>114</v>
       </c>
@@ -20394,7 +20396,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A170" s="20" t="s">
         <v>114</v>
       </c>
@@ -20427,7 +20429,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A171" s="20" t="s">
         <v>114</v>
       </c>
@@ -20460,7 +20462,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A172" s="20" t="s">
         <v>114</v>
       </c>
@@ -20493,7 +20495,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A173" s="20" t="s">
         <v>114</v>
       </c>
@@ -20526,7 +20528,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A174" s="20" t="s">
         <v>114</v>
       </c>
@@ -20559,7 +20561,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A175" s="20" t="s">
         <v>114</v>
       </c>
@@ -20588,7 +20590,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A176" s="20" t="s">
         <v>114</v>
       </c>
@@ -20617,7 +20619,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A177" s="20" t="s">
         <v>114</v>
       </c>
@@ -20646,7 +20648,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A178" s="20" t="s">
         <v>114</v>
       </c>
@@ -20675,7 +20677,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A179" s="20" t="s">
         <v>114</v>
       </c>
@@ -20708,7 +20710,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A180" s="20" t="s">
         <v>114</v>
       </c>
@@ -20741,7 +20743,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A181" s="20" t="s">
         <v>114</v>
       </c>
@@ -20774,7 +20776,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A182" s="20" t="s">
         <v>114</v>
       </c>
@@ -20807,7 +20809,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A183" s="20" t="s">
         <v>114</v>
       </c>
@@ -20840,7 +20842,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A184" s="20" t="s">
         <v>114</v>
       </c>
@@ -20873,7 +20875,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A185" s="20" t="s">
         <v>114</v>
       </c>
@@ -20902,7 +20904,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A186" s="20" t="s">
         <v>114</v>
       </c>
@@ -20931,7 +20933,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A187" s="20" t="s">
         <v>114</v>
       </c>
@@ -20960,7 +20962,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A188" s="20" t="s">
         <v>114</v>
       </c>
@@ -20989,7 +20991,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A189" s="20" t="s">
         <v>114</v>
       </c>
@@ -21022,7 +21024,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A190" s="20" t="s">
         <v>114</v>
       </c>
@@ -21055,7 +21057,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A191" s="20" t="s">
         <v>114</v>
       </c>
@@ -21088,7 +21090,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A192" s="20" t="s">
         <v>114</v>
       </c>
@@ -21121,7 +21123,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A193" s="20" t="s">
         <v>114</v>
       </c>
@@ -21154,7 +21156,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A194" s="20" t="s">
         <v>114</v>
       </c>
@@ -21187,7 +21189,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A195" s="20" t="s">
         <v>114</v>
       </c>
@@ -21213,7 +21215,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A196" s="20" t="s">
         <v>114</v>
       </c>
@@ -21242,7 +21244,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A197" s="20" t="s">
         <v>114</v>
       </c>
@@ -21271,7 +21273,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A198" s="20" t="s">
         <v>114</v>
       </c>
@@ -21300,7 +21302,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A199" s="20" t="s">
         <v>114</v>
       </c>
@@ -21330,7 +21332,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A200" s="20" t="s">
         <v>114</v>
       </c>
@@ -21363,7 +21365,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A201" s="20" t="s">
         <v>114</v>
       </c>
@@ -21396,7 +21398,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A202" s="20" t="s">
         <v>114</v>
       </c>
@@ -21429,7 +21431,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A203" s="20" t="s">
         <v>114</v>
       </c>
@@ -21462,7 +21464,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A204" s="20" t="s">
         <v>114</v>
       </c>
@@ -21495,7 +21497,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A205" s="20" t="s">
         <v>114</v>
       </c>
@@ -21524,7 +21526,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A206" s="20" t="s">
         <v>114</v>
       </c>
@@ -21553,7 +21555,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A207" s="20" t="s">
         <v>114</v>
       </c>
@@ -21582,7 +21584,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A208" s="20" t="s">
         <v>114</v>
       </c>
@@ -21611,7 +21613,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A209" s="20" t="s">
         <v>114</v>
       </c>
@@ -21644,7 +21646,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A210" s="20" t="s">
         <v>114</v>
       </c>
@@ -21677,7 +21679,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A211" s="20" t="s">
         <v>114</v>
       </c>
@@ -21710,7 +21712,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A212" s="20" t="s">
         <v>114</v>
       </c>
@@ -21743,7 +21745,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A213" s="20" t="s">
         <v>114</v>
       </c>
@@ -21776,7 +21778,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A214" s="20" t="s">
         <v>114</v>
       </c>
@@ -21809,7 +21811,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A215" s="20" t="s">
         <v>114</v>
       </c>
@@ -21838,7 +21840,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A216" s="20" t="s">
         <v>114</v>
       </c>
@@ -21867,7 +21869,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A217" s="20" t="s">
         <v>114</v>
       </c>
@@ -21896,7 +21898,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A218" s="20" t="s">
         <v>114</v>
       </c>
@@ -21925,7 +21927,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A219" s="20" t="s">
         <v>114</v>
       </c>
@@ -21958,7 +21960,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A220" s="20" t="s">
         <v>114</v>
       </c>
@@ -21991,7 +21993,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A221" s="20" t="s">
         <v>114</v>
       </c>
@@ -22024,7 +22026,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A222" s="20" t="s">
         <v>114</v>
       </c>
@@ -22057,7 +22059,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A223" s="20" t="s">
         <v>114</v>
       </c>
@@ -22090,7 +22092,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A224" s="20" t="s">
         <v>114</v>
       </c>
@@ -22123,7 +22125,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A225" s="20" t="s">
         <v>114</v>
       </c>
@@ -22152,7 +22154,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A226" s="20" t="s">
         <v>114</v>
       </c>
@@ -22181,7 +22183,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A227" s="20" t="s">
         <v>114</v>
       </c>
@@ -22210,7 +22212,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A228" s="20" t="s">
         <v>114</v>
       </c>
@@ -22239,7 +22241,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A229" s="20" t="s">
         <v>114</v>
       </c>
@@ -22272,7 +22274,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A230" s="20" t="s">
         <v>114</v>
       </c>
@@ -22305,7 +22307,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A231" s="20" t="s">
         <v>114</v>
       </c>
@@ -22338,7 +22340,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A232" s="20" t="s">
         <v>114</v>
       </c>
@@ -22371,7 +22373,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A233" s="20" t="s">
         <v>114</v>
       </c>
@@ -22400,7 +22402,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A234" s="20" t="s">
         <v>114</v>
       </c>
@@ -22429,7 +22431,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A235" s="20" t="s">
         <v>114</v>
       </c>
@@ -22458,7 +22460,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A236" s="20" t="s">
         <v>114</v>
       </c>
@@ -22487,7 +22489,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A237" s="20" t="s">
         <v>114</v>
       </c>
@@ -22516,7 +22518,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A238" s="20" t="s">
         <v>114</v>
       </c>
@@ -22549,7 +22551,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A239" s="20" t="s">
         <v>114</v>
       </c>
@@ -22582,7 +22584,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A240" s="20" t="s">
         <v>114</v>
       </c>
@@ -22615,7 +22617,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A241" s="20" t="s">
         <v>114</v>
       </c>
@@ -22648,7 +22650,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A242" s="20" t="s">
         <v>114</v>
       </c>
@@ -22681,7 +22683,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A243" s="20" t="s">
         <v>114</v>
       </c>
@@ -22710,7 +22712,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A244" s="20" t="s">
         <v>114</v>
       </c>
@@ -22739,7 +22741,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A245" s="20" t="s">
         <v>114</v>
       </c>
@@ -22768,7 +22770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A246" s="20" t="s">
         <v>114</v>
       </c>
@@ -22797,7 +22799,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A247" s="20" t="s">
         <v>114</v>
       </c>
@@ -22826,7 +22828,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A248" s="20" t="s">
         <v>114</v>
       </c>
@@ -22855,7 +22857,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A249" s="20" t="s">
         <v>114</v>
       </c>
@@ -22884,7 +22886,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A250" s="20" t="s">
         <v>114</v>
       </c>
@@ -22913,7 +22915,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A251" s="20" t="s">
         <v>114</v>
       </c>
@@ -22942,7 +22944,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A252" s="20" t="s">
         <v>114</v>
       </c>
@@ -22971,7 +22973,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A253" s="20" t="s">
         <v>114</v>
       </c>
@@ -23000,7 +23002,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A254" s="20" t="s">
         <v>114</v>
       </c>
@@ -23029,7 +23031,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A255" s="20" t="s">
         <v>114</v>
       </c>
@@ -23058,7 +23060,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A256" s="20" t="s">
         <v>114</v>
       </c>
@@ -23087,7 +23089,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A257" s="20" t="s">
         <v>114</v>
       </c>
@@ -23116,7 +23118,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A258" s="20" t="s">
         <v>114</v>
       </c>
@@ -23145,7 +23147,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A259" s="20" t="s">
         <v>114</v>
       </c>
@@ -23174,7 +23176,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A260" s="20" t="s">
         <v>114</v>
       </c>
@@ -23203,7 +23205,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A261" s="20" t="s">
         <v>114</v>
       </c>
@@ -23232,7 +23234,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A262" s="20" t="s">
         <v>114</v>
       </c>
@@ -23261,7 +23263,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A263" s="20" t="s">
         <v>114</v>
       </c>
@@ -23290,7 +23292,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A264" s="20" t="s">
         <v>114</v>
       </c>
@@ -23319,7 +23321,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A265" s="20" t="s">
         <v>114</v>
       </c>
@@ -23348,7 +23350,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A266" s="20" t="s">
         <v>114</v>
       </c>
@@ -23377,7 +23379,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A267" s="20" t="s">
         <v>114</v>
       </c>
@@ -23406,7 +23408,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A268" s="20" t="s">
         <v>114</v>
       </c>
@@ -23435,7 +23437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A269" s="20" t="s">
         <v>114</v>
       </c>
@@ -23464,7 +23466,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A270" s="20" t="s">
         <v>114</v>
       </c>
@@ -23493,7 +23495,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A271" s="20" t="s">
         <v>114</v>
       </c>
@@ -23522,7 +23524,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A272" s="20" t="s">
         <v>114</v>
       </c>
@@ -23551,7 +23553,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A273" s="20" t="s">
         <v>114</v>
       </c>
@@ -23580,7 +23582,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A274" s="20" t="s">
         <v>114</v>
       </c>
@@ -23609,7 +23611,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A275" s="20" t="s">
         <v>114</v>
       </c>
@@ -23638,7 +23640,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A276" s="20" t="s">
         <v>114</v>
       </c>
@@ -23667,7 +23669,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A277" s="20" t="s">
         <v>114</v>
       </c>
@@ -23696,7 +23698,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A278" s="20" t="s">
         <v>114</v>
       </c>
@@ -23725,7 +23727,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A279" s="20" t="s">
         <v>114</v>
       </c>
@@ -23754,7 +23756,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A280" s="20" t="s">
         <v>114</v>
       </c>
@@ -23783,7 +23785,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A281" s="20" t="s">
         <v>114</v>
       </c>
@@ -23812,7 +23814,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A282" s="20" t="s">
         <v>114</v>
       </c>
@@ -23841,7 +23843,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A283" s="20" t="s">
         <v>114</v>
       </c>
@@ -23870,7 +23872,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A284" s="20" t="s">
         <v>114</v>
       </c>
@@ -23899,7 +23901,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A285" s="20" t="s">
         <v>114</v>
       </c>
@@ -23928,7 +23930,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A286" s="20" t="s">
         <v>114</v>
       </c>
@@ -23957,7 +23959,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A287" s="20" t="s">
         <v>114</v>
       </c>
@@ -23986,7 +23988,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A288" s="20" t="s">
         <v>114</v>
       </c>
@@ -24015,7 +24017,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A289" s="20" t="s">
         <v>114</v>
       </c>
@@ -24044,7 +24046,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A290" s="20" t="s">
         <v>114</v>
       </c>
@@ -24073,7 +24075,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A291" s="20" t="s">
         <v>114</v>
       </c>
@@ -24102,7 +24104,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A292" s="20" t="s">
         <v>114</v>
       </c>
@@ -24131,7 +24133,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A293" s="20" t="s">
         <v>114</v>
       </c>
@@ -24160,7 +24162,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A294" s="20" t="s">
         <v>114</v>
       </c>
@@ -24189,7 +24191,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A295" s="20" t="s">
         <v>114</v>
       </c>
@@ -24218,7 +24220,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A296" s="20" t="s">
         <v>114</v>
       </c>
@@ -24247,7 +24249,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A297" s="20" t="s">
         <v>114</v>
       </c>
@@ -24276,7 +24278,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A298" s="20" t="s">
         <v>114</v>
       </c>
@@ -24305,7 +24307,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A299" s="20" t="s">
         <v>114</v>
       </c>
@@ -24334,7 +24336,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A300" s="20" t="s">
         <v>114</v>
       </c>
@@ -24363,7 +24365,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A301" s="20" t="s">
         <v>114</v>
       </c>
@@ -24392,7 +24394,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A302" s="20" t="s">
         <v>114</v>
       </c>
@@ -24421,7 +24423,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A303" s="20" t="s">
         <v>114</v>
       </c>
@@ -24450,7 +24452,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A304" s="20" t="s">
         <v>114</v>
       </c>
@@ -24479,7 +24481,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A305" s="20" t="s">
         <v>114</v>
       </c>
@@ -24508,7 +24510,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A306" s="20" t="s">
         <v>114</v>
       </c>
@@ -24537,7 +24539,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A307" s="20" t="s">
         <v>114</v>
       </c>
@@ -24570,7 +24572,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A308" s="20" t="s">
         <v>114</v>
       </c>
@@ -24603,7 +24605,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A309" s="20" t="s">
         <v>114</v>
       </c>
@@ -24636,7 +24638,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A310" s="20" t="s">
         <v>114</v>
       </c>
@@ -24669,7 +24671,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A311" s="20" t="s">
         <v>114</v>
       </c>
@@ -24698,7 +24700,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A312" s="20" t="s">
         <v>114</v>
       </c>
@@ -24727,7 +24729,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A313" s="20" t="s">
         <v>114</v>
       </c>
@@ -24756,7 +24758,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A314" s="20" t="s">
         <v>114</v>
       </c>
@@ -24785,7 +24787,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A315" s="20" t="s">
         <v>114</v>
       </c>
@@ -24814,7 +24816,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A316" s="20" t="s">
         <v>114</v>
       </c>
@@ -24843,7 +24845,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A317" s="20" t="s">
         <v>114</v>
       </c>
@@ -24876,7 +24878,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A318" s="20" t="s">
         <v>114</v>
       </c>
@@ -24909,7 +24911,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A319" s="20" t="s">
         <v>114</v>
       </c>
@@ -24942,7 +24944,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A320" s="20" t="s">
         <v>114</v>
       </c>
@@ -24975,7 +24977,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A321" s="20" t="s">
         <v>114</v>
       </c>
@@ -25004,7 +25006,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A322" s="20" t="s">
         <v>114</v>
       </c>
@@ -25033,7 +25035,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A323" s="20" t="s">
         <v>114</v>
       </c>
@@ -25062,7 +25064,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A324" s="20" t="s">
         <v>114</v>
       </c>
@@ -25091,7 +25093,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A325" s="20" t="s">
         <v>114</v>
       </c>
@@ -25120,7 +25122,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A326" s="20" t="s">
         <v>114</v>
       </c>
@@ -25149,7 +25151,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A327" s="20" t="s">
         <v>114</v>
       </c>
@@ -25182,7 +25184,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A328" s="20" t="s">
         <v>114</v>
       </c>
@@ -25215,7 +25217,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A329" s="20" t="s">
         <v>114</v>
       </c>
@@ -25248,7 +25250,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A330" s="20" t="s">
         <v>114</v>
       </c>
@@ -25281,7 +25283,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A331" s="20" t="s">
         <v>114</v>
       </c>
@@ -25310,7 +25312,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A332" s="20" t="s">
         <v>114</v>
       </c>
@@ -25339,7 +25341,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A333" s="20" t="s">
         <v>114</v>
       </c>
@@ -25368,7 +25370,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A334" s="20" t="s">
         <v>114</v>
       </c>
@@ -25397,7 +25399,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A335" s="20" t="s">
         <v>114</v>
       </c>
@@ -25426,7 +25428,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A336" s="20" t="s">
         <v>114</v>
       </c>
@@ -25455,7 +25457,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A337" s="20" t="s">
         <v>114</v>
       </c>
@@ -25488,7 +25490,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A338" s="20" t="s">
         <v>114</v>
       </c>
@@ -25521,7 +25523,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A339" s="20" t="s">
         <v>114</v>
       </c>
@@ -25554,7 +25556,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A340" s="20" t="s">
         <v>114</v>
       </c>
@@ -25587,7 +25589,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A341" s="20" t="s">
         <v>114</v>
       </c>
@@ -25616,7 +25618,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A342" s="20" t="s">
         <v>114</v>
       </c>
@@ -25645,7 +25647,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A343" s="20" t="s">
         <v>114</v>
       </c>
@@ -25671,7 +25673,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A344" s="20" t="s">
         <v>114</v>
       </c>
@@ -25700,7 +25702,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A345" s="20" t="s">
         <v>114</v>
       </c>
@@ -25729,7 +25731,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A346" s="20" t="s">
         <v>114</v>
       </c>
@@ -25758,7 +25760,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A347" s="20" t="s">
         <v>114</v>
       </c>
@@ -25788,7 +25790,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A348" s="20" t="s">
         <v>114</v>
       </c>
@@ -25821,7 +25823,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A349" s="20" t="s">
         <v>114</v>
       </c>
@@ -25854,7 +25856,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A350" s="20" t="s">
         <v>114</v>
       </c>
@@ -25887,7 +25889,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A351" s="20" t="s">
         <v>114</v>
       </c>
@@ -25913,7 +25915,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A352" s="20" t="s">
         <v>114</v>
       </c>
@@ -25942,7 +25944,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A353" s="20" t="s">
         <v>114</v>
       </c>
@@ -25971,7 +25973,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A354" s="20" t="s">
         <v>114</v>
       </c>
@@ -26000,7 +26002,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A355" s="20" t="s">
         <v>114</v>
       </c>
@@ -26029,7 +26031,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A356" s="20" t="s">
         <v>114</v>
       </c>
@@ -26058,7 +26060,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A357" s="20" t="s">
         <v>114</v>
       </c>
@@ -26091,7 +26093,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A358" s="20" t="s">
         <v>114</v>
       </c>
@@ -26124,7 +26126,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A359" s="20" t="s">
         <v>114</v>
       </c>
@@ -26157,7 +26159,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A360" s="20" t="s">
         <v>114</v>
       </c>
@@ -26190,7 +26192,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A361" s="20" t="s">
         <v>114</v>
       </c>
@@ -26219,7 +26221,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A362" s="20" t="s">
         <v>114</v>
       </c>
@@ -26248,7 +26250,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A363" s="20" t="s">
         <v>114</v>
       </c>
@@ -26277,7 +26279,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A364" s="20" t="s">
         <v>114</v>
       </c>
@@ -26306,7 +26308,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A365" s="20" t="s">
         <v>114</v>
       </c>
@@ -26335,7 +26337,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A366" s="20" t="s">
         <v>114</v>
       </c>
@@ -26364,7 +26366,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A367" s="20" t="s">
         <v>114</v>
       </c>
@@ -26397,7 +26399,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A368" s="20" t="s">
         <v>114</v>
       </c>
@@ -26430,7 +26432,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A369" s="20" t="s">
         <v>114</v>
       </c>
@@ -26463,7 +26465,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A370" s="20" t="s">
         <v>114</v>
       </c>
@@ -26496,7 +26498,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A371" s="20" t="s">
         <v>114</v>
       </c>
@@ -26525,7 +26527,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A372" s="20" t="s">
         <v>114</v>
       </c>
@@ -26554,7 +26556,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A373" s="20" t="s">
         <v>114</v>
       </c>
@@ -26583,7 +26585,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A374" s="20" t="s">
         <v>114</v>
       </c>
@@ -26612,7 +26614,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A375" s="20" t="s">
         <v>114</v>
       </c>
@@ -26641,7 +26643,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A376" s="20" t="s">
         <v>114</v>
       </c>
@@ -26670,7 +26672,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A377" s="20" t="s">
         <v>114</v>
       </c>
@@ -26703,7 +26705,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A378" s="20" t="s">
         <v>114</v>
       </c>
@@ -26736,7 +26738,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A379" s="20" t="s">
         <v>114</v>
       </c>
@@ -26769,7 +26771,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A380" s="20" t="s">
         <v>114</v>
       </c>
@@ -26802,7 +26804,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A381" s="20" t="s">
         <v>114</v>
       </c>
@@ -26831,7 +26833,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A382" s="20" t="s">
         <v>114</v>
       </c>
@@ -26860,7 +26862,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A383" s="20" t="s">
         <v>114</v>
       </c>
@@ -26889,7 +26891,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A384" s="20" t="s">
         <v>114</v>
       </c>
@@ -26918,7 +26920,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A385" s="20" t="s">
         <v>114</v>
       </c>
@@ -26947,7 +26949,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A386" s="20" t="s">
         <v>114</v>
       </c>
@@ -26976,7 +26978,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A387" s="20" t="s">
         <v>114</v>
       </c>
@@ -27005,7 +27007,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A388" s="20" t="s">
         <v>114</v>
       </c>
@@ -27038,7 +27040,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A389" s="20" t="s">
         <v>114</v>
       </c>
@@ -27071,7 +27073,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A390" s="20" t="s">
         <v>114</v>
       </c>
@@ -27104,7 +27106,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A391" s="20" t="s">
         <v>114</v>
       </c>
@@ -27137,7 +27139,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A392" s="20" t="s">
         <v>114</v>
       </c>
@@ -27170,7 +27172,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A393" s="20" t="s">
         <v>114</v>
       </c>
@@ -27199,7 +27201,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A394" s="20" t="s">
         <v>114</v>
       </c>
@@ -27228,7 +27230,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A395" s="20" t="s">
         <v>114</v>
       </c>
@@ -27257,7 +27259,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A396" s="20" t="s">
         <v>114</v>
       </c>
@@ -27286,7 +27288,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A397" s="20" t="s">
         <v>114</v>
       </c>
@@ -27315,7 +27317,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A398" s="20" t="s">
         <v>114</v>
       </c>
@@ -27344,7 +27346,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A399" s="20" t="s">
         <v>114</v>
       </c>
@@ -27373,7 +27375,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A400" s="20" t="s">
         <v>114</v>
       </c>
@@ -27402,7 +27404,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A401" s="20" t="s">
         <v>114</v>
       </c>
@@ -27431,7 +27433,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A402" s="20" t="s">
         <v>114</v>
       </c>
@@ -27460,7 +27462,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A403" s="20" t="s">
         <v>114</v>
       </c>
@@ -27489,7 +27491,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A404" s="20" t="s">
         <v>114</v>
       </c>
@@ -27518,7 +27520,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A405" s="20" t="s">
         <v>114</v>
       </c>
@@ -27547,7 +27549,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A406" s="20" t="s">
         <v>114</v>
       </c>
@@ -27576,7 +27578,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A407" s="20" t="s">
         <v>114</v>
       </c>
@@ -27605,7 +27607,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A408" s="20" t="s">
         <v>114</v>
       </c>
@@ -27634,7 +27636,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A409" s="20" t="s">
         <v>114</v>
       </c>
@@ -27663,7 +27665,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A410" s="20" t="s">
         <v>114</v>
       </c>
@@ -27692,7 +27694,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A411" s="20" t="s">
         <v>114</v>
       </c>
@@ -27721,7 +27723,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A412" s="20" t="s">
         <v>114</v>
       </c>
@@ -27750,7 +27752,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A413" s="20" t="s">
         <v>114</v>
       </c>
@@ -27779,7 +27781,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A414" s="20" t="s">
         <v>114</v>
       </c>
@@ -27808,7 +27810,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A415" s="20" t="s">
         <v>114</v>
       </c>
@@ -27837,7 +27839,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A416" s="20" t="s">
         <v>114</v>
       </c>
@@ -27866,7 +27868,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A417" s="20" t="s">
         <v>114</v>
       </c>
@@ -27895,7 +27897,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A418" s="20" t="s">
         <v>114</v>
       </c>
@@ -27924,7 +27926,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A419" s="20" t="s">
         <v>114</v>
       </c>
@@ -27953,7 +27955,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A420" s="20" t="s">
         <v>114</v>
       </c>
@@ -27982,7 +27984,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A421" s="20" t="s">
         <v>114</v>
       </c>
@@ -28011,7 +28013,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A422" s="20" t="s">
         <v>114</v>
       </c>
@@ -28040,7 +28042,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A423" s="20" t="s">
         <v>114</v>
       </c>
@@ -28069,7 +28071,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A424" s="20" t="s">
         <v>114</v>
       </c>
@@ -28098,7 +28100,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A425" s="20" t="s">
         <v>114</v>
       </c>
@@ -28127,7 +28129,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A426" s="20" t="s">
         <v>114</v>
       </c>
@@ -28156,7 +28158,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A427" s="20" t="s">
         <v>114</v>
       </c>
@@ -28185,7 +28187,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A428" s="20" t="s">
         <v>114</v>
       </c>
@@ -28214,7 +28216,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A429" s="20" t="s">
         <v>114</v>
       </c>
@@ -28243,7 +28245,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A430" s="20" t="s">
         <v>114</v>
       </c>
@@ -28272,7 +28274,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A431" s="20" t="s">
         <v>114</v>
       </c>
@@ -28301,7 +28303,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A432" s="20" t="s">
         <v>114</v>
       </c>
@@ -28330,7 +28332,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A433" s="20" t="s">
         <v>114</v>
       </c>
@@ -28359,7 +28361,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A434" s="20" t="s">
         <v>114</v>
       </c>
@@ -28388,7 +28390,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A435" s="20" t="s">
         <v>114</v>
       </c>
@@ -28417,7 +28419,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A436" s="20" t="s">
         <v>114</v>
       </c>
@@ -28446,7 +28448,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A437" s="20" t="s">
         <v>114</v>
       </c>
@@ -28475,7 +28477,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A438" s="20" t="s">
         <v>114</v>
       </c>
@@ -28504,7 +28506,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A439" s="20" t="s">
         <v>114</v>
       </c>
@@ -28533,7 +28535,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A440" s="20" t="s">
         <v>114</v>
       </c>
@@ -28562,7 +28564,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A441" s="20" t="s">
         <v>114</v>
       </c>
@@ -28591,7 +28593,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A442" s="20" t="s">
         <v>114</v>
       </c>
@@ -28620,7 +28622,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A443" s="20" t="s">
         <v>114</v>
       </c>
@@ -28649,7 +28651,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A444" s="20" t="s">
         <v>114</v>
       </c>
@@ -28678,7 +28680,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A445" s="20" t="s">
         <v>114</v>
       </c>
@@ -28707,7 +28709,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A446" s="20" t="s">
         <v>114</v>
       </c>
@@ -28736,7 +28738,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A447" s="20" t="s">
         <v>114</v>
       </c>
@@ -28765,7 +28767,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A448" s="20" t="s">
         <v>114</v>
       </c>
@@ -28794,7 +28796,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A449" s="20" t="s">
         <v>114</v>
       </c>
@@ -28823,7 +28825,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A450" s="20" t="s">
         <v>114</v>
       </c>
@@ -28852,7 +28854,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A451" s="20" t="s">
         <v>114</v>
       </c>
@@ -28881,7 +28883,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A452" s="20" t="s">
         <v>114</v>
       </c>
@@ -28910,7 +28912,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A453" s="20" t="s">
         <v>114</v>
       </c>
@@ -28939,7 +28941,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A454" s="20" t="s">
         <v>114</v>
       </c>
@@ -28968,7 +28970,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A455" s="20" t="s">
         <v>114</v>
       </c>
@@ -29001,7 +29003,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A456" s="20" t="s">
         <v>114</v>
       </c>
@@ -29034,7 +29036,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A457" s="20" t="s">
         <v>114</v>
       </c>
@@ -29067,7 +29069,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A458" s="20" t="s">
         <v>114</v>
       </c>
@@ -29100,7 +29102,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A459" s="20" t="s">
         <v>114</v>
       </c>
@@ -29129,7 +29131,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A460" s="20" t="s">
         <v>114</v>
       </c>
@@ -29158,7 +29160,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A461" s="20" t="s">
         <v>114</v>
       </c>
@@ -29187,7 +29189,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A462" s="20" t="s">
         <v>114</v>
       </c>
@@ -29216,7 +29218,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A463" s="20" t="s">
         <v>114</v>
       </c>
@@ -29245,7 +29247,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A464" s="20" t="s">
         <v>114</v>
       </c>
@@ -29274,7 +29276,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A465" s="20" t="s">
         <v>114</v>
       </c>
@@ -29307,7 +29309,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A466" s="20" t="s">
         <v>114</v>
       </c>
@@ -29340,7 +29342,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A467" s="20" t="s">
         <v>114</v>
       </c>
@@ -29373,7 +29375,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A468" s="20" t="s">
         <v>114</v>
       </c>
@@ -29406,7 +29408,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A469" s="20" t="s">
         <v>114</v>
       </c>
@@ -29435,7 +29437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A470" s="20" t="s">
         <v>114</v>
       </c>
@@ -29464,7 +29466,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A471" s="20" t="s">
         <v>114</v>
       </c>
@@ -29493,7 +29495,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A472" s="20" t="s">
         <v>114</v>
       </c>
@@ -29522,7 +29524,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A473" s="20" t="s">
         <v>114</v>
       </c>
@@ -29551,7 +29553,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A474" s="20" t="s">
         <v>114</v>
       </c>
@@ -29580,7 +29582,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A475" s="20" t="s">
         <v>114</v>
       </c>
@@ -29613,7 +29615,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A476" s="20" t="s">
         <v>114</v>
       </c>
@@ -29646,7 +29648,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A477" s="20" t="s">
         <v>114</v>
       </c>
@@ -29679,7 +29681,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A478" s="20" t="s">
         <v>114</v>
       </c>
@@ -29712,7 +29714,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A479" s="20" t="s">
         <v>114</v>
       </c>
@@ -29741,7 +29743,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A480" s="20" t="s">
         <v>114</v>
       </c>
@@ -29770,7 +29772,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A481" s="20" t="s">
         <v>114</v>
       </c>
@@ -29799,7 +29801,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A482" s="20" t="s">
         <v>114</v>
       </c>
@@ -29828,7 +29830,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A483" s="20" t="s">
         <v>114</v>
       </c>
@@ -29857,7 +29859,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A484" s="20" t="s">
         <v>114</v>
       </c>
@@ -29886,7 +29888,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A485" s="20" t="s">
         <v>114</v>
       </c>
@@ -29919,7 +29921,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A486" s="20" t="s">
         <v>114</v>
       </c>
@@ -29952,7 +29954,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A487" s="20" t="s">
         <v>114</v>
       </c>
@@ -29985,7 +29987,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A488" s="20" t="s">
         <v>114</v>
       </c>
@@ -30018,7 +30020,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A489" s="20" t="s">
         <v>114</v>
       </c>
@@ -30047,7 +30049,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A490" s="20" t="s">
         <v>114</v>
       </c>
@@ -30076,7 +30078,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A491" s="20" t="s">
         <v>114</v>
       </c>
@@ -30105,7 +30107,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A492" s="20" t="s">
         <v>114</v>
       </c>
@@ -30134,7 +30136,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A493" s="20" t="s">
         <v>114</v>
       </c>
@@ -30163,7 +30165,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A494" s="20" t="s">
         <v>114</v>
       </c>
@@ -30192,7 +30194,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A495" s="20" t="s">
         <v>114</v>
       </c>
@@ -30222,7 +30224,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A496" s="20" t="s">
         <v>114</v>
       </c>
@@ -30255,7 +30257,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A497" s="20" t="s">
         <v>114</v>
       </c>
@@ -30288,7 +30290,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A498" s="20" t="s">
         <v>114</v>
       </c>
@@ -30321,7 +30323,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A499" s="20" t="s">
         <v>114</v>
       </c>
@@ -30347,7 +30349,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A500" s="20" t="s">
         <v>114</v>
       </c>
@@ -30376,7 +30378,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A501" s="20" t="s">
         <v>114</v>
       </c>
@@ -30405,7 +30407,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A502" s="20" t="s">
         <v>114</v>
       </c>
@@ -30434,7 +30436,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A503" s="20" t="s">
         <v>114</v>
       </c>
@@ -30463,7 +30465,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A504" s="20" t="s">
         <v>114</v>
       </c>
@@ -30492,7 +30494,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A505" s="20" t="s">
         <v>114</v>
       </c>
@@ -30525,7 +30527,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A506" s="20" t="s">
         <v>114</v>
       </c>
@@ -30558,7 +30560,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A507" s="20" t="s">
         <v>114</v>
       </c>
@@ -30591,7 +30593,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A508" s="20" t="s">
         <v>114</v>
       </c>
@@ -30624,7 +30626,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A509" s="20" t="s">
         <v>114</v>
       </c>
@@ -30653,7 +30655,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A510" s="20" t="s">
         <v>114</v>
       </c>
@@ -30682,7 +30684,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A511" s="20" t="s">
         <v>114</v>
       </c>
@@ -30711,7 +30713,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A512" s="20" t="s">
         <v>114</v>
       </c>
@@ -30740,7 +30742,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A513" s="20" t="s">
         <v>114</v>
       </c>
@@ -30769,7 +30771,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A514" s="20" t="s">
         <v>114</v>
       </c>
@@ -30798,7 +30800,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A515" s="20" t="s">
         <v>114</v>
       </c>
@@ -30831,7 +30833,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A516" s="20" t="s">
         <v>114</v>
       </c>
@@ -30864,7 +30866,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A517" s="20" t="s">
         <v>114</v>
       </c>
@@ -30897,7 +30899,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A518" s="20" t="s">
         <v>114</v>
       </c>
@@ -30930,7 +30932,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A519" s="20" t="s">
         <v>114</v>
       </c>
@@ -30959,7 +30961,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A520" s="20" t="s">
         <v>114</v>
       </c>
@@ -30988,7 +30990,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A521" s="20" t="s">
         <v>114</v>
       </c>
@@ -31017,7 +31019,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A522" s="20" t="s">
         <v>114</v>
       </c>
@@ -31046,7 +31048,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A523" s="20" t="s">
         <v>114</v>
       </c>
@@ -31075,7 +31077,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A524" s="20" t="s">
         <v>114</v>
       </c>
@@ -31104,7 +31106,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A525" s="20" t="s">
         <v>114</v>
       </c>
@@ -31137,7 +31139,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A526" s="20" t="s">
         <v>114</v>
       </c>
@@ -31170,7 +31172,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A527" s="20" t="s">
         <v>114</v>
       </c>
@@ -31203,7 +31205,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A528" s="20" t="s">
         <v>114</v>
       </c>
@@ -31236,7 +31238,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A529" s="20" t="s">
         <v>114</v>
       </c>
@@ -31265,7 +31267,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A530" s="20" t="s">
         <v>114</v>
       </c>
@@ -31294,7 +31296,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A531" s="20" t="s">
         <v>114</v>
       </c>
@@ -31323,7 +31325,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A532" s="20" t="s">
         <v>114</v>
       </c>
@@ -31352,7 +31354,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A533" s="20" t="s">
         <v>114</v>
       </c>
@@ -31381,7 +31383,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A534" s="20" t="s">
         <v>114</v>
       </c>
@@ -31410,7 +31412,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A535" s="20" t="s">
         <v>114</v>
       </c>
@@ -31439,7 +31441,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A536" s="20" t="s">
         <v>114</v>
       </c>
@@ -31468,7 +31470,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A537" s="20" t="s">
         <v>114</v>
       </c>
@@ -31497,7 +31499,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A538" s="20" t="s">
         <v>114</v>
       </c>
@@ -31530,7 +31532,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A539" s="20" t="s">
         <v>114</v>
       </c>
@@ -31563,7 +31565,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A540" s="20" t="s">
         <v>114</v>
       </c>
@@ -31596,7 +31598,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A541" s="20" t="s">
         <v>114</v>
       </c>
@@ -31629,7 +31631,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A542" s="20" t="s">
         <v>114</v>
       </c>
@@ -31662,7 +31664,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A543" s="20" t="s">
         <v>114</v>
       </c>
@@ -31691,7 +31693,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A544" s="20" t="s">
         <v>114</v>
       </c>
@@ -31720,7 +31722,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A545" s="20" t="s">
         <v>114</v>
       </c>
@@ -31749,7 +31751,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A546" s="20" t="s">
         <v>114</v>
       </c>
@@ -31778,7 +31780,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A547" s="20" t="s">
         <v>114</v>
       </c>
@@ -31807,7 +31809,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A548" s="20" t="s">
         <v>114</v>
       </c>
@@ -31836,7 +31838,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A549" s="20" t="s">
         <v>114</v>
       </c>
@@ -31865,7 +31867,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A550" s="20" t="s">
         <v>114</v>
       </c>
@@ -31894,7 +31896,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A551" s="20" t="s">
         <v>114</v>
       </c>
@@ -31923,7 +31925,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A552" s="20" t="s">
         <v>114</v>
       </c>
@@ -31952,7 +31954,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A553" s="20" t="s">
         <v>114</v>
       </c>
@@ -31981,7 +31983,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A554" s="20" t="s">
         <v>114</v>
       </c>
@@ -32010,7 +32012,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A555" s="20" t="s">
         <v>114</v>
       </c>
@@ -32039,7 +32041,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A556" s="20" t="s">
         <v>114</v>
       </c>
@@ -32068,7 +32070,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A557" s="20" t="s">
         <v>114</v>
       </c>
@@ -32097,7 +32099,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A558" s="20" t="s">
         <v>114</v>
       </c>
@@ -32126,7 +32128,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A559" s="20" t="s">
         <v>114</v>
       </c>
@@ -32155,7 +32157,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A560" s="20" t="s">
         <v>114</v>
       </c>
@@ -32184,7 +32186,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A561" s="20" t="s">
         <v>114</v>
       </c>
@@ -32213,7 +32215,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A562" s="20" t="s">
         <v>114</v>
       </c>
@@ -32242,7 +32244,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A563" s="20" t="s">
         <v>114</v>
       </c>
@@ -32271,7 +32273,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A564" s="20" t="s">
         <v>114</v>
       </c>
@@ -32300,7 +32302,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A565" s="20" t="s">
         <v>114</v>
       </c>
@@ -32329,7 +32331,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A566" s="20" t="s">
         <v>114</v>
       </c>
@@ -32358,7 +32360,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A567" s="20" t="s">
         <v>114</v>
       </c>
@@ -32387,7 +32389,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A568" s="20" t="s">
         <v>114</v>
       </c>
@@ -32416,7 +32418,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A569" s="20" t="s">
         <v>114</v>
       </c>
@@ -32445,7 +32447,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A570" s="20" t="s">
         <v>114</v>
       </c>
@@ -32474,7 +32476,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A571" s="20" t="s">
         <v>114</v>
       </c>
@@ -32503,7 +32505,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A572" s="20" t="s">
         <v>114</v>
       </c>
@@ -32532,7 +32534,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A573" s="20" t="s">
         <v>114</v>
       </c>
@@ -32561,7 +32563,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A574" s="20" t="s">
         <v>114</v>
       </c>
@@ -32590,7 +32592,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A575" s="20" t="s">
         <v>114</v>
       </c>
@@ -32619,7 +32621,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A576" s="20" t="s">
         <v>114</v>
       </c>
@@ -32648,7 +32650,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A577" s="20" t="s">
         <v>114</v>
       </c>
@@ -32677,7 +32679,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A578" s="20" t="s">
         <v>114</v>
       </c>
@@ -32706,7 +32708,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A579" s="20" t="s">
         <v>114</v>
       </c>
@@ -32735,7 +32737,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A580" s="20" t="s">
         <v>114</v>
       </c>
@@ -32764,7 +32766,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A581" s="20" t="s">
         <v>114</v>
       </c>
@@ -32793,7 +32795,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A582" s="20" t="s">
         <v>114</v>
       </c>
@@ -32822,7 +32824,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A583" s="20" t="s">
         <v>114</v>
       </c>
@@ -32851,7 +32853,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A584" s="20" t="s">
         <v>114</v>
       </c>
@@ -32880,7 +32882,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A585" s="20" t="s">
         <v>114</v>
       </c>
@@ -32909,7 +32911,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A586" s="20" t="s">
         <v>114</v>
       </c>
@@ -32938,7 +32940,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A587" s="20" t="s">
         <v>114</v>
       </c>
@@ -32967,7 +32969,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A588" s="20" t="s">
         <v>114</v>
       </c>
@@ -32996,7 +32998,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A589" s="20" t="s">
         <v>114</v>
       </c>
@@ -33025,7 +33027,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A590" s="20" t="s">
         <v>114</v>
       </c>
@@ -33054,7 +33056,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A591" s="20" t="s">
         <v>114</v>
       </c>
@@ -33083,7 +33085,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A592" s="20" t="s">
         <v>114</v>
       </c>
@@ -33112,7 +33114,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A593" s="20" t="s">
         <v>114</v>
       </c>
@@ -33141,7 +33143,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A594" s="20" t="s">
         <v>114</v>
       </c>
@@ -33170,7 +33172,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A595" s="20" t="s">
         <v>114</v>
       </c>
@@ -33199,7 +33201,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A596" s="20" t="s">
         <v>114</v>
       </c>
@@ -33228,7 +33230,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A597" s="20" t="s">
         <v>114</v>
       </c>
@@ -33257,7 +33259,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A598" s="20" t="s">
         <v>114</v>
       </c>
@@ -33286,7 +33288,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A599" s="20" t="s">
         <v>114</v>
       </c>
@@ -33315,7 +33317,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A600" s="20" t="s">
         <v>114</v>
       </c>
@@ -33344,7 +33346,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A601" s="20" t="s">
         <v>114</v>
       </c>
@@ -33373,7 +33375,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A602" s="20" t="s">
         <v>114</v>
       </c>
@@ -33426,32 +33428,32 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D039B65-B517-48F3-ABEF-F6AA7FDFDF8B}">
   <dimension ref="A1:AE60"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="37.28515625" style="20" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="12" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" style="20" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="12.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="8.7109375" style="20"/>
+    <col min="1" max="1" width="37.26953125" style="20" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.453125" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="12" width="13.7265625" style="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.1796875" style="20" customWidth="1"/>
+    <col min="14" max="14" width="13.7265625" style="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="8.7265625" style="20"/>
     <col min="20" max="20" width="12" style="20" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="8.7109375" style="20"/>
-    <col min="24" max="24" width="9.85546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.5703125" style="20" customWidth="1"/>
-    <col min="26" max="26" width="17.7109375" style="20" customWidth="1"/>
-    <col min="27" max="27" width="8.7109375" style="20"/>
+    <col min="21" max="23" width="8.7265625" style="20"/>
+    <col min="24" max="24" width="9.81640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.54296875" style="20" customWidth="1"/>
+    <col min="26" max="26" width="17.7265625" style="20" customWidth="1"/>
+    <col min="27" max="27" width="8.7265625" style="20"/>
     <col min="28" max="28" width="14" style="20" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="8.7109375" style="20"/>
+    <col min="29" max="30" width="8.7265625" style="20"/>
     <col min="31" max="32" width="12" style="20" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.7109375" style="20"/>
-    <col min="34" max="34" width="9.85546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="8.7109375" style="20"/>
+    <col min="33" max="33" width="8.7265625" style="20"/>
+    <col min="34" max="34" width="9.81640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="8.7265625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A1" s="20" t="s">
         <v>107</v>
       </c>
@@ -33459,7 +33461,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A2" s="20" t="s">
         <v>109</v>
       </c>
@@ -33467,7 +33469,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A3" s="20" t="s">
         <v>110</v>
       </c>
@@ -33475,7 +33477,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A5" s="20" t="s">
         <v>136</v>
       </c>
@@ -33483,7 +33485,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A6" s="20" t="s">
         <v>138</v>
       </c>
@@ -33503,7 +33505,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A7" s="21" t="s">
         <v>117</v>
       </c>
@@ -33526,7 +33528,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A8" s="21" t="s">
         <v>124</v>
       </c>
@@ -33549,7 +33551,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A9" s="21" t="s">
         <v>123</v>
       </c>
@@ -33572,7 +33574,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A10" s="21" t="s">
         <v>125</v>
       </c>
@@ -33595,7 +33597,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A11" s="21" t="s">
         <v>126</v>
       </c>
@@ -33615,7 +33617,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" s="21" t="s">
         <v>127</v>
       </c>
@@ -33638,7 +33640,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A13" s="21" t="s">
         <v>128</v>
       </c>
@@ -33661,7 +33663,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A14" s="21" t="s">
         <v>129</v>
       </c>
@@ -33684,7 +33686,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A15" s="21" t="s">
         <v>131</v>
       </c>
@@ -33704,7 +33706,7 @@
         <v>-1020.6999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A16" s="21" t="s">
         <v>139</v>
       </c>
@@ -33724,7 +33726,7 @@
         <v>-2041.4</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A18" s="21" t="s">
         <v>140</v>
       </c>
@@ -33745,12 +33747,12 @@
         <v>-368.4</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A20" s="22" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A21" s="22"/>
       <c r="B21" s="20" t="s">
         <v>141</v>
@@ -33761,7 +33763,7 @@
       </c>
       <c r="Z21" s="23"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.75">
       <c r="B22" s="20">
         <v>2025</v>
       </c>
@@ -33787,7 +33789,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A23" s="20">
         <v>5</v>
       </c>
@@ -33829,7 +33831,7 @@
       <c r="AB23" s="24"/>
       <c r="AC23" s="24"/>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A24" s="20">
         <v>20</v>
       </c>
@@ -33871,7 +33873,7 @@
       <c r="AB24" s="24"/>
       <c r="AC24" s="24"/>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A25" s="20">
         <v>35</v>
       </c>
@@ -33913,7 +33915,7 @@
       <c r="AB25" s="24"/>
       <c r="AC25" s="24"/>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A26" s="20">
         <v>50</v>
       </c>
@@ -33955,7 +33957,7 @@
       <c r="AB26" s="24"/>
       <c r="AC26" s="24"/>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A27" s="20">
         <v>100</v>
       </c>
@@ -33997,12 +33999,12 @@
       <c r="AB27" s="24"/>
       <c r="AC27" s="24"/>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A29" s="22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A30" s="22"/>
       <c r="B30" s="20" t="s">
         <v>141</v>
@@ -34013,7 +34015,7 @@
       </c>
       <c r="Z30" s="23"/>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.75">
       <c r="B31" s="20">
         <v>2025</v>
       </c>
@@ -34039,7 +34041,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A32" s="20">
         <v>5</v>
       </c>
@@ -34081,7 +34083,7 @@
       <c r="AB32" s="24"/>
       <c r="AC32" s="24"/>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A33" s="20">
         <v>20</v>
       </c>
@@ -34123,7 +34125,7 @@
       <c r="AB33" s="24"/>
       <c r="AC33" s="24"/>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A34" s="20">
         <v>35</v>
       </c>
@@ -34165,7 +34167,7 @@
       <c r="AB34" s="24"/>
       <c r="AC34" s="24"/>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A35" s="20">
         <v>50</v>
       </c>
@@ -34207,7 +34209,7 @@
       <c r="AB35" s="25"/>
       <c r="AC35" s="24"/>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A36" s="20">
         <v>100</v>
       </c>
@@ -34249,15 +34251,15 @@
       <c r="AB36" s="24"/>
       <c r="AC36" s="24"/>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A37" s="22"/>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A38" s="22" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A39" s="34" t="s">
         <v>159</v>
       </c>
@@ -34352,7 +34354,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A40" s="20">
         <v>5</v>
       </c>
@@ -34477,7 +34479,7 @@
         <v>24900000000000.09</v>
       </c>
     </row>
-    <row r="41" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A41" s="20">
         <v>20</v>
       </c>
@@ -34602,7 +34604,7 @@
         <v>28299999999999.953</v>
       </c>
     </row>
-    <row r="42" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A42" s="20">
         <v>35</v>
       </c>
@@ -34727,7 +34729,7 @@
         <v>12750000000000</v>
       </c>
     </row>
-    <row r="43" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A43" s="20">
         <v>50</v>
       </c>
@@ -34852,7 +34854,7 @@
         <v>4450000000000.0029</v>
       </c>
     </row>
-    <row r="44" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A44" s="20">
         <v>100</v>
       </c>
@@ -34977,12 +34979,12 @@
         <v>11949999999999.988</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A46" s="22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A47" s="34" t="s">
         <v>159</v>
       </c>
@@ -35077,7 +35079,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="48" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A48" s="20">
         <v>5</v>
       </c>
@@ -35202,7 +35204,7 @@
         <v>1050000000000.0114</v>
       </c>
     </row>
-    <row r="49" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A49" s="20">
         <v>20</v>
       </c>
@@ -35327,7 +35329,7 @@
         <v>50250000000000</v>
       </c>
     </row>
-    <row r="50" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A50" s="20">
         <v>35</v>
       </c>
@@ -35452,7 +35454,7 @@
         <v>60350000000000.023</v>
       </c>
     </row>
-    <row r="51" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A51" s="20">
         <v>50</v>
       </c>
@@ -35577,7 +35579,7 @@
         <v>43500000000000</v>
       </c>
     </row>
-    <row r="52" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A52" s="20">
         <v>100</v>
       </c>
@@ -35702,12 +35704,12 @@
         <v>19899999999999.863</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A54" s="22" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A55" s="34" t="s">
         <v>159</v>
       </c>
@@ -35802,7 +35804,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="56" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A56" s="20">
         <v>5</v>
       </c>
@@ -35927,7 +35929,7 @@
         <v>1050000000000.0114</v>
       </c>
     </row>
-    <row r="57" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A57" s="20">
         <v>20</v>
       </c>
@@ -36052,7 +36054,7 @@
         <v>50250000000000</v>
       </c>
     </row>
-    <row r="58" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A58" s="20">
         <v>35</v>
       </c>
@@ -36177,7 +36179,7 @@
         <v>60350000000000.023</v>
       </c>
     </row>
-    <row r="59" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A59" s="20">
         <v>50</v>
       </c>
@@ -36302,7 +36304,7 @@
         <v>43500000000000</v>
       </c>
     </row>
-    <row r="60" spans="1:31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A60" s="20">
         <v>100</v>
       </c>
@@ -36438,20 +36440,20 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:BM272"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="73.85546875" customWidth="1"/>
+    <col min="1" max="1" width="73.81640625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="36.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" customWidth="1"/>
+    <col min="5" max="6" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A1" s="8" t="s">
         <v>77</v>
       </c>
@@ -36519,17 +36521,17 @@
       <c r="BK1" s="10"/>
       <c r="BL1" s="10"/>
     </row>
-    <row r="2" spans="1:64" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:64" ht="145.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A2" s="11" t="s">
         <v>91</v>
       </c>
       <c r="B2" s="12"/>
     </row>
-    <row r="3" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
     </row>
-    <row r="4" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A4" s="8" t="s">
         <v>78</v>
       </c>
@@ -36597,7 +36599,7 @@
       <c r="BK4" s="10"/>
       <c r="BL4" s="10"/>
     </row>
-    <row r="5" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -36605,12 +36607,12 @@
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -36621,7 +36623,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -36632,7 +36634,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>83</v>
       </c>
@@ -36643,7 +36645,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>84</v>
       </c>
@@ -36654,7 +36656,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -36665,7 +36667,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>86</v>
       </c>
@@ -36676,7 +36678,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>86</v>
       </c>
@@ -36687,7 +36689,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -36698,7 +36700,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -36709,7 +36711,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -36720,7 +36722,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -36731,7 +36733,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -36742,12 +36744,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>85</v>
       </c>
@@ -36756,7 +36758,7 @@
         <v>1299999999.9999998</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>89</v>
       </c>
@@ -36765,12 +36767,12 @@
         <v>1500000000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.75">
       <c r="B42">
         <v>2023</v>
       </c>
@@ -36799,7 +36801,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>156</v>
       </c>
@@ -36831,7 +36833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>157</v>
       </c>
@@ -36863,7 +36865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>158</v>
       </c>
@@ -36895,7 +36897,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>154</v>
       </c>
@@ -36936,7 +36938,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>155</v>
       </c>
@@ -36977,7 +36979,7 @@
         <v>5.1172707889125799E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.75">
       <c r="B48" s="36"/>
       <c r="C48" s="36"/>
       <c r="D48" s="36"/>
@@ -36988,7 +36990,7 @@
       <c r="I48" s="36"/>
       <c r="J48" s="36"/>
     </row>
-    <row r="49" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A49" s="27"/>
       <c r="B49" s="28"/>
       <c r="C49" s="27"/>
@@ -37061,7 +37063,7 @@
       <c r="BL49" s="16"/>
       <c r="BM49" s="16"/>
     </row>
-    <row r="50" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A50" s="27"/>
       <c r="B50" s="12">
         <v>2023</v>
@@ -37153,7 +37155,7 @@
       <c r="BL50" s="16"/>
       <c r="BM50" s="16"/>
     </row>
-    <row r="51" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A51" s="27" t="s">
         <v>160</v>
       </c>
@@ -37260,7 +37262,7 @@
       <c r="BL51" s="16"/>
       <c r="BM51" s="16"/>
     </row>
-    <row r="52" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A52" s="27" t="s">
         <v>161</v>
       </c>
@@ -37367,7 +37369,7 @@
       <c r="BL52" s="16"/>
       <c r="BM52" s="16"/>
     </row>
-    <row r="53" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A53" s="27"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -37433,7 +37435,7 @@
       <c r="BL53" s="16"/>
       <c r="BM53" s="16"/>
     </row>
-    <row r="54" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A54" s="27"/>
       <c r="B54" s="30"/>
       <c r="C54" s="27"/>
@@ -37499,7 +37501,7 @@
       <c r="BL54" s="16"/>
       <c r="BM54" s="16"/>
     </row>
-    <row r="55" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A55" s="31" t="s">
         <v>162</v>
       </c>
@@ -37543,7 +37545,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="56" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A56" s="32">
         <v>5</v>
       </c>
@@ -37600,7 +37602,7 @@
         <v>78500000.000000224</v>
       </c>
     </row>
-    <row r="57" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A57" s="32">
         <v>20</v>
       </c>
@@ -37657,7 +37659,7 @@
         <v>468000000.00000179</v>
       </c>
     </row>
-    <row r="58" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A58" s="32">
         <v>35</v>
       </c>
@@ -37714,7 +37716,7 @@
         <v>364000000.00000316</v>
       </c>
     </row>
-    <row r="59" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A59" s="32">
         <v>50</v>
       </c>
@@ -37771,7 +37773,7 @@
         <v>189999999.99999917</v>
       </c>
     </row>
-    <row r="60" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A60" s="32">
         <v>100</v>
       </c>
@@ -37828,7 +37830,7 @@
         <v>1080000000.0000012</v>
       </c>
     </row>
-    <row r="61" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A61" s="32"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -37841,7 +37843,7 @@
       <c r="J61" s="12"/>
       <c r="L61" s="12"/>
     </row>
-    <row r="62" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A62" s="31" t="s">
         <v>163</v>
       </c>
@@ -37885,7 +37887,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="63" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A63" s="32">
         <v>5</v>
       </c>
@@ -37942,7 +37944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A64" s="32">
         <v>20</v>
       </c>
@@ -37999,7 +38001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A65" s="32">
         <v>35</v>
       </c>
@@ -38056,7 +38058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A66" s="32">
         <v>50</v>
       </c>
@@ -38113,7 +38115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A67" s="32">
         <v>100</v>
       </c>
@@ -38170,7 +38172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A68" s="27"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -38186,7 +38188,7 @@
       <c r="M68" s="12"/>
       <c r="N68" s="12"/>
     </row>
-    <row r="69" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A69" s="31" t="s">
         <v>165</v>
       </c>
@@ -38243,7 +38245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A70" s="31" t="s">
         <v>164</v>
       </c>
@@ -38350,7 +38352,7 @@
       <c r="BK70" s="12"/>
       <c r="BL70" s="12"/>
     </row>
-    <row r="71" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
@@ -38416,7 +38418,7 @@
       <c r="BK71" s="12"/>
       <c r="BL71" s="12"/>
     </row>
-    <row r="72" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A72" s="31" t="s">
         <v>169</v>
       </c>
@@ -38460,7 +38462,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="73" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A73" s="32">
         <v>5</v>
       </c>
@@ -38517,7 +38519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A74" s="32">
         <v>20</v>
       </c>
@@ -38574,7 +38576,7 @@
         <v>437200000.00001162</v>
       </c>
     </row>
-    <row r="75" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A75" s="32">
         <v>35</v>
       </c>
@@ -38631,7 +38633,7 @@
         <v>908600000.00000119</v>
       </c>
     </row>
-    <row r="76" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A76" s="32">
         <v>50</v>
       </c>
@@ -38688,7 +38690,7 @@
         <v>2238000000.0000048</v>
       </c>
     </row>
-    <row r="77" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A77" s="32">
         <v>100</v>
       </c>
@@ -38745,7 +38747,7 @@
         <v>1595999999.9999583</v>
       </c>
     </row>
-    <row r="78" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A78" s="32"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
@@ -38758,7 +38760,7 @@
       <c r="J78" s="12"/>
       <c r="L78" s="12"/>
     </row>
-    <row r="79" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A79" s="31" t="s">
         <v>166</v>
       </c>
@@ -38802,7 +38804,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="80" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A80" s="32">
         <v>5</v>
       </c>
@@ -38859,7 +38861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A81" s="32">
         <v>20</v>
       </c>
@@ -38916,7 +38918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A82" s="32">
         <v>35</v>
       </c>
@@ -38973,7 +38975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A83" s="32">
         <v>50</v>
       </c>
@@ -39030,7 +39032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A84" s="32">
         <v>100</v>
       </c>
@@ -39087,7 +39089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A85" s="27"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
@@ -39103,7 +39105,7 @@
       <c r="M85" s="12"/>
       <c r="N85" s="12"/>
     </row>
-    <row r="86" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A86" s="31" t="s">
         <v>167</v>
       </c>
@@ -39160,7 +39162,7 @@
         <v>10179858186482.16</v>
       </c>
     </row>
-    <row r="87" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A87" s="13"/>
       <c r="B87" s="12">
         <f>B86/10^12</f>
@@ -39265,10 +39267,10 @@
       <c r="BK87" s="12"/>
       <c r="BL87" s="12"/>
     </row>
-    <row r="88" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A88" s="13"/>
     </row>
-    <row r="89" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A89" s="13"/>
       <c r="B89" s="12">
         <v>2021</v>
@@ -39361,7 +39363,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="90" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A90" s="1" t="s">
         <v>170</v>
       </c>
@@ -39487,7 +39489,7 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
     </row>
-    <row r="91" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A91" s="1" t="s">
         <v>171</v>
       </c>
@@ -39613,7 +39615,7 @@
       <c r="AG91" s="18"/>
       <c r="AH91" s="18"/>
     </row>
-    <row r="92" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:64" x14ac:dyDescent="0.75">
       <c r="D92" s="18"/>
       <c r="E92" s="18"/>
       <c r="F92" s="18"/>
@@ -39644,7 +39646,7 @@
       <c r="AE92" s="18"/>
       <c r="AF92" s="18"/>
     </row>
-    <row r="93" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
         <v>172</v>
       </c>
@@ -39678,7 +39680,7 @@
       <c r="AE93" s="18"/>
       <c r="AF93" s="18"/>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A252" s="13" t="s">
         <v>92</v>
       </c>
@@ -39686,15 +39688,15 @@
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A253" s="13"/>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A254" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A255" s="16" t="s">
         <v>80</v>
       </c>
@@ -39706,7 +39708,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A256" s="16" t="s">
         <v>82</v>
       </c>
@@ -39718,7 +39720,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A257" s="16" t="s">
         <v>83</v>
       </c>
@@ -39730,7 +39732,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A258" s="16" t="s">
         <v>84</v>
       </c>
@@ -39742,7 +39744,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A259" s="16" t="s">
         <v>86</v>
       </c>
@@ -39754,7 +39756,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A260" s="16" t="s">
         <v>86</v>
       </c>
@@ -39766,7 +39768,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A261" s="16" t="s">
         <v>86</v>
       </c>
@@ -39778,7 +39780,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A262" s="16" t="s">
         <v>86</v>
       </c>
@@ -39790,7 +39792,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A263" s="16" t="s">
         <v>87</v>
       </c>
@@ -39802,7 +39804,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A264" s="16" t="s">
         <v>86</v>
       </c>
@@ -39814,7 +39816,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A265" s="16" t="s">
         <v>88</v>
       </c>
@@ -39826,7 +39828,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A266" s="16" t="s">
         <v>90</v>
       </c>
@@ -39838,13 +39840,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A268" s="15" t="s">
         <v>144</v>
       </c>
       <c r="B268" s="14"/>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A269" s="16" t="s">
         <v>85</v>
       </c>
@@ -39853,7 +39855,7 @@
         <v>102049999.99999999</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A270" s="16" t="s">
         <v>89</v>
       </c>
@@ -39862,7 +39864,7 @@
         <v>117750000</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A272" s="1" t="s">
         <v>146</v>
       </c>
@@ -39880,13 +39882,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" customWidth="1"/>
+    <col min="2" max="17" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="32" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>102</v>
       </c>
@@ -39984,136 +39987,136 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="39">
         <f>Calcs!B4*10^12</f>
         <v>-972800000000000</v>
       </c>
-      <c r="C2" s="3">
-        <f>Calcs!C4*10^12-'Inflation Reduction Act'!B90</f>
+      <c r="C2" s="39">
+        <f>Calcs!C4*10^12</f>
         <v>-983400000000000</v>
       </c>
-      <c r="D2" s="3">
-        <f>Calcs!D4*10^12-'Inflation Reduction Act'!C90</f>
+      <c r="D2" s="39">
+        <f>Calcs!D4*10^12</f>
         <v>-921800000000000</v>
       </c>
-      <c r="E2" s="3">
-        <f>Calcs!E4*10^12-'Inflation Reduction Act'!D90</f>
+      <c r="E2" s="39">
+        <f>Calcs!E4*10^12</f>
         <v>-956473333333333.38</v>
       </c>
-      <c r="F2" s="3">
-        <f>Calcs!F4*10^12-'Inflation Reduction Act'!E90</f>
+      <c r="F2" s="39">
+        <f>Calcs!F4*10^12</f>
         <v>-956384848484848.5</v>
       </c>
-      <c r="G2" s="3">
-        <f>Calcs!G4*10^12-'Inflation Reduction Act'!F90</f>
+      <c r="G2" s="39">
+        <f>Calcs!G4*10^12</f>
         <v>-956296363636363.63</v>
       </c>
-      <c r="H2" s="3">
-        <f>Calcs!H4*10^12-'Inflation Reduction Act'!G90</f>
-        <v>-963781270634201.13</v>
-      </c>
-      <c r="I2" s="3">
-        <f>Calcs!I4*10^12-'Inflation Reduction Act'!H90</f>
-        <v>-974205885478659.13</v>
-      </c>
-      <c r="J2" s="3">
-        <f>Calcs!J4*10^12-'Inflation Reduction Act'!I90</f>
-        <v>-980543585639673.13</v>
-      </c>
-      <c r="K2" s="3">
-        <f>Calcs!K4*10^12-'Inflation Reduction Act'!J90</f>
-        <v>-981937847460889.38</v>
-      </c>
-      <c r="L2" s="3">
-        <f>Calcs!L4*10^12-'Inflation Reduction Act'!K90</f>
-        <v>-980829453230741.38</v>
-      </c>
-      <c r="M2" s="3">
-        <f>Calcs!M4*10^12-'Inflation Reduction Act'!L90</f>
-        <v>-978196538744729.75</v>
-      </c>
-      <c r="N2" s="3">
-        <f>Calcs!N4*10^12-'Inflation Reduction Act'!M90</f>
-        <v>-975835505921831.25</v>
-      </c>
-      <c r="O2" s="3">
-        <f>Calcs!O4*10^12-'Inflation Reduction Act'!N90</f>
-        <v>-972420795060553.25</v>
-      </c>
-      <c r="P2" s="3">
-        <f>Calcs!P4*10^12-'Inflation Reduction Act'!O90</f>
-        <v>-969006084199275.38</v>
-      </c>
-      <c r="Q2" s="3">
-        <f>Calcs!Q4*10^12-'Inflation Reduction Act'!P90</f>
-        <v>-965591373337997.25</v>
-      </c>
-      <c r="R2" s="3">
-        <f>Calcs!R4*10^12-'Inflation Reduction Act'!Q90</f>
-        <v>-965502888489512.38</v>
-      </c>
-      <c r="S2" s="3">
-        <f>Calcs!S4*10^12-'Inflation Reduction Act'!R90</f>
-        <v>-965414403641027.63</v>
-      </c>
-      <c r="T2" s="3">
-        <f>Calcs!T4*10^12-'Inflation Reduction Act'!S90</f>
-        <v>-965325918792542.75</v>
-      </c>
-      <c r="U2" s="3">
-        <f>Calcs!U4*10^12-'Inflation Reduction Act'!T90</f>
-        <v>-965237433944057.88</v>
-      </c>
-      <c r="V2" s="3">
-        <f>Calcs!V4*10^12-'Inflation Reduction Act'!U90</f>
-        <v>-965148949095573</v>
-      </c>
-      <c r="W2" s="3">
-        <f>Calcs!W4*10^12-'Inflation Reduction Act'!V90</f>
-        <v>-965060464247088.13</v>
-      </c>
-      <c r="X2" s="3">
-        <f>Calcs!X4*10^12-'Inflation Reduction Act'!W90</f>
-        <v>-964971979398603.25</v>
-      </c>
-      <c r="Y2" s="3">
-        <f>Calcs!Y4*10^12-'Inflation Reduction Act'!X90</f>
-        <v>-964883494550118.38</v>
-      </c>
-      <c r="Z2" s="3">
-        <f>Calcs!Z4*10^12-'Inflation Reduction Act'!Y90</f>
-        <v>-964795009701633.5</v>
-      </c>
-      <c r="AA2" s="3">
-        <f>Calcs!AA4*10^12-'Inflation Reduction Act'!Z90</f>
-        <v>-964706524853148.75</v>
-      </c>
-      <c r="AB2" s="3">
-        <f>Calcs!AB4*10^12-'Inflation Reduction Act'!AA90</f>
-        <v>-964618040004663.88</v>
-      </c>
-      <c r="AC2" s="3">
-        <f>Calcs!AC4*10^12-'Inflation Reduction Act'!AB90</f>
-        <v>-964529555156179</v>
-      </c>
-      <c r="AD2" s="3">
-        <f>Calcs!AD4*10^12-'Inflation Reduction Act'!AC90</f>
-        <v>-964441070307694.25</v>
-      </c>
-      <c r="AE2" s="3">
-        <f>Calcs!AE4*10^12-'Inflation Reduction Act'!AD90</f>
-        <v>-964352585459209.38</v>
-      </c>
-      <c r="AF2" s="3">
-        <f>Calcs!AF4*10^12-'Inflation Reduction Act'!AE90</f>
-        <v>-964264100610724.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="H2" s="39">
+        <f>Calcs!H4*10^12</f>
+        <v>-956207878787878.88</v>
+      </c>
+      <c r="I2" s="39">
+        <f>Calcs!I4*10^12</f>
+        <v>-956119393939394</v>
+      </c>
+      <c r="J2" s="39">
+        <f>Calcs!J4*10^12</f>
+        <v>-956030909090909.13</v>
+      </c>
+      <c r="K2" s="39">
+        <f>Calcs!K4*10^12</f>
+        <v>-955942424242424.25</v>
+      </c>
+      <c r="L2" s="39">
+        <f>Calcs!L4*10^12</f>
+        <v>-955853939393939.38</v>
+      </c>
+      <c r="M2" s="39">
+        <f>Calcs!M4*10^12</f>
+        <v>-955765454545454.5</v>
+      </c>
+      <c r="N2" s="39">
+        <f>Calcs!N4*10^12</f>
+        <v>-955676969696969.63</v>
+      </c>
+      <c r="O2" s="39">
+        <f>Calcs!O4*10^12</f>
+        <v>-955588484848484.75</v>
+      </c>
+      <c r="P2" s="39">
+        <f>Calcs!P4*10^12</f>
+        <v>-955500000000000</v>
+      </c>
+      <c r="Q2" s="39">
+        <f>Calcs!Q4*10^12</f>
+        <v>-955411515151515.13</v>
+      </c>
+      <c r="R2" s="39">
+        <f>Calcs!R4*10^12</f>
+        <v>-955323030303030.25</v>
+      </c>
+      <c r="S2" s="39">
+        <f>Calcs!S4*10^12</f>
+        <v>-955234545454545.5</v>
+      </c>
+      <c r="T2" s="39">
+        <f>Calcs!T4*10^12</f>
+        <v>-955146060606060.63</v>
+      </c>
+      <c r="U2" s="39">
+        <f>Calcs!U4*10^12</f>
+        <v>-955057575757575.75</v>
+      </c>
+      <c r="V2" s="39">
+        <f>Calcs!V4*10^12</f>
+        <v>-954969090909090.88</v>
+      </c>
+      <c r="W2" s="39">
+        <f>Calcs!W4*10^12</f>
+        <v>-954880606060606</v>
+      </c>
+      <c r="X2" s="39">
+        <f>Calcs!X4*10^12</f>
+        <v>-954792121212121.13</v>
+      </c>
+      <c r="Y2" s="39">
+        <f>Calcs!Y4*10^12</f>
+        <v>-954703636363636.25</v>
+      </c>
+      <c r="Z2" s="39">
+        <f>Calcs!Z4*10^12</f>
+        <v>-954615151515151.38</v>
+      </c>
+      <c r="AA2" s="39">
+        <f>Calcs!AA4*10^12</f>
+        <v>-954526666666666.63</v>
+      </c>
+      <c r="AB2" s="39">
+        <f>Calcs!AB4*10^12</f>
+        <v>-954438181818181.75</v>
+      </c>
+      <c r="AC2" s="39">
+        <f>Calcs!AC4*10^12</f>
+        <v>-954349696969696.88</v>
+      </c>
+      <c r="AD2" s="39">
+        <f>Calcs!AD4*10^12</f>
+        <v>-954261212121212.13</v>
+      </c>
+      <c r="AE2" s="39">
+        <f>Calcs!AE4*10^12</f>
+        <v>-954172727272727.25</v>
+      </c>
+      <c r="AF2" s="39">
+        <f>Calcs!AF4*10^12</f>
+        <v>-954084242424242.38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -40211,7 +40214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -40309,7 +40312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -40407,7 +40410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -40505,7 +40508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -40603,7 +40606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -40701,7 +40704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -40799,7 +40802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -40897,265 +40900,265 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="39">
         <f>Calcs!B5*10^12/About!$B$17</f>
         <v>2117857142857.1428</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="39">
         <f>Calcs!C5*10^12/About!$B$17</f>
         <v>2217857142857.1431</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="39">
         <f>Calcs!D5*10^12/About!$B$17</f>
         <v>2085714285714.2856</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="39">
         <f>Calcs!E5*10^12/About!$B$17</f>
         <v>2121060606060.6055</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="39">
         <f>Calcs!F5*10^12/About!$B$17</f>
         <v>2136883116883.1184</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="39">
         <f>Calcs!G5*10^12/About!$B$17</f>
         <v>2152705627705.6309</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="39">
         <f>Calcs!H5*10^12/About!$B$17</f>
         <v>2168528138528.1394</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="39">
         <f>Calcs!I5*10^12/About!$B$17</f>
         <v>2184350649350.6523</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="39">
         <f>Calcs!J5*10^12/About!$B$17</f>
         <v>2200173160173.1606</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="39">
         <f>Calcs!K5*10^12/About!$B$17</f>
         <v>2215995670995.6733</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="39">
         <f>Calcs!L5*10^12/About!$B$17</f>
         <v>2231818181818.1821</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="39">
         <f>Calcs!M5*10^12/About!$B$17</f>
         <v>2247640692640.6948</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="39">
         <f>Calcs!N5*10^12/About!$B$17</f>
         <v>2263463203463.2036</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="39">
         <f>Calcs!O5*10^12/About!$B$17</f>
         <v>2279285714285.7158</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="39">
         <f>Calcs!P5*10^12/About!$B$17</f>
         <v>2295108225108.2246</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="39">
         <f>Calcs!Q5*10^12/About!$B$17</f>
         <v>2310930735930.7373</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="39">
         <f>Calcs!R5*10^12/About!$B$17</f>
         <v>2326753246753.25</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11" s="39">
         <f>Calcs!S5*10^12/About!$B$17</f>
         <v>2342575757575.7588</v>
       </c>
-      <c r="T11" s="3">
+      <c r="T11" s="39">
         <f>Calcs!T5*10^12/About!$B$17</f>
         <v>2358398268398.271</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U11" s="39">
         <f>Calcs!U5*10^12/About!$B$17</f>
         <v>2374220779220.7798</v>
       </c>
-      <c r="V11" s="3">
+      <c r="V11" s="39">
         <f>Calcs!V5*10^12/About!$B$17</f>
         <v>2390043290043.2925</v>
       </c>
-      <c r="W11" s="3">
+      <c r="W11" s="39">
         <f>Calcs!W5*10^12/About!$B$17</f>
         <v>2405865800865.8013</v>
       </c>
-      <c r="X11" s="3">
+      <c r="X11" s="39">
         <f>Calcs!X5*10^12/About!$B$17</f>
         <v>2421688311688.314</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="Y11" s="39">
         <f>Calcs!Y5*10^12/About!$B$17</f>
         <v>2437510822510.8228</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="Z11" s="39">
         <f>Calcs!Z5*10^12/About!$B$17</f>
         <v>2453333333333.335</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AA11" s="39">
         <f>Calcs!AA5*10^12/About!$B$17</f>
         <v>2469155844155.8438</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AB11" s="39">
         <f>Calcs!AB5*10^12/About!$B$17</f>
         <v>2484978354978.3564</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AC11" s="39">
         <f>Calcs!AC5*10^12/About!$B$17</f>
         <v>2500800865800.8647</v>
       </c>
-      <c r="AD11" s="3">
+      <c r="AD11" s="39">
         <f>Calcs!AD5*10^12/About!$B$17</f>
         <v>2516623376623.3779</v>
       </c>
-      <c r="AE11" s="3">
+      <c r="AE11" s="39">
         <f>Calcs!AE5*10^12/About!$B$17</f>
         <v>2532445887445.8906</v>
       </c>
-      <c r="AF11" s="3">
+      <c r="AF11" s="39">
         <f>Calcs!AF5*10^12/About!$B$17</f>
         <v>2548268398268.3989</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="39">
         <f>Calcs!B6*10^12/About!$B$18</f>
         <v>34339622641.509434</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="39">
         <f>Calcs!C6*10^12/About!$B$18</f>
         <v>40377358490.56604</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="39">
         <f>Calcs!D6*10^12/About!$B$18</f>
         <v>34339622641.509434</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="39">
         <f>Calcs!E6*10^12/About!$B$18</f>
         <v>34810748999.428329</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="39">
         <f>Calcs!F6*10^12/About!$B$18</f>
         <v>35684391080.617645</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="39">
         <f>Calcs!G6*10^12/About!$B$18</f>
         <v>36558033161.806961</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="39">
         <f>Calcs!H6*10^12/About!$B$18</f>
         <v>37431675242.996277</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="39">
         <f>Calcs!I6*10^12/About!$B$18</f>
         <v>38305317324.185379</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="39">
         <f>Calcs!J6*10^12/About!$B$18</f>
         <v>39178959405.374687</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="39">
         <f>Calcs!K6*10^12/About!$B$18</f>
         <v>40052601486.564003</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="39">
         <f>Calcs!L6*10^12/About!$B$18</f>
         <v>40926243567.753105</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="39">
         <f>Calcs!M6*10^12/About!$B$18</f>
         <v>41799885648.942413</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="39">
         <f>Calcs!N6*10^12/About!$B$18</f>
         <v>42673527730.131729</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="39">
         <f>Calcs!O6*10^12/About!$B$18</f>
         <v>43547169811.320831</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="39">
         <f>Calcs!P6*10^12/About!$B$18</f>
         <v>44420811892.510147</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="39">
         <f>Calcs!Q6*10^12/About!$B$18</f>
         <v>45294453973.699463</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="39">
         <f>Calcs!R6*10^12/About!$B$18</f>
         <v>46168096054.888779</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="39">
         <f>Calcs!S6*10^12/About!$B$18</f>
         <v>47041738136.077873</v>
       </c>
-      <c r="T12" s="3">
+      <c r="T12" s="39">
         <f>Calcs!T6*10^12/About!$B$18</f>
         <v>47915380217.267189</v>
       </c>
-      <c r="U12" s="3">
+      <c r="U12" s="39">
         <f>Calcs!U6*10^12/About!$B$18</f>
         <v>48789022298.456497</v>
       </c>
-      <c r="V12" s="3">
+      <c r="V12" s="39">
         <f>Calcs!V6*10^12/About!$B$18</f>
         <v>49662664379.645607</v>
       </c>
-      <c r="W12" s="3">
+      <c r="W12" s="39">
         <f>Calcs!W6*10^12/About!$B$18</f>
         <v>50536306460.834923</v>
       </c>
-      <c r="X12" s="3">
+      <c r="X12" s="39">
         <f>Calcs!X6*10^12/About!$B$18</f>
         <v>51409948542.024231</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Y12" s="39">
         <f>Calcs!Y6*10^12/About!$B$18</f>
         <v>52283590623.213333</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="Z12" s="39">
         <f>Calcs!Z6*10^12/About!$B$18</f>
         <v>53157232704.402649</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AA12" s="39">
         <f>Calcs!AA6*10^12/About!$B$18</f>
         <v>54030874785.591957</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AB12" s="39">
         <f>Calcs!AB6*10^12/About!$B$18</f>
         <v>54904516866.781281</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AC12" s="39">
         <f>Calcs!AC6*10^12/About!$B$18</f>
         <v>55778158947.970375</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AD12" s="39">
         <f>Calcs!AD6*10^12/About!$B$18</f>
         <v>56651801029.159691</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AE12" s="39">
         <f>Calcs!AE6*10^12/About!$B$18</f>
         <v>57525443110.349007</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AF12" s="39">
         <f>Calcs!AF6*10^12/About!$B$18</f>
         <v>58399085191.538101</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>7</v>
       </c>

--- a/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
+++ b/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\land\BLAPE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us-analysis\InputData\land\BLAPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C994E1-3E4F-43E0-A513-39717EA92B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C77911D-64E4-4705-BF98-CEE780ECF87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37695" yWindow="2850" windowWidth="19185" windowHeight="11265" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="11" r:id="rId14"/>
+    <pivotCache cacheId="3" r:id="rId14"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -828,10 +828,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Currency" xfId="3" builtinId="4"/>
@@ -1258,7 +1258,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1266,6 +1265,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9247,7 +9247,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9616E194-24DA-4C46-8097-71C6F2CA831B}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9616E194-24DA-4C46-8097-71C6F2CA831B}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:F16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -9670,18 +9670,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.1796875" customWidth="1"/>
     <col min="2" max="2" width="51.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -9689,62 +9689,62 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="4">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" s="26" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="4">
         <v>2024</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -9760,27 +9760,27 @@
         <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>145</v>
       </c>
@@ -9797,22 +9797,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AH15"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="63.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B3" s="6">
         <v>2020</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -10036,7 +10036,7 @@
         <v>-954.08424242424235</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>71.351515151515173</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -10294,29 +10294,29 @@
         <v>15.475757575757598</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
       <c r="AG11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="AH11" s="7"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -10557,7 +10557,7 @@
         <v>-921.8</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -10840,18 +10840,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH56"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="255.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="33" width="6.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -10955,7 +10955,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -11059,7 +11059,7 @@
         <v>-771.7</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>-787</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -11267,7 +11267,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -11371,7 +11371,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>-100.3</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -11683,7 +11683,7 @@
         <v>-100.3</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>-31.7</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -11891,7 +11891,7 @@
         <v>-31.7</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -12203,7 +12203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -12307,7 +12307,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -12411,7 +12411,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -12515,7 +12515,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -12723,7 +12723,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -12827,7 +12827,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -12931,7 +12931,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -13035,7 +13035,7 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -13139,7 +13139,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -13555,7 +13555,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -13763,7 +13763,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -13867,7 +13867,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>53</v>
       </c>
@@ -13971,7 +13971,7 @@
         <v>-132.30000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -14075,7 +14075,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>-138.5</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>57</v>
       </c>
@@ -14387,7 +14387,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>58</v>
       </c>
@@ -14491,7 +14491,7 @@
         <v>68.2</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>68.2</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>59</v>
       </c>
@@ -14699,7 +14699,7 @@
         <v>67.599999999999994</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -14803,7 +14803,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -14907,7 +14907,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>60</v>
       </c>
@@ -15011,7 +15011,7 @@
         <v>-921.8</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -15115,67 +15115,67 @@
         <v>-854.2</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -15190,27 +15190,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D41D2ED-A995-4355-B1B7-DFF537DF2BE3}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AE602"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="11.453125" style="20"/>
     <col min="5" max="5" width="18.26953125" style="20" customWidth="1"/>
     <col min="6" max="16384" width="11.453125" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
         <v>104</v>
       </c>
@@ -15242,7 +15242,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>114</v>
       </c>
@@ -15275,7 +15275,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="20" t="s">
         <v>114</v>
       </c>
@@ -15308,7 +15308,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
         <v>114</v>
       </c>
@@ -15341,7 +15341,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
         <v>114</v>
       </c>
@@ -15374,7 +15374,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
         <v>114</v>
       </c>
@@ -15403,7 +15403,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
         <v>114</v>
       </c>
@@ -15432,7 +15432,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="20" t="s">
         <v>114</v>
       </c>
@@ -15461,7 +15461,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
         <v>114</v>
       </c>
@@ -15490,7 +15490,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="20" t="s">
         <v>114</v>
       </c>
@@ -15523,7 +15523,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
         <v>114</v>
       </c>
@@ -15556,7 +15556,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="20" t="s">
         <v>114</v>
       </c>
@@ -15589,7 +15589,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="20" t="s">
         <v>114</v>
       </c>
@@ -15622,7 +15622,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="20" t="s">
         <v>114</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
         <v>114</v>
       </c>
@@ -15688,7 +15688,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20" t="s">
         <v>114</v>
       </c>
@@ -15717,7 +15717,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
         <v>114</v>
       </c>
@@ -15746,7 +15746,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
         <v>114</v>
       </c>
@@ -15775,7 +15775,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
         <v>114</v>
       </c>
@@ -15804,7 +15804,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="20" t="s">
         <v>114</v>
       </c>
@@ -15837,7 +15837,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="20" t="s">
         <v>114</v>
       </c>
@@ -15870,7 +15870,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="20" t="s">
         <v>114</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="20" t="s">
         <v>114</v>
       </c>
@@ -15936,7 +15936,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
         <v>114</v>
       </c>
@@ -15969,7 +15969,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="20" t="s">
         <v>114</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="20" t="s">
         <v>114</v>
       </c>
@@ -16031,7 +16031,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="20" t="s">
         <v>114</v>
       </c>
@@ -16060,7 +16060,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="20" t="s">
         <v>114</v>
       </c>
@@ -16089,7 +16089,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="20" t="s">
         <v>114</v>
       </c>
@@ -16118,7 +16118,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="20" t="s">
         <v>114</v>
       </c>
@@ -16151,7 +16151,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="20" t="s">
         <v>114</v>
       </c>
@@ -16184,7 +16184,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A33" s="20" t="s">
         <v>114</v>
       </c>
@@ -16217,7 +16217,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A34" s="20" t="s">
         <v>114</v>
       </c>
@@ -16250,7 +16250,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A35" s="20" t="s">
         <v>114</v>
       </c>
@@ -16283,7 +16283,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A36" s="20" t="s">
         <v>114</v>
       </c>
@@ -16316,7 +16316,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="37" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="20" t="s">
         <v>114</v>
       </c>
@@ -16345,7 +16345,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="20" t="s">
         <v>114</v>
       </c>
@@ -16374,7 +16374,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="20" t="s">
         <v>114</v>
       </c>
@@ -16403,7 +16403,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="20" t="s">
         <v>114</v>
       </c>
@@ -16432,7 +16432,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A41" s="20" t="s">
         <v>114</v>
       </c>
@@ -16465,7 +16465,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A42" s="20" t="s">
         <v>114</v>
       </c>
@@ -16498,7 +16498,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A43" s="20" t="s">
         <v>114</v>
       </c>
@@ -16528,7 +16528,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A44" s="20" t="s">
         <v>114</v>
       </c>
@@ -16633,7 +16633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A45" s="20" t="s">
         <v>114</v>
       </c>
@@ -16666,7 +16666,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A46" s="20" t="s">
         <v>114</v>
       </c>
@@ -16699,7 +16699,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="47" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="20" t="s">
         <v>114</v>
       </c>
@@ -16725,7 +16725,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="20" t="s">
         <v>114</v>
       </c>
@@ -16754,7 +16754,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="20" t="s">
         <v>114</v>
       </c>
@@ -16783,7 +16783,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="20" t="s">
         <v>114</v>
       </c>
@@ -16812,7 +16812,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="20" t="s">
         <v>114</v>
       </c>
@@ -16842,7 +16842,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="20" t="s">
         <v>114</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="20" t="s">
         <v>114</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="20" t="s">
         <v>114</v>
       </c>
@@ -16941,7 +16941,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="20" t="s">
         <v>114</v>
       </c>
@@ -16974,7 +16974,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="20" t="s">
         <v>114</v>
       </c>
@@ -17007,7 +17007,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="20" t="s">
         <v>114</v>
       </c>
@@ -17036,7 +17036,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="20" t="s">
         <v>114</v>
       </c>
@@ -17065,7 +17065,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="20" t="s">
         <v>114</v>
       </c>
@@ -17094,7 +17094,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="20" t="s">
         <v>114</v>
       </c>
@@ -17123,7 +17123,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="20" t="s">
         <v>114</v>
       </c>
@@ -17156,7 +17156,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="20" t="s">
         <v>114</v>
       </c>
@@ -17189,7 +17189,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="20" t="s">
         <v>114</v>
       </c>
@@ -17222,7 +17222,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="20" t="s">
         <v>114</v>
       </c>
@@ -17255,7 +17255,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="20" t="s">
         <v>114</v>
       </c>
@@ -17288,7 +17288,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="20" t="s">
         <v>114</v>
       </c>
@@ -17321,7 +17321,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="20" t="s">
         <v>114</v>
       </c>
@@ -17350,7 +17350,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="20" t="s">
         <v>114</v>
       </c>
@@ -17379,7 +17379,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="20" t="s">
         <v>114</v>
       </c>
@@ -17408,7 +17408,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="20" t="s">
         <v>114</v>
       </c>
@@ -17437,7 +17437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="20" t="s">
         <v>114</v>
       </c>
@@ -17470,7 +17470,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="20" t="s">
         <v>114</v>
       </c>
@@ -17503,7 +17503,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="20" t="s">
         <v>114</v>
       </c>
@@ -17536,7 +17536,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="20" t="s">
         <v>114</v>
       </c>
@@ -17569,7 +17569,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="20" t="s">
         <v>114</v>
       </c>
@@ -17602,7 +17602,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="20" t="s">
         <v>114</v>
       </c>
@@ -17635,7 +17635,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="20" t="s">
         <v>114</v>
       </c>
@@ -17664,7 +17664,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="20" t="s">
         <v>114</v>
       </c>
@@ -17693,7 +17693,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="20" t="s">
         <v>114</v>
       </c>
@@ -17722,7 +17722,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="20" t="s">
         <v>114</v>
       </c>
@@ -17751,7 +17751,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="20" t="s">
         <v>114</v>
       </c>
@@ -17784,7 +17784,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="20" t="s">
         <v>114</v>
       </c>
@@ -17817,7 +17817,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="20" t="s">
         <v>114</v>
       </c>
@@ -17846,7 +17846,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="20" t="s">
         <v>114</v>
       </c>
@@ -17875,7 +17875,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="20" t="s">
         <v>114</v>
       </c>
@@ -17904,7 +17904,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="20" t="s">
         <v>114</v>
       </c>
@@ -17933,7 +17933,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="20" t="s">
         <v>114</v>
       </c>
@@ -17962,7 +17962,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="20" t="s">
         <v>114</v>
       </c>
@@ -17995,7 +17995,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="20" t="s">
         <v>114</v>
       </c>
@@ -18028,7 +18028,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="20" t="s">
         <v>114</v>
       </c>
@@ -18061,7 +18061,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="20" t="s">
         <v>114</v>
       </c>
@@ -18094,7 +18094,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="20" t="s">
         <v>114</v>
       </c>
@@ -18127,7 +18127,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="20" t="s">
         <v>114</v>
       </c>
@@ -18156,7 +18156,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="20" t="s">
         <v>114</v>
       </c>
@@ -18185,7 +18185,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="20" t="s">
         <v>114</v>
       </c>
@@ -18214,7 +18214,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="20" t="s">
         <v>114</v>
       </c>
@@ -18243,7 +18243,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="20" t="s">
         <v>114</v>
       </c>
@@ -18272,7 +18272,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="20" t="s">
         <v>114</v>
       </c>
@@ -18301,7 +18301,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="20" t="s">
         <v>114</v>
       </c>
@@ -18330,7 +18330,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="20" t="s">
         <v>114</v>
       </c>
@@ -18359,7 +18359,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="20" t="s">
         <v>114</v>
       </c>
@@ -18388,7 +18388,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="20" t="s">
         <v>114</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="20" t="s">
         <v>114</v>
       </c>
@@ -18446,7 +18446,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="20" t="s">
         <v>114</v>
       </c>
@@ -18475,7 +18475,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="20" t="s">
         <v>114</v>
       </c>
@@ -18504,7 +18504,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="20" t="s">
         <v>114</v>
       </c>
@@ -18533,7 +18533,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="20" t="s">
         <v>114</v>
       </c>
@@ -18562,7 +18562,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="20" t="s">
         <v>114</v>
       </c>
@@ -18591,7 +18591,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="20" t="s">
         <v>114</v>
       </c>
@@ -18620,7 +18620,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="20" t="s">
         <v>114</v>
       </c>
@@ -18649,7 +18649,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="20" t="s">
         <v>114</v>
       </c>
@@ -18678,7 +18678,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="20" t="s">
         <v>114</v>
       </c>
@@ -18707,7 +18707,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="20" t="s">
         <v>114</v>
       </c>
@@ -18736,7 +18736,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="20" t="s">
         <v>114</v>
       </c>
@@ -18765,7 +18765,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="20" t="s">
         <v>114</v>
       </c>
@@ -18794,7 +18794,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="20" t="s">
         <v>114</v>
       </c>
@@ -18823,7 +18823,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="20" t="s">
         <v>114</v>
       </c>
@@ -18852,7 +18852,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="20" t="s">
         <v>114</v>
       </c>
@@ -18881,7 +18881,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="20" t="s">
         <v>114</v>
       </c>
@@ -18910,7 +18910,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="20" t="s">
         <v>114</v>
       </c>
@@ -18939,7 +18939,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="20" t="s">
         <v>114</v>
       </c>
@@ -18968,7 +18968,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="20" t="s">
         <v>114</v>
       </c>
@@ -18997,7 +18997,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="20" t="s">
         <v>114</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="20" t="s">
         <v>114</v>
       </c>
@@ -19055,7 +19055,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="20" t="s">
         <v>114</v>
       </c>
@@ -19084,7 +19084,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="20" t="s">
         <v>114</v>
       </c>
@@ -19113,7 +19113,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="20" t="s">
         <v>114</v>
       </c>
@@ -19142,7 +19142,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="20" t="s">
         <v>114</v>
       </c>
@@ -19171,7 +19171,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="20" t="s">
         <v>114</v>
       </c>
@@ -19200,7 +19200,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="20" t="s">
         <v>114</v>
       </c>
@@ -19229,7 +19229,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="20" t="s">
         <v>114</v>
       </c>
@@ -19258,7 +19258,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="20" t="s">
         <v>114</v>
       </c>
@@ -19287,7 +19287,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="20" t="s">
         <v>114</v>
       </c>
@@ -19316,7 +19316,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="20" t="s">
         <v>114</v>
       </c>
@@ -19345,7 +19345,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="20" t="s">
         <v>114</v>
       </c>
@@ -19374,7 +19374,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="20" t="s">
         <v>114</v>
       </c>
@@ -19403,7 +19403,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="20" t="s">
         <v>114</v>
       </c>
@@ -19432,7 +19432,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="20" t="s">
         <v>114</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="20" t="s">
         <v>114</v>
       </c>
@@ -19490,7 +19490,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="20" t="s">
         <v>114</v>
       </c>
@@ -19519,7 +19519,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="20" t="s">
         <v>114</v>
       </c>
@@ -19548,7 +19548,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="20" t="s">
         <v>114</v>
       </c>
@@ -19577,7 +19577,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="20" t="s">
         <v>114</v>
       </c>
@@ -19606,7 +19606,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="20" t="s">
         <v>114</v>
       </c>
@@ -19635,7 +19635,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="20" t="s">
         <v>114</v>
       </c>
@@ -19664,7 +19664,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="20" t="s">
         <v>114</v>
       </c>
@@ -19693,7 +19693,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="20" t="s">
         <v>114</v>
       </c>
@@ -19722,7 +19722,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="20" t="s">
         <v>114</v>
       </c>
@@ -19751,7 +19751,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="20" t="s">
         <v>114</v>
       </c>
@@ -19780,7 +19780,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="20" t="s">
         <v>114</v>
       </c>
@@ -19809,7 +19809,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="20" t="s">
         <v>114</v>
       </c>
@@ -19838,7 +19838,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="20" t="s">
         <v>114</v>
       </c>
@@ -19867,7 +19867,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="20" t="s">
         <v>114</v>
       </c>
@@ -19900,7 +19900,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="20" t="s">
         <v>114</v>
       </c>
@@ -19933,7 +19933,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="20" t="s">
         <v>114</v>
       </c>
@@ -19962,7 +19962,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="20" t="s">
         <v>114</v>
       </c>
@@ -19991,7 +19991,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="20" t="s">
         <v>114</v>
       </c>
@@ -20020,7 +20020,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="20" t="s">
         <v>114</v>
       </c>
@@ -20049,7 +20049,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="20" t="s">
         <v>114</v>
       </c>
@@ -20082,7 +20082,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="20" t="s">
         <v>114</v>
       </c>
@@ -20115,7 +20115,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" s="20" t="s">
         <v>114</v>
       </c>
@@ -20148,7 +20148,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" s="20" t="s">
         <v>114</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" s="20" t="s">
         <v>114</v>
       </c>
@@ -20214,7 +20214,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="20" t="s">
         <v>114</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="20" t="s">
         <v>114</v>
       </c>
@@ -20276,7 +20276,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="20" t="s">
         <v>114</v>
       </c>
@@ -20305,7 +20305,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="20" t="s">
         <v>114</v>
       </c>
@@ -20334,7 +20334,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="20" t="s">
         <v>114</v>
       </c>
@@ -20363,7 +20363,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" s="20" t="s">
         <v>114</v>
       </c>
@@ -20396,7 +20396,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" s="20" t="s">
         <v>114</v>
       </c>
@@ -20429,7 +20429,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" s="20" t="s">
         <v>114</v>
       </c>
@@ -20462,7 +20462,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" s="20" t="s">
         <v>114</v>
       </c>
@@ -20495,7 +20495,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" s="20" t="s">
         <v>114</v>
       </c>
@@ -20528,7 +20528,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" s="20" t="s">
         <v>114</v>
       </c>
@@ -20561,7 +20561,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="20" t="s">
         <v>114</v>
       </c>
@@ -20590,7 +20590,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="20" t="s">
         <v>114</v>
       </c>
@@ -20619,7 +20619,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="20" t="s">
         <v>114</v>
       </c>
@@ -20648,7 +20648,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="20" t="s">
         <v>114</v>
       </c>
@@ -20677,7 +20677,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="20" t="s">
         <v>114</v>
       </c>
@@ -20710,7 +20710,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="20" t="s">
         <v>114</v>
       </c>
@@ -20743,7 +20743,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="20" t="s">
         <v>114</v>
       </c>
@@ -20776,7 +20776,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" s="20" t="s">
         <v>114</v>
       </c>
@@ -20809,7 +20809,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" s="20" t="s">
         <v>114</v>
       </c>
@@ -20842,7 +20842,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" s="20" t="s">
         <v>114</v>
       </c>
@@ -20875,7 +20875,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="20" t="s">
         <v>114</v>
       </c>
@@ -20904,7 +20904,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="20" t="s">
         <v>114</v>
       </c>
@@ -20933,7 +20933,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="20" t="s">
         <v>114</v>
       </c>
@@ -20962,7 +20962,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="20" t="s">
         <v>114</v>
       </c>
@@ -20991,7 +20991,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189" s="20" t="s">
         <v>114</v>
       </c>
@@ -21024,7 +21024,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="20" t="s">
         <v>114</v>
       </c>
@@ -21057,7 +21057,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191" s="20" t="s">
         <v>114</v>
       </c>
@@ -21090,7 +21090,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A192" s="20" t="s">
         <v>114</v>
       </c>
@@ -21123,7 +21123,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" s="20" t="s">
         <v>114</v>
       </c>
@@ -21156,7 +21156,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" s="20" t="s">
         <v>114</v>
       </c>
@@ -21189,7 +21189,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="20" t="s">
         <v>114</v>
       </c>
@@ -21215,7 +21215,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="20" t="s">
         <v>114</v>
       </c>
@@ -21244,7 +21244,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="20" t="s">
         <v>114</v>
       </c>
@@ -21273,7 +21273,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="20" t="s">
         <v>114</v>
       </c>
@@ -21302,7 +21302,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" s="20" t="s">
         <v>114</v>
       </c>
@@ -21332,7 +21332,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" s="20" t="s">
         <v>114</v>
       </c>
@@ -21365,7 +21365,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" s="20" t="s">
         <v>114</v>
       </c>
@@ -21398,7 +21398,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" s="20" t="s">
         <v>114</v>
       </c>
@@ -21431,7 +21431,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" s="20" t="s">
         <v>114</v>
       </c>
@@ -21464,7 +21464,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" s="20" t="s">
         <v>114</v>
       </c>
@@ -21497,7 +21497,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="20" t="s">
         <v>114</v>
       </c>
@@ -21526,7 +21526,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="20" t="s">
         <v>114</v>
       </c>
@@ -21555,7 +21555,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="20" t="s">
         <v>114</v>
       </c>
@@ -21584,7 +21584,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="20" t="s">
         <v>114</v>
       </c>
@@ -21613,7 +21613,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" s="20" t="s">
         <v>114</v>
       </c>
@@ -21646,7 +21646,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" s="20" t="s">
         <v>114</v>
       </c>
@@ -21679,7 +21679,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" s="20" t="s">
         <v>114</v>
       </c>
@@ -21712,7 +21712,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" s="20" t="s">
         <v>114</v>
       </c>
@@ -21745,7 +21745,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" s="20" t="s">
         <v>114</v>
       </c>
@@ -21778,7 +21778,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" s="20" t="s">
         <v>114</v>
       </c>
@@ -21811,7 +21811,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="20" t="s">
         <v>114</v>
       </c>
@@ -21840,7 +21840,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="20" t="s">
         <v>114</v>
       </c>
@@ -21869,7 +21869,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="20" t="s">
         <v>114</v>
       </c>
@@ -21898,7 +21898,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="20" t="s">
         <v>114</v>
       </c>
@@ -21927,7 +21927,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A219" s="20" t="s">
         <v>114</v>
       </c>
@@ -21960,7 +21960,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A220" s="20" t="s">
         <v>114</v>
       </c>
@@ -21993,7 +21993,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A221" s="20" t="s">
         <v>114</v>
       </c>
@@ -22026,7 +22026,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A222" s="20" t="s">
         <v>114</v>
       </c>
@@ -22059,7 +22059,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A223" s="20" t="s">
         <v>114</v>
       </c>
@@ -22092,7 +22092,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A224" s="20" t="s">
         <v>114</v>
       </c>
@@ -22125,7 +22125,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="20" t="s">
         <v>114</v>
       </c>
@@ -22154,7 +22154,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="20" t="s">
         <v>114</v>
       </c>
@@ -22183,7 +22183,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="20" t="s">
         <v>114</v>
       </c>
@@ -22212,7 +22212,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="20" t="s">
         <v>114</v>
       </c>
@@ -22241,7 +22241,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A229" s="20" t="s">
         <v>114</v>
       </c>
@@ -22274,7 +22274,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A230" s="20" t="s">
         <v>114</v>
       </c>
@@ -22307,7 +22307,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A231" s="20" t="s">
         <v>114</v>
       </c>
@@ -22340,7 +22340,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A232" s="20" t="s">
         <v>114</v>
       </c>
@@ -22373,7 +22373,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="20" t="s">
         <v>114</v>
       </c>
@@ -22402,7 +22402,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="20" t="s">
         <v>114</v>
       </c>
@@ -22431,7 +22431,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="20" t="s">
         <v>114</v>
       </c>
@@ -22460,7 +22460,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="20" t="s">
         <v>114</v>
       </c>
@@ -22489,7 +22489,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="20" t="s">
         <v>114</v>
       </c>
@@ -22518,7 +22518,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A238" s="20" t="s">
         <v>114</v>
       </c>
@@ -22551,7 +22551,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A239" s="20" t="s">
         <v>114</v>
       </c>
@@ -22584,7 +22584,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A240" s="20" t="s">
         <v>114</v>
       </c>
@@ -22617,7 +22617,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A241" s="20" t="s">
         <v>114</v>
       </c>
@@ -22650,7 +22650,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A242" s="20" t="s">
         <v>114</v>
       </c>
@@ -22683,7 +22683,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="20" t="s">
         <v>114</v>
       </c>
@@ -22712,7 +22712,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="20" t="s">
         <v>114</v>
       </c>
@@ -22741,7 +22741,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="20" t="s">
         <v>114</v>
       </c>
@@ -22770,7 +22770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="20" t="s">
         <v>114</v>
       </c>
@@ -22799,7 +22799,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="20" t="s">
         <v>114</v>
       </c>
@@ -22828,7 +22828,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="20" t="s">
         <v>114</v>
       </c>
@@ -22857,7 +22857,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="20" t="s">
         <v>114</v>
       </c>
@@ -22886,7 +22886,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="20" t="s">
         <v>114</v>
       </c>
@@ -22915,7 +22915,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="20" t="s">
         <v>114</v>
       </c>
@@ -22944,7 +22944,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="20" t="s">
         <v>114</v>
       </c>
@@ -22973,7 +22973,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="20" t="s">
         <v>114</v>
       </c>
@@ -23002,7 +23002,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="20" t="s">
         <v>114</v>
       </c>
@@ -23031,7 +23031,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="20" t="s">
         <v>114</v>
       </c>
@@ -23060,7 +23060,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="20" t="s">
         <v>114</v>
       </c>
@@ -23089,7 +23089,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="20" t="s">
         <v>114</v>
       </c>
@@ -23118,7 +23118,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="20" t="s">
         <v>114</v>
       </c>
@@ -23147,7 +23147,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="20" t="s">
         <v>114</v>
       </c>
@@ -23176,7 +23176,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="20" t="s">
         <v>114</v>
       </c>
@@ -23205,7 +23205,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="20" t="s">
         <v>114</v>
       </c>
@@ -23234,7 +23234,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="20" t="s">
         <v>114</v>
       </c>
@@ -23263,7 +23263,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="20" t="s">
         <v>114</v>
       </c>
@@ -23292,7 +23292,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="20" t="s">
         <v>114</v>
       </c>
@@ -23321,7 +23321,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="20" t="s">
         <v>114</v>
       </c>
@@ -23350,7 +23350,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="20" t="s">
         <v>114</v>
       </c>
@@ -23379,7 +23379,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="20" t="s">
         <v>114</v>
       </c>
@@ -23408,7 +23408,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="20" t="s">
         <v>114</v>
       </c>
@@ -23437,7 +23437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="20" t="s">
         <v>114</v>
       </c>
@@ -23466,7 +23466,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="20" t="s">
         <v>114</v>
       </c>
@@ -23495,7 +23495,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="20" t="s">
         <v>114</v>
       </c>
@@ -23524,7 +23524,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="20" t="s">
         <v>114</v>
       </c>
@@ -23553,7 +23553,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="20" t="s">
         <v>114</v>
       </c>
@@ -23582,7 +23582,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="20" t="s">
         <v>114</v>
       </c>
@@ -23611,7 +23611,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="20" t="s">
         <v>114</v>
       </c>
@@ -23640,7 +23640,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="20" t="s">
         <v>114</v>
       </c>
@@ -23669,7 +23669,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="20" t="s">
         <v>114</v>
       </c>
@@ -23698,7 +23698,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="20" t="s">
         <v>114</v>
       </c>
@@ -23727,7 +23727,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="20" t="s">
         <v>114</v>
       </c>
@@ -23756,7 +23756,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="20" t="s">
         <v>114</v>
       </c>
@@ -23785,7 +23785,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="20" t="s">
         <v>114</v>
       </c>
@@ -23814,7 +23814,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="20" t="s">
         <v>114</v>
       </c>
@@ -23843,7 +23843,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="20" t="s">
         <v>114</v>
       </c>
@@ -23872,7 +23872,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="20" t="s">
         <v>114</v>
       </c>
@@ -23901,7 +23901,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="20" t="s">
         <v>114</v>
       </c>
@@ -23930,7 +23930,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="20" t="s">
         <v>114</v>
       </c>
@@ -23959,7 +23959,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="20" t="s">
         <v>114</v>
       </c>
@@ -23988,7 +23988,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="20" t="s">
         <v>114</v>
       </c>
@@ -24017,7 +24017,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="20" t="s">
         <v>114</v>
       </c>
@@ -24046,7 +24046,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="20" t="s">
         <v>114</v>
       </c>
@@ -24075,7 +24075,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="20" t="s">
         <v>114</v>
       </c>
@@ -24104,7 +24104,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="20" t="s">
         <v>114</v>
       </c>
@@ -24133,7 +24133,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="20" t="s">
         <v>114</v>
       </c>
@@ -24162,7 +24162,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="20" t="s">
         <v>114</v>
       </c>
@@ -24191,7 +24191,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="20" t="s">
         <v>114</v>
       </c>
@@ -24220,7 +24220,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="20" t="s">
         <v>114</v>
       </c>
@@ -24249,7 +24249,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="20" t="s">
         <v>114</v>
       </c>
@@ -24278,7 +24278,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="20" t="s">
         <v>114</v>
       </c>
@@ -24307,7 +24307,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="20" t="s">
         <v>114</v>
       </c>
@@ -24336,7 +24336,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="20" t="s">
         <v>114</v>
       </c>
@@ -24365,7 +24365,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="20" t="s">
         <v>114</v>
       </c>
@@ -24394,7 +24394,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="20" t="s">
         <v>114</v>
       </c>
@@ -24423,7 +24423,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="20" t="s">
         <v>114</v>
       </c>
@@ -24452,7 +24452,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="20" t="s">
         <v>114</v>
       </c>
@@ -24481,7 +24481,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="20" t="s">
         <v>114</v>
       </c>
@@ -24510,7 +24510,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="20" t="s">
         <v>114</v>
       </c>
@@ -24539,7 +24539,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A307" s="20" t="s">
         <v>114</v>
       </c>
@@ -24572,7 +24572,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A308" s="20" t="s">
         <v>114</v>
       </c>
@@ -24605,7 +24605,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A309" s="20" t="s">
         <v>114</v>
       </c>
@@ -24638,7 +24638,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A310" s="20" t="s">
         <v>114</v>
       </c>
@@ -24671,7 +24671,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="20" t="s">
         <v>114</v>
       </c>
@@ -24700,7 +24700,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="20" t="s">
         <v>114</v>
       </c>
@@ -24729,7 +24729,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="20" t="s">
         <v>114</v>
       </c>
@@ -24758,7 +24758,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="20" t="s">
         <v>114</v>
       </c>
@@ -24787,7 +24787,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="20" t="s">
         <v>114</v>
       </c>
@@ -24816,7 +24816,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="20" t="s">
         <v>114</v>
       </c>
@@ -24845,7 +24845,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A317" s="20" t="s">
         <v>114</v>
       </c>
@@ -24878,7 +24878,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A318" s="20" t="s">
         <v>114</v>
       </c>
@@ -24911,7 +24911,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A319" s="20" t="s">
         <v>114</v>
       </c>
@@ -24944,7 +24944,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A320" s="20" t="s">
         <v>114</v>
       </c>
@@ -24977,7 +24977,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="20" t="s">
         <v>114</v>
       </c>
@@ -25006,7 +25006,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="20" t="s">
         <v>114</v>
       </c>
@@ -25035,7 +25035,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="20" t="s">
         <v>114</v>
       </c>
@@ -25064,7 +25064,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="20" t="s">
         <v>114</v>
       </c>
@@ -25093,7 +25093,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="20" t="s">
         <v>114</v>
       </c>
@@ -25122,7 +25122,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="20" t="s">
         <v>114</v>
       </c>
@@ -25151,7 +25151,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A327" s="20" t="s">
         <v>114</v>
       </c>
@@ -25184,7 +25184,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A328" s="20" t="s">
         <v>114</v>
       </c>
@@ -25217,7 +25217,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A329" s="20" t="s">
         <v>114</v>
       </c>
@@ -25250,7 +25250,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A330" s="20" t="s">
         <v>114</v>
       </c>
@@ -25283,7 +25283,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="20" t="s">
         <v>114</v>
       </c>
@@ -25312,7 +25312,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="20" t="s">
         <v>114</v>
       </c>
@@ -25341,7 +25341,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="20" t="s">
         <v>114</v>
       </c>
@@ -25370,7 +25370,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="20" t="s">
         <v>114</v>
       </c>
@@ -25399,7 +25399,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="20" t="s">
         <v>114</v>
       </c>
@@ -25428,7 +25428,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="20" t="s">
         <v>114</v>
       </c>
@@ -25457,7 +25457,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A337" s="20" t="s">
         <v>114</v>
       </c>
@@ -25490,7 +25490,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A338" s="20" t="s">
         <v>114</v>
       </c>
@@ -25523,7 +25523,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A339" s="20" t="s">
         <v>114</v>
       </c>
@@ -25556,7 +25556,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A340" s="20" t="s">
         <v>114</v>
       </c>
@@ -25589,7 +25589,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="20" t="s">
         <v>114</v>
       </c>
@@ -25618,7 +25618,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="20" t="s">
         <v>114</v>
       </c>
@@ -25647,7 +25647,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="20" t="s">
         <v>114</v>
       </c>
@@ -25673,7 +25673,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="20" t="s">
         <v>114</v>
       </c>
@@ -25702,7 +25702,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="20" t="s">
         <v>114</v>
       </c>
@@ -25731,7 +25731,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="20" t="s">
         <v>114</v>
       </c>
@@ -25760,7 +25760,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A347" s="20" t="s">
         <v>114</v>
       </c>
@@ -25790,7 +25790,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A348" s="20" t="s">
         <v>114</v>
       </c>
@@ -25823,7 +25823,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A349" s="20" t="s">
         <v>114</v>
       </c>
@@ -25856,7 +25856,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A350" s="20" t="s">
         <v>114</v>
       </c>
@@ -25889,7 +25889,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="20" t="s">
         <v>114</v>
       </c>
@@ -25915,7 +25915,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="20" t="s">
         <v>114</v>
       </c>
@@ -25944,7 +25944,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="20" t="s">
         <v>114</v>
       </c>
@@ -25973,7 +25973,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="20" t="s">
         <v>114</v>
       </c>
@@ -26002,7 +26002,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="20" t="s">
         <v>114</v>
       </c>
@@ -26031,7 +26031,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="20" t="s">
         <v>114</v>
       </c>
@@ -26060,7 +26060,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A357" s="20" t="s">
         <v>114</v>
       </c>
@@ -26093,7 +26093,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A358" s="20" t="s">
         <v>114</v>
       </c>
@@ -26126,7 +26126,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A359" s="20" t="s">
         <v>114</v>
       </c>
@@ -26159,7 +26159,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A360" s="20" t="s">
         <v>114</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="20" t="s">
         <v>114</v>
       </c>
@@ -26221,7 +26221,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="20" t="s">
         <v>114</v>
       </c>
@@ -26250,7 +26250,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="20" t="s">
         <v>114</v>
       </c>
@@ -26279,7 +26279,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="20" t="s">
         <v>114</v>
       </c>
@@ -26308,7 +26308,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="20" t="s">
         <v>114</v>
       </c>
@@ -26337,7 +26337,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="20" t="s">
         <v>114</v>
       </c>
@@ -26366,7 +26366,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A367" s="20" t="s">
         <v>114</v>
       </c>
@@ -26399,7 +26399,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A368" s="20" t="s">
         <v>114</v>
       </c>
@@ -26432,7 +26432,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A369" s="20" t="s">
         <v>114</v>
       </c>
@@ -26465,7 +26465,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A370" s="20" t="s">
         <v>114</v>
       </c>
@@ -26498,7 +26498,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="20" t="s">
         <v>114</v>
       </c>
@@ -26527,7 +26527,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="20" t="s">
         <v>114</v>
       </c>
@@ -26556,7 +26556,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="20" t="s">
         <v>114</v>
       </c>
@@ -26585,7 +26585,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="20" t="s">
         <v>114</v>
       </c>
@@ -26614,7 +26614,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="20" t="s">
         <v>114</v>
       </c>
@@ -26643,7 +26643,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="20" t="s">
         <v>114</v>
       </c>
@@ -26672,7 +26672,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A377" s="20" t="s">
         <v>114</v>
       </c>
@@ -26705,7 +26705,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A378" s="20" t="s">
         <v>114</v>
       </c>
@@ -26738,7 +26738,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A379" s="20" t="s">
         <v>114</v>
       </c>
@@ -26771,7 +26771,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A380" s="20" t="s">
         <v>114</v>
       </c>
@@ -26804,7 +26804,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="20" t="s">
         <v>114</v>
       </c>
@@ -26833,7 +26833,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="20" t="s">
         <v>114</v>
       </c>
@@ -26862,7 +26862,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="20" t="s">
         <v>114</v>
       </c>
@@ -26891,7 +26891,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="20" t="s">
         <v>114</v>
       </c>
@@ -26920,7 +26920,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="20" t="s">
         <v>114</v>
       </c>
@@ -26949,7 +26949,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="20" t="s">
         <v>114</v>
       </c>
@@ -26978,7 +26978,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="20" t="s">
         <v>114</v>
       </c>
@@ -27007,7 +27007,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A388" s="20" t="s">
         <v>114</v>
       </c>
@@ -27040,7 +27040,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A389" s="20" t="s">
         <v>114</v>
       </c>
@@ -27073,7 +27073,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A390" s="20" t="s">
         <v>114</v>
       </c>
@@ -27106,7 +27106,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A391" s="20" t="s">
         <v>114</v>
       </c>
@@ -27139,7 +27139,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A392" s="20" t="s">
         <v>114</v>
       </c>
@@ -27172,7 +27172,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="20" t="s">
         <v>114</v>
       </c>
@@ -27201,7 +27201,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" s="20" t="s">
         <v>114</v>
       </c>
@@ -27230,7 +27230,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="20" t="s">
         <v>114</v>
       </c>
@@ -27259,7 +27259,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="20" t="s">
         <v>114</v>
       </c>
@@ -27288,7 +27288,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="20" t="s">
         <v>114</v>
       </c>
@@ -27317,7 +27317,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="20" t="s">
         <v>114</v>
       </c>
@@ -27346,7 +27346,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="20" t="s">
         <v>114</v>
       </c>
@@ -27375,7 +27375,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="20" t="s">
         <v>114</v>
       </c>
@@ -27404,7 +27404,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="20" t="s">
         <v>114</v>
       </c>
@@ -27433,7 +27433,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="20" t="s">
         <v>114</v>
       </c>
@@ -27462,7 +27462,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" s="20" t="s">
         <v>114</v>
       </c>
@@ -27491,7 +27491,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="20" t="s">
         <v>114</v>
       </c>
@@ -27520,7 +27520,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" s="20" t="s">
         <v>114</v>
       </c>
@@ -27549,7 +27549,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" s="20" t="s">
         <v>114</v>
       </c>
@@ -27578,7 +27578,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="20" t="s">
         <v>114</v>
       </c>
@@ -27607,7 +27607,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" s="20" t="s">
         <v>114</v>
       </c>
@@ -27636,7 +27636,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="20" t="s">
         <v>114</v>
       </c>
@@ -27665,7 +27665,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="20" t="s">
         <v>114</v>
       </c>
@@ -27694,7 +27694,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="20" t="s">
         <v>114</v>
       </c>
@@ -27723,7 +27723,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="20" t="s">
         <v>114</v>
       </c>
@@ -27752,7 +27752,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="20" t="s">
         <v>114</v>
       </c>
@@ -27781,7 +27781,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="20" t="s">
         <v>114</v>
       </c>
@@ -27810,7 +27810,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="20" t="s">
         <v>114</v>
       </c>
@@ -27839,7 +27839,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="20" t="s">
         <v>114</v>
       </c>
@@ -27868,7 +27868,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="20" t="s">
         <v>114</v>
       </c>
@@ -27897,7 +27897,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="20" t="s">
         <v>114</v>
       </c>
@@ -27926,7 +27926,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" s="20" t="s">
         <v>114</v>
       </c>
@@ -27955,7 +27955,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" s="20" t="s">
         <v>114</v>
       </c>
@@ -27984,7 +27984,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" s="20" t="s">
         <v>114</v>
       </c>
@@ -28013,7 +28013,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" s="20" t="s">
         <v>114</v>
       </c>
@@ -28042,7 +28042,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" s="20" t="s">
         <v>114</v>
       </c>
@@ -28071,7 +28071,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" s="20" t="s">
         <v>114</v>
       </c>
@@ -28100,7 +28100,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" s="20" t="s">
         <v>114</v>
       </c>
@@ -28129,7 +28129,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" s="20" t="s">
         <v>114</v>
       </c>
@@ -28158,7 +28158,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" s="20" t="s">
         <v>114</v>
       </c>
@@ -28187,7 +28187,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" s="20" t="s">
         <v>114</v>
       </c>
@@ -28216,7 +28216,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" s="20" t="s">
         <v>114</v>
       </c>
@@ -28245,7 +28245,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" s="20" t="s">
         <v>114</v>
       </c>
@@ -28274,7 +28274,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" s="20" t="s">
         <v>114</v>
       </c>
@@ -28303,7 +28303,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" s="20" t="s">
         <v>114</v>
       </c>
@@ -28332,7 +28332,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" s="20" t="s">
         <v>114</v>
       </c>
@@ -28361,7 +28361,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" s="20" t="s">
         <v>114</v>
       </c>
@@ -28390,7 +28390,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" s="20" t="s">
         <v>114</v>
       </c>
@@ -28419,7 +28419,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" s="20" t="s">
         <v>114</v>
       </c>
@@ -28448,7 +28448,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" s="20" t="s">
         <v>114</v>
       </c>
@@ -28477,7 +28477,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" s="20" t="s">
         <v>114</v>
       </c>
@@ -28506,7 +28506,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" s="20" t="s">
         <v>114</v>
       </c>
@@ -28535,7 +28535,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" s="20" t="s">
         <v>114</v>
       </c>
@@ -28564,7 +28564,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" s="20" t="s">
         <v>114</v>
       </c>
@@ -28593,7 +28593,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" s="20" t="s">
         <v>114</v>
       </c>
@@ -28622,7 +28622,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" s="20" t="s">
         <v>114</v>
       </c>
@@ -28651,7 +28651,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" s="20" t="s">
         <v>114</v>
       </c>
@@ -28680,7 +28680,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" s="20" t="s">
         <v>114</v>
       </c>
@@ -28709,7 +28709,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" s="20" t="s">
         <v>114</v>
       </c>
@@ -28738,7 +28738,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" s="20" t="s">
         <v>114</v>
       </c>
@@ -28767,7 +28767,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" s="20" t="s">
         <v>114</v>
       </c>
@@ -28796,7 +28796,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" s="20" t="s">
         <v>114</v>
       </c>
@@ -28825,7 +28825,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" s="20" t="s">
         <v>114</v>
       </c>
@@ -28854,7 +28854,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" s="20" t="s">
         <v>114</v>
       </c>
@@ -28883,7 +28883,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" s="20" t="s">
         <v>114</v>
       </c>
@@ -28912,7 +28912,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" s="20" t="s">
         <v>114</v>
       </c>
@@ -28941,7 +28941,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" s="20" t="s">
         <v>114</v>
       </c>
@@ -28970,7 +28970,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A455" s="20" t="s">
         <v>114</v>
       </c>
@@ -29003,7 +29003,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A456" s="20" t="s">
         <v>114</v>
       </c>
@@ -29036,7 +29036,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A457" s="20" t="s">
         <v>114</v>
       </c>
@@ -29069,7 +29069,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A458" s="20" t="s">
         <v>114</v>
       </c>
@@ -29102,7 +29102,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" s="20" t="s">
         <v>114</v>
       </c>
@@ -29131,7 +29131,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" s="20" t="s">
         <v>114</v>
       </c>
@@ -29160,7 +29160,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" s="20" t="s">
         <v>114</v>
       </c>
@@ -29189,7 +29189,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" s="20" t="s">
         <v>114</v>
       </c>
@@ -29218,7 +29218,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" s="20" t="s">
         <v>114</v>
       </c>
@@ -29247,7 +29247,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" s="20" t="s">
         <v>114</v>
       </c>
@@ -29276,7 +29276,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A465" s="20" t="s">
         <v>114</v>
       </c>
@@ -29309,7 +29309,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A466" s="20" t="s">
         <v>114</v>
       </c>
@@ -29342,7 +29342,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A467" s="20" t="s">
         <v>114</v>
       </c>
@@ -29375,7 +29375,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A468" s="20" t="s">
         <v>114</v>
       </c>
@@ -29408,7 +29408,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" s="20" t="s">
         <v>114</v>
       </c>
@@ -29437,7 +29437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" s="20" t="s">
         <v>114</v>
       </c>
@@ -29466,7 +29466,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" s="20" t="s">
         <v>114</v>
       </c>
@@ -29495,7 +29495,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" s="20" t="s">
         <v>114</v>
       </c>
@@ -29524,7 +29524,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" s="20" t="s">
         <v>114</v>
       </c>
@@ -29553,7 +29553,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" s="20" t="s">
         <v>114</v>
       </c>
@@ -29582,7 +29582,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A475" s="20" t="s">
         <v>114</v>
       </c>
@@ -29615,7 +29615,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A476" s="20" t="s">
         <v>114</v>
       </c>
@@ -29648,7 +29648,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A477" s="20" t="s">
         <v>114</v>
       </c>
@@ -29681,7 +29681,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A478" s="20" t="s">
         <v>114</v>
       </c>
@@ -29714,7 +29714,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" s="20" t="s">
         <v>114</v>
       </c>
@@ -29743,7 +29743,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" s="20" t="s">
         <v>114</v>
       </c>
@@ -29772,7 +29772,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" s="20" t="s">
         <v>114</v>
       </c>
@@ -29801,7 +29801,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" s="20" t="s">
         <v>114</v>
       </c>
@@ -29830,7 +29830,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" s="20" t="s">
         <v>114</v>
       </c>
@@ -29859,7 +29859,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" s="20" t="s">
         <v>114</v>
       </c>
@@ -29888,7 +29888,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A485" s="20" t="s">
         <v>114</v>
       </c>
@@ -29921,7 +29921,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A486" s="20" t="s">
         <v>114</v>
       </c>
@@ -29954,7 +29954,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A487" s="20" t="s">
         <v>114</v>
       </c>
@@ -29987,7 +29987,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A488" s="20" t="s">
         <v>114</v>
       </c>
@@ -30020,7 +30020,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" s="20" t="s">
         <v>114</v>
       </c>
@@ -30049,7 +30049,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="20" t="s">
         <v>114</v>
       </c>
@@ -30078,7 +30078,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="20" t="s">
         <v>114</v>
       </c>
@@ -30107,7 +30107,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" s="20" t="s">
         <v>114</v>
       </c>
@@ -30136,7 +30136,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" s="20" t="s">
         <v>114</v>
       </c>
@@ -30165,7 +30165,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" s="20" t="s">
         <v>114</v>
       </c>
@@ -30194,7 +30194,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A495" s="20" t="s">
         <v>114</v>
       </c>
@@ -30224,7 +30224,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A496" s="20" t="s">
         <v>114</v>
       </c>
@@ -30257,7 +30257,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A497" s="20" t="s">
         <v>114</v>
       </c>
@@ -30290,7 +30290,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A498" s="20" t="s">
         <v>114</v>
       </c>
@@ -30323,7 +30323,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" s="20" t="s">
         <v>114</v>
       </c>
@@ -30349,7 +30349,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" s="20" t="s">
         <v>114</v>
       </c>
@@ -30378,7 +30378,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" s="20" t="s">
         <v>114</v>
       </c>
@@ -30407,7 +30407,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" s="20" t="s">
         <v>114</v>
       </c>
@@ -30436,7 +30436,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" s="20" t="s">
         <v>114</v>
       </c>
@@ -30465,7 +30465,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" s="20" t="s">
         <v>114</v>
       </c>
@@ -30494,7 +30494,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A505" s="20" t="s">
         <v>114</v>
       </c>
@@ -30527,7 +30527,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A506" s="20" t="s">
         <v>114</v>
       </c>
@@ -30560,7 +30560,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A507" s="20" t="s">
         <v>114</v>
       </c>
@@ -30593,7 +30593,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A508" s="20" t="s">
         <v>114</v>
       </c>
@@ -30626,7 +30626,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" s="20" t="s">
         <v>114</v>
       </c>
@@ -30655,7 +30655,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" s="20" t="s">
         <v>114</v>
       </c>
@@ -30684,7 +30684,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" s="20" t="s">
         <v>114</v>
       </c>
@@ -30713,7 +30713,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" s="20" t="s">
         <v>114</v>
       </c>
@@ -30742,7 +30742,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" s="20" t="s">
         <v>114</v>
       </c>
@@ -30771,7 +30771,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" s="20" t="s">
         <v>114</v>
       </c>
@@ -30800,7 +30800,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A515" s="20" t="s">
         <v>114</v>
       </c>
@@ -30833,7 +30833,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A516" s="20" t="s">
         <v>114</v>
       </c>
@@ -30866,7 +30866,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A517" s="20" t="s">
         <v>114</v>
       </c>
@@ -30899,7 +30899,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A518" s="20" t="s">
         <v>114</v>
       </c>
@@ -30932,7 +30932,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="20" t="s">
         <v>114</v>
       </c>
@@ -30961,7 +30961,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" s="20" t="s">
         <v>114</v>
       </c>
@@ -30990,7 +30990,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" s="20" t="s">
         <v>114</v>
       </c>
@@ -31019,7 +31019,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" s="20" t="s">
         <v>114</v>
       </c>
@@ -31048,7 +31048,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" s="20" t="s">
         <v>114</v>
       </c>
@@ -31077,7 +31077,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" s="20" t="s">
         <v>114</v>
       </c>
@@ -31106,7 +31106,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A525" s="20" t="s">
         <v>114</v>
       </c>
@@ -31139,7 +31139,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A526" s="20" t="s">
         <v>114</v>
       </c>
@@ -31172,7 +31172,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A527" s="20" t="s">
         <v>114</v>
       </c>
@@ -31205,7 +31205,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A528" s="20" t="s">
         <v>114</v>
       </c>
@@ -31238,7 +31238,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" s="20" t="s">
         <v>114</v>
       </c>
@@ -31267,7 +31267,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" s="20" t="s">
         <v>114</v>
       </c>
@@ -31296,7 +31296,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531" s="20" t="s">
         <v>114</v>
       </c>
@@ -31325,7 +31325,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" s="20" t="s">
         <v>114</v>
       </c>
@@ -31354,7 +31354,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" s="20" t="s">
         <v>114</v>
       </c>
@@ -31383,7 +31383,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" s="20" t="s">
         <v>114</v>
       </c>
@@ -31412,7 +31412,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" s="20" t="s">
         <v>114</v>
       </c>
@@ -31441,7 +31441,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" s="20" t="s">
         <v>114</v>
       </c>
@@ -31470,7 +31470,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" s="20" t="s">
         <v>114</v>
       </c>
@@ -31499,7 +31499,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A538" s="20" t="s">
         <v>114</v>
       </c>
@@ -31532,7 +31532,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A539" s="20" t="s">
         <v>114</v>
       </c>
@@ -31565,7 +31565,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A540" s="20" t="s">
         <v>114</v>
       </c>
@@ -31598,7 +31598,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A541" s="20" t="s">
         <v>114</v>
       </c>
@@ -31631,7 +31631,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A542" s="20" t="s">
         <v>114</v>
       </c>
@@ -31664,7 +31664,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" s="20" t="s">
         <v>114</v>
       </c>
@@ -31693,7 +31693,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" s="20" t="s">
         <v>114</v>
       </c>
@@ -31722,7 +31722,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" s="20" t="s">
         <v>114</v>
       </c>
@@ -31751,7 +31751,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" s="20" t="s">
         <v>114</v>
       </c>
@@ -31780,7 +31780,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" s="20" t="s">
         <v>114</v>
       </c>
@@ -31809,7 +31809,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" s="20" t="s">
         <v>114</v>
       </c>
@@ -31838,7 +31838,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" s="20" t="s">
         <v>114</v>
       </c>
@@ -31867,7 +31867,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" s="20" t="s">
         <v>114</v>
       </c>
@@ -31896,7 +31896,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" s="20" t="s">
         <v>114</v>
       </c>
@@ -31925,7 +31925,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" s="20" t="s">
         <v>114</v>
       </c>
@@ -31954,7 +31954,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" s="20" t="s">
         <v>114</v>
       </c>
@@ -31983,7 +31983,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" s="20" t="s">
         <v>114</v>
       </c>
@@ -32012,7 +32012,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" s="20" t="s">
         <v>114</v>
       </c>
@@ -32041,7 +32041,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" s="20" t="s">
         <v>114</v>
       </c>
@@ -32070,7 +32070,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" s="20" t="s">
         <v>114</v>
       </c>
@@ -32099,7 +32099,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A558" s="20" t="s">
         <v>114</v>
       </c>
@@ -32128,7 +32128,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A559" s="20" t="s">
         <v>114</v>
       </c>
@@ -32157,7 +32157,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560" s="20" t="s">
         <v>114</v>
       </c>
@@ -32186,7 +32186,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A561" s="20" t="s">
         <v>114</v>
       </c>
@@ -32215,7 +32215,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" s="20" t="s">
         <v>114</v>
       </c>
@@ -32244,7 +32244,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" s="20" t="s">
         <v>114</v>
       </c>
@@ -32273,7 +32273,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" s="20" t="s">
         <v>114</v>
       </c>
@@ -32302,7 +32302,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" s="20" t="s">
         <v>114</v>
       </c>
@@ -32331,7 +32331,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A566" s="20" t="s">
         <v>114</v>
       </c>
@@ -32360,7 +32360,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A567" s="20" t="s">
         <v>114</v>
       </c>
@@ -32389,7 +32389,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568" s="20" t="s">
         <v>114</v>
       </c>
@@ -32418,7 +32418,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569" s="20" t="s">
         <v>114</v>
       </c>
@@ -32447,7 +32447,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570" s="20" t="s">
         <v>114</v>
       </c>
@@ -32476,7 +32476,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" s="20" t="s">
         <v>114</v>
       </c>
@@ -32505,7 +32505,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" s="20" t="s">
         <v>114</v>
       </c>
@@ -32534,7 +32534,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" s="20" t="s">
         <v>114</v>
       </c>
@@ -32563,7 +32563,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" s="20" t="s">
         <v>114</v>
       </c>
@@ -32592,7 +32592,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575" s="20" t="s">
         <v>114</v>
       </c>
@@ -32621,7 +32621,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A576" s="20" t="s">
         <v>114</v>
       </c>
@@ -32650,7 +32650,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" s="20" t="s">
         <v>114</v>
       </c>
@@ -32679,7 +32679,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" s="20" t="s">
         <v>114</v>
       </c>
@@ -32708,7 +32708,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" s="20" t="s">
         <v>114</v>
       </c>
@@ -32737,7 +32737,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" s="20" t="s">
         <v>114</v>
       </c>
@@ -32766,7 +32766,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A581" s="20" t="s">
         <v>114</v>
       </c>
@@ -32795,7 +32795,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582" s="20" t="s">
         <v>114</v>
       </c>
@@ -32824,7 +32824,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583" s="20" t="s">
         <v>114</v>
       </c>
@@ -32853,7 +32853,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" s="20" t="s">
         <v>114</v>
       </c>
@@ -32882,7 +32882,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" s="20" t="s">
         <v>114</v>
       </c>
@@ -32911,7 +32911,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" s="20" t="s">
         <v>114</v>
       </c>
@@ -32940,7 +32940,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" s="20" t="s">
         <v>114</v>
       </c>
@@ -32969,7 +32969,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" s="20" t="s">
         <v>114</v>
       </c>
@@ -32998,7 +32998,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" s="20" t="s">
         <v>114</v>
       </c>
@@ -33027,7 +33027,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590" s="20" t="s">
         <v>114</v>
       </c>
@@ -33056,7 +33056,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591" s="20" t="s">
         <v>114</v>
       </c>
@@ -33085,7 +33085,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" s="20" t="s">
         <v>114</v>
       </c>
@@ -33114,7 +33114,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593" s="20" t="s">
         <v>114</v>
       </c>
@@ -33143,7 +33143,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594" s="20" t="s">
         <v>114</v>
       </c>
@@ -33172,7 +33172,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595" s="20" t="s">
         <v>114</v>
       </c>
@@ -33201,7 +33201,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" s="20" t="s">
         <v>114</v>
       </c>
@@ -33230,7 +33230,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" s="20" t="s">
         <v>114</v>
       </c>
@@ -33259,7 +33259,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598" s="20" t="s">
         <v>114</v>
       </c>
@@ -33288,7 +33288,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" s="20" t="s">
         <v>114</v>
       </c>
@@ -33317,7 +33317,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" s="20" t="s">
         <v>114</v>
       </c>
@@ -33346,7 +33346,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A601" s="20" t="s">
         <v>114</v>
       </c>
@@ -33375,7 +33375,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602" s="20" t="s">
         <v>114</v>
       </c>
@@ -33428,7 +33428,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D039B65-B517-48F3-ABEF-F6AA7FDFDF8B}">
   <dimension ref="A1:AE60"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37.26953125" style="20" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" style="20" bestFit="1" customWidth="1"/>
@@ -33453,7 +33453,7 @@
     <col min="35" max="16384" width="8.7265625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>107</v>
       </c>
@@ -33461,7 +33461,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
         <v>109</v>
       </c>
@@ -33469,7 +33469,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>110</v>
       </c>
@@ -33477,7 +33477,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
         <v>136</v>
       </c>
@@ -33485,7 +33485,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
         <v>138</v>
       </c>
@@ -33505,7 +33505,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
         <v>117</v>
       </c>
@@ -33528,7 +33528,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
         <v>124</v>
       </c>
@@ -33551,7 +33551,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
         <v>123</v>
       </c>
@@ -33574,7 +33574,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
         <v>125</v>
       </c>
@@ -33597,7 +33597,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
         <v>126</v>
       </c>
@@ -33617,7 +33617,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
         <v>127</v>
       </c>
@@ -33640,7 +33640,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
         <v>128</v>
       </c>
@@ -33663,7 +33663,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
         <v>129</v>
       </c>
@@ -33686,7 +33686,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
         <v>131</v>
       </c>
@@ -33706,7 +33706,7 @@
         <v>-1020.6999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
         <v>139</v>
       </c>
@@ -33726,7 +33726,7 @@
         <v>-2041.4</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A18" s="21" t="s">
         <v>140</v>
       </c>
@@ -33747,12 +33747,12 @@
         <v>-368.4</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A21" s="22"/>
       <c r="B21" s="20" t="s">
         <v>141</v>
@@ -33763,7 +33763,7 @@
       </c>
       <c r="Z21" s="23"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.35">
       <c r="B22" s="20">
         <v>2025</v>
       </c>
@@ -33789,7 +33789,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A23" s="20">
         <v>5</v>
       </c>
@@ -33831,7 +33831,7 @@
       <c r="AB23" s="24"/>
       <c r="AC23" s="24"/>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A24" s="20">
         <v>20</v>
       </c>
@@ -33873,7 +33873,7 @@
       <c r="AB24" s="24"/>
       <c r="AC24" s="24"/>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A25" s="20">
         <v>35</v>
       </c>
@@ -33915,7 +33915,7 @@
       <c r="AB25" s="24"/>
       <c r="AC25" s="24"/>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A26" s="20">
         <v>50</v>
       </c>
@@ -33957,7 +33957,7 @@
       <c r="AB26" s="24"/>
       <c r="AC26" s="24"/>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A27" s="20">
         <v>100</v>
       </c>
@@ -33999,12 +33999,12 @@
       <c r="AB27" s="24"/>
       <c r="AC27" s="24"/>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A30" s="22"/>
       <c r="B30" s="20" t="s">
         <v>141</v>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="Z30" s="23"/>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.35">
       <c r="B31" s="20">
         <v>2025</v>
       </c>
@@ -34041,7 +34041,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A32" s="20">
         <v>5</v>
       </c>
@@ -34083,7 +34083,7 @@
       <c r="AB32" s="24"/>
       <c r="AC32" s="24"/>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
         <v>20</v>
       </c>
@@ -34125,7 +34125,7 @@
       <c r="AB33" s="24"/>
       <c r="AC33" s="24"/>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A34" s="20">
         <v>35</v>
       </c>
@@ -34167,7 +34167,7 @@
       <c r="AB34" s="24"/>
       <c r="AC34" s="24"/>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A35" s="20">
         <v>50</v>
       </c>
@@ -34209,7 +34209,7 @@
       <c r="AB35" s="25"/>
       <c r="AC35" s="24"/>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A36" s="20">
         <v>100</v>
       </c>
@@ -34251,15 +34251,15 @@
       <c r="AB36" s="24"/>
       <c r="AC36" s="24"/>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A37" s="22"/>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A38" s="22" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="34" t="s">
         <v>159</v>
       </c>
@@ -34354,7 +34354,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="20">
         <v>5</v>
       </c>
@@ -34479,7 +34479,7 @@
         <v>24900000000000.09</v>
       </c>
     </row>
-    <row r="41" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="20">
         <v>20</v>
       </c>
@@ -34604,7 +34604,7 @@
         <v>28299999999999.953</v>
       </c>
     </row>
-    <row r="42" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="20">
         <v>35</v>
       </c>
@@ -34729,7 +34729,7 @@
         <v>12750000000000</v>
       </c>
     </row>
-    <row r="43" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20">
         <v>50</v>
       </c>
@@ -34854,7 +34854,7 @@
         <v>4450000000000.0029</v>
       </c>
     </row>
-    <row r="44" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="20">
         <v>100</v>
       </c>
@@ -34979,12 +34979,12 @@
         <v>11949999999999.988</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A46" s="22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="34" t="s">
         <v>159</v>
       </c>
@@ -35079,7 +35079,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="48" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="20">
         <v>5</v>
       </c>
@@ -35204,7 +35204,7 @@
         <v>1050000000000.0114</v>
       </c>
     </row>
-    <row r="49" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="20">
         <v>20</v>
       </c>
@@ -35329,7 +35329,7 @@
         <v>50250000000000</v>
       </c>
     </row>
-    <row r="50" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="20">
         <v>35</v>
       </c>
@@ -35454,7 +35454,7 @@
         <v>60350000000000.023</v>
       </c>
     </row>
-    <row r="51" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="20">
         <v>50</v>
       </c>
@@ -35579,7 +35579,7 @@
         <v>43500000000000</v>
       </c>
     </row>
-    <row r="52" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="20">
         <v>100</v>
       </c>
@@ -35704,12 +35704,12 @@
         <v>19899999999999.863</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A54" s="22" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="34" t="s">
         <v>159</v>
       </c>
@@ -35804,7 +35804,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="56" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="20">
         <v>5</v>
       </c>
@@ -35929,7 +35929,7 @@
         <v>1050000000000.0114</v>
       </c>
     </row>
-    <row r="57" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="20">
         <v>20</v>
       </c>
@@ -36054,7 +36054,7 @@
         <v>50250000000000</v>
       </c>
     </row>
-    <row r="58" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="20">
         <v>35</v>
       </c>
@@ -36179,7 +36179,7 @@
         <v>60350000000000.023</v>
       </c>
     </row>
-    <row r="59" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="20">
         <v>50</v>
       </c>
@@ -36304,7 +36304,7 @@
         <v>43500000000000</v>
       </c>
     </row>
-    <row r="60" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="20">
         <v>100</v>
       </c>
@@ -36440,7 +36440,7 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:BM272"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="73.81640625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -36453,7 +36453,7 @@
     <col min="16" max="16" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>77</v>
       </c>
@@ -36521,17 +36521,17 @@
       <c r="BK1" s="10"/>
       <c r="BL1" s="10"/>
     </row>
-    <row r="2" spans="1:64" ht="145.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:64" ht="145.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>91</v>
       </c>
       <c r="B2" s="12"/>
     </row>
-    <row r="3" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
     </row>
-    <row r="4" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>78</v>
       </c>
@@ -36599,7 +36599,7 @@
       <c r="BK4" s="10"/>
       <c r="BL4" s="10"/>
     </row>
-    <row r="5" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -36607,12 +36607,12 @@
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -36623,7 +36623,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -36634,7 +36634,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>83</v>
       </c>
@@ -36645,7 +36645,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>84</v>
       </c>
@@ -36656,7 +36656,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -36667,7 +36667,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>86</v>
       </c>
@@ -36678,7 +36678,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>86</v>
       </c>
@@ -36689,7 +36689,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -36700,7 +36700,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -36711,7 +36711,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -36722,7 +36722,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -36733,7 +36733,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -36744,12 +36744,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>85</v>
       </c>
@@ -36758,7 +36758,7 @@
         <v>1299999999.9999998</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>89</v>
       </c>
@@ -36767,12 +36767,12 @@
         <v>1500000000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B42">
         <v>2023</v>
       </c>
@@ -36801,7 +36801,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>156</v>
       </c>
@@ -36833,7 +36833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>157</v>
       </c>
@@ -36865,7 +36865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>158</v>
       </c>
@@ -36897,7 +36897,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>154</v>
       </c>
@@ -36938,7 +36938,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>155</v>
       </c>
@@ -36979,7 +36979,7 @@
         <v>5.1172707889125799E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B48" s="36"/>
       <c r="C48" s="36"/>
       <c r="D48" s="36"/>
@@ -36990,7 +36990,7 @@
       <c r="I48" s="36"/>
       <c r="J48" s="36"/>
     </row>
-    <row r="49" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A49" s="27"/>
       <c r="B49" s="28"/>
       <c r="C49" s="27"/>
@@ -37063,7 +37063,7 @@
       <c r="BL49" s="16"/>
       <c r="BM49" s="16"/>
     </row>
-    <row r="50" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A50" s="27"/>
       <c r="B50" s="12">
         <v>2023</v>
@@ -37155,7 +37155,7 @@
       <c r="BL50" s="16"/>
       <c r="BM50" s="16"/>
     </row>
-    <row r="51" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A51" s="27" t="s">
         <v>160</v>
       </c>
@@ -37262,7 +37262,7 @@
       <c r="BL51" s="16"/>
       <c r="BM51" s="16"/>
     </row>
-    <row r="52" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A52" s="27" t="s">
         <v>161</v>
       </c>
@@ -37369,7 +37369,7 @@
       <c r="BL52" s="16"/>
       <c r="BM52" s="16"/>
     </row>
-    <row r="53" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A53" s="27"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -37435,7 +37435,7 @@
       <c r="BL53" s="16"/>
       <c r="BM53" s="16"/>
     </row>
-    <row r="54" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A54" s="27"/>
       <c r="B54" s="30"/>
       <c r="C54" s="27"/>
@@ -37501,7 +37501,7 @@
       <c r="BL54" s="16"/>
       <c r="BM54" s="16"/>
     </row>
-    <row r="55" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A55" s="31" t="s">
         <v>162</v>
       </c>
@@ -37545,7 +37545,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="56" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A56" s="32">
         <v>5</v>
       </c>
@@ -37602,7 +37602,7 @@
         <v>78500000.000000224</v>
       </c>
     </row>
-    <row r="57" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A57" s="32">
         <v>20</v>
       </c>
@@ -37659,7 +37659,7 @@
         <v>468000000.00000179</v>
       </c>
     </row>
-    <row r="58" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A58" s="32">
         <v>35</v>
       </c>
@@ -37716,7 +37716,7 @@
         <v>364000000.00000316</v>
       </c>
     </row>
-    <row r="59" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A59" s="32">
         <v>50</v>
       </c>
@@ -37773,7 +37773,7 @@
         <v>189999999.99999917</v>
       </c>
     </row>
-    <row r="60" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A60" s="32">
         <v>100</v>
       </c>
@@ -37830,7 +37830,7 @@
         <v>1080000000.0000012</v>
       </c>
     </row>
-    <row r="61" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A61" s="32"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -37843,7 +37843,7 @@
       <c r="J61" s="12"/>
       <c r="L61" s="12"/>
     </row>
-    <row r="62" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A62" s="31" t="s">
         <v>163</v>
       </c>
@@ -37887,7 +37887,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="63" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A63" s="32">
         <v>5</v>
       </c>
@@ -37944,7 +37944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:65" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A64" s="32">
         <v>20</v>
       </c>
@@ -38001,7 +38001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A65" s="32">
         <v>35</v>
       </c>
@@ -38058,7 +38058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A66" s="32">
         <v>50</v>
       </c>
@@ -38115,7 +38115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A67" s="32">
         <v>100</v>
       </c>
@@ -38172,7 +38172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A68" s="27"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -38188,7 +38188,7 @@
       <c r="M68" s="12"/>
       <c r="N68" s="12"/>
     </row>
-    <row r="69" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A69" s="31" t="s">
         <v>165</v>
       </c>
@@ -38245,7 +38245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A70" s="31" t="s">
         <v>164</v>
       </c>
@@ -38352,7 +38352,7 @@
       <c r="BK70" s="12"/>
       <c r="BL70" s="12"/>
     </row>
-    <row r="71" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
@@ -38418,7 +38418,7 @@
       <c r="BK71" s="12"/>
       <c r="BL71" s="12"/>
     </row>
-    <row r="72" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A72" s="31" t="s">
         <v>169</v>
       </c>
@@ -38462,7 +38462,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="73" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A73" s="32">
         <v>5</v>
       </c>
@@ -38519,7 +38519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A74" s="32">
         <v>20</v>
       </c>
@@ -38576,7 +38576,7 @@
         <v>437200000.00001162</v>
       </c>
     </row>
-    <row r="75" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A75" s="32">
         <v>35</v>
       </c>
@@ -38633,7 +38633,7 @@
         <v>908600000.00000119</v>
       </c>
     </row>
-    <row r="76" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A76" s="32">
         <v>50</v>
       </c>
@@ -38690,7 +38690,7 @@
         <v>2238000000.0000048</v>
       </c>
     </row>
-    <row r="77" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A77" s="32">
         <v>100</v>
       </c>
@@ -38747,7 +38747,7 @@
         <v>1595999999.9999583</v>
       </c>
     </row>
-    <row r="78" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A78" s="32"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
@@ -38760,7 +38760,7 @@
       <c r="J78" s="12"/>
       <c r="L78" s="12"/>
     </row>
-    <row r="79" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A79" s="31" t="s">
         <v>166</v>
       </c>
@@ -38804,7 +38804,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="80" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A80" s="32">
         <v>5</v>
       </c>
@@ -38861,7 +38861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A81" s="32">
         <v>20</v>
       </c>
@@ -38918,7 +38918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A82" s="32">
         <v>35</v>
       </c>
@@ -38975,7 +38975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A83" s="32">
         <v>50</v>
       </c>
@@ -39032,7 +39032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A84" s="32">
         <v>100</v>
       </c>
@@ -39089,7 +39089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A85" s="27"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
@@ -39105,7 +39105,7 @@
       <c r="M85" s="12"/>
       <c r="N85" s="12"/>
     </row>
-    <row r="86" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A86" s="31" t="s">
         <v>167</v>
       </c>
@@ -39162,7 +39162,7 @@
         <v>10179858186482.16</v>
       </c>
     </row>
-    <row r="87" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A87" s="13"/>
       <c r="B87" s="12">
         <f>B86/10^12</f>
@@ -39267,10 +39267,10 @@
       <c r="BK87" s="12"/>
       <c r="BL87" s="12"/>
     </row>
-    <row r="88" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A88" s="13"/>
     </row>
-    <row r="89" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A89" s="13"/>
       <c r="B89" s="12">
         <v>2021</v>
@@ -39363,7 +39363,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="90" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>170</v>
       </c>
@@ -39489,7 +39489,7 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
     </row>
-    <row r="91" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>171</v>
       </c>
@@ -39615,7 +39615,7 @@
       <c r="AG91" s="18"/>
       <c r="AH91" s="18"/>
     </row>
-    <row r="92" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:64" x14ac:dyDescent="0.35">
       <c r="D92" s="18"/>
       <c r="E92" s="18"/>
       <c r="F92" s="18"/>
@@ -39646,7 +39646,7 @@
       <c r="AE92" s="18"/>
       <c r="AF92" s="18"/>
     </row>
-    <row r="93" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>172</v>
       </c>
@@ -39680,7 +39680,7 @@
       <c r="AE93" s="18"/>
       <c r="AF93" s="18"/>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" s="13" t="s">
         <v>92</v>
       </c>
@@ -39688,15 +39688,15 @@
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" s="13"/>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" s="16" t="s">
         <v>80</v>
       </c>
@@ -39708,7 +39708,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" s="16" t="s">
         <v>82</v>
       </c>
@@ -39720,7 +39720,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A257" s="16" t="s">
         <v>83</v>
       </c>
@@ -39732,7 +39732,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" s="16" t="s">
         <v>84</v>
       </c>
@@ -39744,7 +39744,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" s="16" t="s">
         <v>86</v>
       </c>
@@ -39756,7 +39756,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" s="16" t="s">
         <v>86</v>
       </c>
@@ -39768,7 +39768,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" s="16" t="s">
         <v>86</v>
       </c>
@@ -39780,7 +39780,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" s="16" t="s">
         <v>86</v>
       </c>
@@ -39792,7 +39792,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" s="16" t="s">
         <v>87</v>
       </c>
@@ -39804,7 +39804,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" s="16" t="s">
         <v>86</v>
       </c>
@@ -39816,7 +39816,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" s="16" t="s">
         <v>88</v>
       </c>
@@ -39828,7 +39828,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" s="16" t="s">
         <v>90</v>
       </c>
@@ -39840,13 +39840,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" s="15" t="s">
         <v>144</v>
       </c>
       <c r="B268" s="14"/>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" s="16" t="s">
         <v>85</v>
       </c>
@@ -39855,7 +39855,7 @@
         <v>102049999.99999999</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" s="16" t="s">
         <v>89</v>
       </c>
@@ -39864,7 +39864,7 @@
         <v>117750000</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>146</v>
       </c>
@@ -39882,14 +39882,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF13"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.7265625" customWidth="1"/>
     <col min="2" max="17" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="18" max="32" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>102</v>
       </c>
@@ -39987,136 +39987,136 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="39">
+      <c r="B2" s="40">
         <f>Calcs!B4*10^12</f>
         <v>-972800000000000</v>
       </c>
-      <c r="C2" s="39">
-        <f>Calcs!C4*10^12</f>
+      <c r="C2" s="40">
+        <f>Calcs!C4*10^12-'Inflation Reduction Act'!B90</f>
         <v>-983400000000000</v>
       </c>
-      <c r="D2" s="39">
-        <f>Calcs!D4*10^12</f>
+      <c r="D2" s="40">
+        <f>Calcs!D4*10^12-'Inflation Reduction Act'!C90</f>
         <v>-921800000000000</v>
       </c>
-      <c r="E2" s="39">
-        <f>Calcs!E4*10^12</f>
+      <c r="E2" s="40">
+        <f>Calcs!E4*10^12-'Inflation Reduction Act'!D90</f>
         <v>-956473333333333.38</v>
       </c>
-      <c r="F2" s="39">
-        <f>Calcs!F4*10^12</f>
+      <c r="F2" s="40">
+        <f>Calcs!F4*10^12-'Inflation Reduction Act'!E90</f>
         <v>-956384848484848.5</v>
       </c>
-      <c r="G2" s="39">
-        <f>Calcs!G4*10^12</f>
+      <c r="G2" s="40">
+        <f>Calcs!G4*10^12-'Inflation Reduction Act'!F90</f>
         <v>-956296363636363.63</v>
       </c>
-      <c r="H2" s="39">
-        <f>Calcs!H4*10^12</f>
-        <v>-956207878787878.88</v>
-      </c>
-      <c r="I2" s="39">
-        <f>Calcs!I4*10^12</f>
-        <v>-956119393939394</v>
-      </c>
-      <c r="J2" s="39">
-        <f>Calcs!J4*10^12</f>
-        <v>-956030909090909.13</v>
-      </c>
-      <c r="K2" s="39">
-        <f>Calcs!K4*10^12</f>
-        <v>-955942424242424.25</v>
-      </c>
-      <c r="L2" s="39">
-        <f>Calcs!L4*10^12</f>
-        <v>-955853939393939.38</v>
-      </c>
-      <c r="M2" s="39">
-        <f>Calcs!M4*10^12</f>
-        <v>-955765454545454.5</v>
-      </c>
-      <c r="N2" s="39">
-        <f>Calcs!N4*10^12</f>
-        <v>-955676969696969.63</v>
-      </c>
-      <c r="O2" s="39">
-        <f>Calcs!O4*10^12</f>
-        <v>-955588484848484.75</v>
-      </c>
-      <c r="P2" s="39">
-        <f>Calcs!P4*10^12</f>
-        <v>-955500000000000</v>
-      </c>
-      <c r="Q2" s="39">
-        <f>Calcs!Q4*10^12</f>
-        <v>-955411515151515.13</v>
-      </c>
-      <c r="R2" s="39">
-        <f>Calcs!R4*10^12</f>
-        <v>-955323030303030.25</v>
-      </c>
-      <c r="S2" s="39">
-        <f>Calcs!S4*10^12</f>
-        <v>-955234545454545.5</v>
-      </c>
-      <c r="T2" s="39">
-        <f>Calcs!T4*10^12</f>
-        <v>-955146060606060.63</v>
-      </c>
-      <c r="U2" s="39">
-        <f>Calcs!U4*10^12</f>
-        <v>-955057575757575.75</v>
-      </c>
-      <c r="V2" s="39">
-        <f>Calcs!V4*10^12</f>
-        <v>-954969090909090.88</v>
-      </c>
-      <c r="W2" s="39">
-        <f>Calcs!W4*10^12</f>
-        <v>-954880606060606</v>
-      </c>
-      <c r="X2" s="39">
-        <f>Calcs!X4*10^12</f>
-        <v>-954792121212121.13</v>
-      </c>
-      <c r="Y2" s="39">
-        <f>Calcs!Y4*10^12</f>
-        <v>-954703636363636.25</v>
-      </c>
-      <c r="Z2" s="39">
-        <f>Calcs!Z4*10^12</f>
-        <v>-954615151515151.38</v>
-      </c>
-      <c r="AA2" s="39">
-        <f>Calcs!AA4*10^12</f>
-        <v>-954526666666666.63</v>
-      </c>
-      <c r="AB2" s="39">
-        <f>Calcs!AB4*10^12</f>
-        <v>-954438181818181.75</v>
-      </c>
-      <c r="AC2" s="39">
-        <f>Calcs!AC4*10^12</f>
-        <v>-954349696969696.88</v>
-      </c>
-      <c r="AD2" s="39">
-        <f>Calcs!AD4*10^12</f>
-        <v>-954261212121212.13</v>
-      </c>
-      <c r="AE2" s="39">
-        <f>Calcs!AE4*10^12</f>
-        <v>-954172727272727.25</v>
-      </c>
-      <c r="AF2" s="39">
-        <f>Calcs!AF4*10^12</f>
-        <v>-954084242424242.38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="H2" s="40">
+        <f>Calcs!H4*10^12-'Inflation Reduction Act'!G90</f>
+        <v>-963781270634201.13</v>
+      </c>
+      <c r="I2" s="40">
+        <f>Calcs!I4*10^12-'Inflation Reduction Act'!H90</f>
+        <v>-974205885478659.13</v>
+      </c>
+      <c r="J2" s="40">
+        <f>Calcs!J4*10^12-'Inflation Reduction Act'!I90</f>
+        <v>-980543585639673.13</v>
+      </c>
+      <c r="K2" s="40">
+        <f>Calcs!K4*10^12-'Inflation Reduction Act'!J90</f>
+        <v>-981937847460889.38</v>
+      </c>
+      <c r="L2" s="40">
+        <f>Calcs!L4*10^12-'Inflation Reduction Act'!K90</f>
+        <v>-980829453230741.38</v>
+      </c>
+      <c r="M2" s="40">
+        <f>Calcs!M4*10^12-'Inflation Reduction Act'!L90</f>
+        <v>-978196538744729.75</v>
+      </c>
+      <c r="N2" s="40">
+        <f>Calcs!N4*10^12-'Inflation Reduction Act'!M90</f>
+        <v>-975835505921831.25</v>
+      </c>
+      <c r="O2" s="40">
+        <f>Calcs!O4*10^12-'Inflation Reduction Act'!N90</f>
+        <v>-972420795060553.25</v>
+      </c>
+      <c r="P2" s="40">
+        <f>Calcs!P4*10^12-'Inflation Reduction Act'!O90</f>
+        <v>-969006084199275.38</v>
+      </c>
+      <c r="Q2" s="40">
+        <f>Calcs!Q4*10^12-'Inflation Reduction Act'!P90</f>
+        <v>-965591373337997.25</v>
+      </c>
+      <c r="R2" s="40">
+        <f>Calcs!R4*10^12-'Inflation Reduction Act'!Q90</f>
+        <v>-965502888489512.38</v>
+      </c>
+      <c r="S2" s="40">
+        <f>Calcs!S4*10^12-'Inflation Reduction Act'!R90</f>
+        <v>-965414403641027.63</v>
+      </c>
+      <c r="T2" s="40">
+        <f>Calcs!T4*10^12-'Inflation Reduction Act'!S90</f>
+        <v>-965325918792542.75</v>
+      </c>
+      <c r="U2" s="40">
+        <f>Calcs!U4*10^12-'Inflation Reduction Act'!T90</f>
+        <v>-965237433944057.88</v>
+      </c>
+      <c r="V2" s="40">
+        <f>Calcs!V4*10^12-'Inflation Reduction Act'!U90</f>
+        <v>-965148949095573</v>
+      </c>
+      <c r="W2" s="40">
+        <f>Calcs!W4*10^12-'Inflation Reduction Act'!V90</f>
+        <v>-965060464247088.13</v>
+      </c>
+      <c r="X2" s="40">
+        <f>Calcs!X4*10^12-'Inflation Reduction Act'!W90</f>
+        <v>-964971979398603.25</v>
+      </c>
+      <c r="Y2" s="40">
+        <f>Calcs!Y4*10^12-'Inflation Reduction Act'!X90</f>
+        <v>-964883494550118.38</v>
+      </c>
+      <c r="Z2" s="40">
+        <f>Calcs!Z4*10^12-'Inflation Reduction Act'!Y90</f>
+        <v>-964795009701633.5</v>
+      </c>
+      <c r="AA2" s="40">
+        <f>Calcs!AA4*10^12-'Inflation Reduction Act'!Z90</f>
+        <v>-964706524853148.75</v>
+      </c>
+      <c r="AB2" s="40">
+        <f>Calcs!AB4*10^12-'Inflation Reduction Act'!AA90</f>
+        <v>-964618040004663.88</v>
+      </c>
+      <c r="AC2" s="40">
+        <f>Calcs!AC4*10^12-'Inflation Reduction Act'!AB90</f>
+        <v>-964529555156179</v>
+      </c>
+      <c r="AD2" s="40">
+        <f>Calcs!AD4*10^12-'Inflation Reduction Act'!AC90</f>
+        <v>-964441070307694.25</v>
+      </c>
+      <c r="AE2" s="40">
+        <f>Calcs!AE4*10^12-'Inflation Reduction Act'!AD90</f>
+        <v>-964352585459209.38</v>
+      </c>
+      <c r="AF2" s="40">
+        <f>Calcs!AF4*10^12-'Inflation Reduction Act'!AE90</f>
+        <v>-964264100610724.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -40214,7 +40214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -40312,7 +40312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -40410,7 +40410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -40508,7 +40508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -40606,7 +40606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -40704,7 +40704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -40802,7 +40802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -40900,265 +40900,265 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="40">
         <f>Calcs!B5*10^12/About!$B$17</f>
         <v>2117857142857.1428</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="40">
         <f>Calcs!C5*10^12/About!$B$17</f>
         <v>2217857142857.1431</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="40">
         <f>Calcs!D5*10^12/About!$B$17</f>
         <v>2085714285714.2856</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="40">
         <f>Calcs!E5*10^12/About!$B$17</f>
         <v>2121060606060.6055</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="40">
         <f>Calcs!F5*10^12/About!$B$17</f>
         <v>2136883116883.1184</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="40">
         <f>Calcs!G5*10^12/About!$B$17</f>
         <v>2152705627705.6309</v>
       </c>
-      <c r="H11" s="39">
+      <c r="H11" s="40">
         <f>Calcs!H5*10^12/About!$B$17</f>
         <v>2168528138528.1394</v>
       </c>
-      <c r="I11" s="39">
+      <c r="I11" s="40">
         <f>Calcs!I5*10^12/About!$B$17</f>
         <v>2184350649350.6523</v>
       </c>
-      <c r="J11" s="39">
+      <c r="J11" s="40">
         <f>Calcs!J5*10^12/About!$B$17</f>
         <v>2200173160173.1606</v>
       </c>
-      <c r="K11" s="39">
+      <c r="K11" s="40">
         <f>Calcs!K5*10^12/About!$B$17</f>
         <v>2215995670995.6733</v>
       </c>
-      <c r="L11" s="39">
+      <c r="L11" s="40">
         <f>Calcs!L5*10^12/About!$B$17</f>
         <v>2231818181818.1821</v>
       </c>
-      <c r="M11" s="39">
+      <c r="M11" s="40">
         <f>Calcs!M5*10^12/About!$B$17</f>
         <v>2247640692640.6948</v>
       </c>
-      <c r="N11" s="39">
+      <c r="N11" s="40">
         <f>Calcs!N5*10^12/About!$B$17</f>
         <v>2263463203463.2036</v>
       </c>
-      <c r="O11" s="39">
+      <c r="O11" s="40">
         <f>Calcs!O5*10^12/About!$B$17</f>
         <v>2279285714285.7158</v>
       </c>
-      <c r="P11" s="39">
+      <c r="P11" s="40">
         <f>Calcs!P5*10^12/About!$B$17</f>
         <v>2295108225108.2246</v>
       </c>
-      <c r="Q11" s="39">
+      <c r="Q11" s="40">
         <f>Calcs!Q5*10^12/About!$B$17</f>
         <v>2310930735930.7373</v>
       </c>
-      <c r="R11" s="39">
+      <c r="R11" s="40">
         <f>Calcs!R5*10^12/About!$B$17</f>
         <v>2326753246753.25</v>
       </c>
-      <c r="S11" s="39">
+      <c r="S11" s="40">
         <f>Calcs!S5*10^12/About!$B$17</f>
         <v>2342575757575.7588</v>
       </c>
-      <c r="T11" s="39">
+      <c r="T11" s="40">
         <f>Calcs!T5*10^12/About!$B$17</f>
         <v>2358398268398.271</v>
       </c>
-      <c r="U11" s="39">
+      <c r="U11" s="40">
         <f>Calcs!U5*10^12/About!$B$17</f>
         <v>2374220779220.7798</v>
       </c>
-      <c r="V11" s="39">
+      <c r="V11" s="40">
         <f>Calcs!V5*10^12/About!$B$17</f>
         <v>2390043290043.2925</v>
       </c>
-      <c r="W11" s="39">
+      <c r="W11" s="40">
         <f>Calcs!W5*10^12/About!$B$17</f>
         <v>2405865800865.8013</v>
       </c>
-      <c r="X11" s="39">
+      <c r="X11" s="40">
         <f>Calcs!X5*10^12/About!$B$17</f>
         <v>2421688311688.314</v>
       </c>
-      <c r="Y11" s="39">
+      <c r="Y11" s="40">
         <f>Calcs!Y5*10^12/About!$B$17</f>
         <v>2437510822510.8228</v>
       </c>
-      <c r="Z11" s="39">
+      <c r="Z11" s="40">
         <f>Calcs!Z5*10^12/About!$B$17</f>
         <v>2453333333333.335</v>
       </c>
-      <c r="AA11" s="39">
+      <c r="AA11" s="40">
         <f>Calcs!AA5*10^12/About!$B$17</f>
         <v>2469155844155.8438</v>
       </c>
-      <c r="AB11" s="39">
+      <c r="AB11" s="40">
         <f>Calcs!AB5*10^12/About!$B$17</f>
         <v>2484978354978.3564</v>
       </c>
-      <c r="AC11" s="39">
+      <c r="AC11" s="40">
         <f>Calcs!AC5*10^12/About!$B$17</f>
         <v>2500800865800.8647</v>
       </c>
-      <c r="AD11" s="39">
+      <c r="AD11" s="40">
         <f>Calcs!AD5*10^12/About!$B$17</f>
         <v>2516623376623.3779</v>
       </c>
-      <c r="AE11" s="39">
+      <c r="AE11" s="40">
         <f>Calcs!AE5*10^12/About!$B$17</f>
         <v>2532445887445.8906</v>
       </c>
-      <c r="AF11" s="39">
+      <c r="AF11" s="40">
         <f>Calcs!AF5*10^12/About!$B$17</f>
         <v>2548268398268.3989</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="39">
+      <c r="B12" s="40">
         <f>Calcs!B6*10^12/About!$B$18</f>
         <v>34339622641.509434</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="40">
         <f>Calcs!C6*10^12/About!$B$18</f>
         <v>40377358490.56604</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="40">
         <f>Calcs!D6*10^12/About!$B$18</f>
         <v>34339622641.509434</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="40">
         <f>Calcs!E6*10^12/About!$B$18</f>
         <v>34810748999.428329</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="40">
         <f>Calcs!F6*10^12/About!$B$18</f>
         <v>35684391080.617645</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="40">
         <f>Calcs!G6*10^12/About!$B$18</f>
         <v>36558033161.806961</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H12" s="40">
         <f>Calcs!H6*10^12/About!$B$18</f>
         <v>37431675242.996277</v>
       </c>
-      <c r="I12" s="39">
+      <c r="I12" s="40">
         <f>Calcs!I6*10^12/About!$B$18</f>
         <v>38305317324.185379</v>
       </c>
-      <c r="J12" s="39">
+      <c r="J12" s="40">
         <f>Calcs!J6*10^12/About!$B$18</f>
         <v>39178959405.374687</v>
       </c>
-      <c r="K12" s="39">
+      <c r="K12" s="40">
         <f>Calcs!K6*10^12/About!$B$18</f>
         <v>40052601486.564003</v>
       </c>
-      <c r="L12" s="39">
+      <c r="L12" s="40">
         <f>Calcs!L6*10^12/About!$B$18</f>
         <v>40926243567.753105</v>
       </c>
-      <c r="M12" s="39">
+      <c r="M12" s="40">
         <f>Calcs!M6*10^12/About!$B$18</f>
         <v>41799885648.942413</v>
       </c>
-      <c r="N12" s="39">
+      <c r="N12" s="40">
         <f>Calcs!N6*10^12/About!$B$18</f>
         <v>42673527730.131729</v>
       </c>
-      <c r="O12" s="39">
+      <c r="O12" s="40">
         <f>Calcs!O6*10^12/About!$B$18</f>
         <v>43547169811.320831</v>
       </c>
-      <c r="P12" s="39">
+      <c r="P12" s="40">
         <f>Calcs!P6*10^12/About!$B$18</f>
         <v>44420811892.510147</v>
       </c>
-      <c r="Q12" s="39">
+      <c r="Q12" s="40">
         <f>Calcs!Q6*10^12/About!$B$18</f>
         <v>45294453973.699463</v>
       </c>
-      <c r="R12" s="39">
+      <c r="R12" s="40">
         <f>Calcs!R6*10^12/About!$B$18</f>
         <v>46168096054.888779</v>
       </c>
-      <c r="S12" s="39">
+      <c r="S12" s="40">
         <f>Calcs!S6*10^12/About!$B$18</f>
         <v>47041738136.077873</v>
       </c>
-      <c r="T12" s="39">
+      <c r="T12" s="40">
         <f>Calcs!T6*10^12/About!$B$18</f>
         <v>47915380217.267189</v>
       </c>
-      <c r="U12" s="39">
+      <c r="U12" s="40">
         <f>Calcs!U6*10^12/About!$B$18</f>
         <v>48789022298.456497</v>
       </c>
-      <c r="V12" s="39">
+      <c r="V12" s="40">
         <f>Calcs!V6*10^12/About!$B$18</f>
         <v>49662664379.645607</v>
       </c>
-      <c r="W12" s="39">
+      <c r="W12" s="40">
         <f>Calcs!W6*10^12/About!$B$18</f>
         <v>50536306460.834923</v>
       </c>
-      <c r="X12" s="39">
+      <c r="X12" s="40">
         <f>Calcs!X6*10^12/About!$B$18</f>
         <v>51409948542.024231</v>
       </c>
-      <c r="Y12" s="39">
+      <c r="Y12" s="40">
         <f>Calcs!Y6*10^12/About!$B$18</f>
         <v>52283590623.213333</v>
       </c>
-      <c r="Z12" s="39">
+      <c r="Z12" s="40">
         <f>Calcs!Z6*10^12/About!$B$18</f>
         <v>53157232704.402649</v>
       </c>
-      <c r="AA12" s="39">
+      <c r="AA12" s="40">
         <f>Calcs!AA6*10^12/About!$B$18</f>
         <v>54030874785.591957</v>
       </c>
-      <c r="AB12" s="39">
+      <c r="AB12" s="40">
         <f>Calcs!AB6*10^12/About!$B$18</f>
         <v>54904516866.781281</v>
       </c>
-      <c r="AC12" s="39">
+      <c r="AC12" s="40">
         <f>Calcs!AC6*10^12/About!$B$18</f>
         <v>55778158947.970375</v>
       </c>
-      <c r="AD12" s="39">
+      <c r="AD12" s="40">
         <f>Calcs!AD6*10^12/About!$B$18</f>
         <v>56651801029.159691</v>
       </c>
-      <c r="AE12" s="39">
+      <c r="AE12" s="40">
         <f>Calcs!AE6*10^12/About!$B$18</f>
         <v>57525443110.349007</v>
       </c>
-      <c r="AF12" s="39">
+      <c r="AF12" s="40">
         <f>Calcs!AF6*10^12/About!$B$18</f>
         <v>58399085191.538101</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>

--- a/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
+++ b/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us-analysis\InputData\land\BLAPE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\land\BLAPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C77911D-64E4-4705-BF98-CEE780ECF87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C994E1-3E4F-43E0-A513-39717EA92B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37695" yWindow="2850" windowWidth="19185" windowHeight="11265" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId14"/>
+    <pivotCache cacheId="11" r:id="rId14"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -828,10 +828,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Currency" xfId="3" builtinId="4"/>
@@ -1258,6 +1258,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1265,7 +1266,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9247,7 +9247,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9616E194-24DA-4C46-8097-71C6F2CA831B}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9616E194-24DA-4C46-8097-71C6F2CA831B}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:F16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -9670,18 +9670,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="19.1796875" customWidth="1"/>
     <col min="2" max="2" width="51.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -9689,62 +9689,62 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B5" s="4">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B7" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B10" s="26" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B11" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B12" s="4">
         <v>2024</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -9760,27 +9760,27 @@
         <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>145</v>
       </c>
@@ -9797,22 +9797,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AH15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="63.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.75">
       <c r="B3" s="6">
         <v>2020</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -10036,7 +10036,7 @@
         <v>-954.08424242424235</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>71.351515151515173</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -10294,29 +10294,29 @@
         <v>15.475757575757598</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.75">
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.75">
       <c r="AG11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="AH11" s="7"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -10557,7 +10557,7 @@
         <v>-921.8</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -10840,18 +10840,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH56"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="255.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="33" width="6.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -10955,7 +10955,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -11059,7 +11059,7 @@
         <v>-771.7</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>-787</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -11267,7 +11267,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -11371,7 +11371,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>-100.3</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -11683,7 +11683,7 @@
         <v>-100.3</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>-31.7</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -11891,7 +11891,7 @@
         <v>-31.7</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -12203,7 +12203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -12307,7 +12307,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -12411,7 +12411,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -12515,7 +12515,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -12723,7 +12723,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -12827,7 +12827,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -12931,7 +12931,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -13035,7 +13035,7 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -13139,7 +13139,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -13555,7 +13555,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -13763,7 +13763,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -13867,7 +13867,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>53</v>
       </c>
@@ -13971,7 +13971,7 @@
         <v>-132.30000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -14075,7 +14075,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>-138.5</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>57</v>
       </c>
@@ -14387,7 +14387,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>58</v>
       </c>
@@ -14491,7 +14491,7 @@
         <v>68.2</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>68.2</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>59</v>
       </c>
@@ -14699,7 +14699,7 @@
         <v>67.599999999999994</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -14803,7 +14803,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -14907,7 +14907,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>60</v>
       </c>
@@ -15011,7 +15011,7 @@
         <v>-921.8</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -15115,67 +15115,67 @@
         <v>-854.2</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -15190,27 +15190,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D41D2ED-A995-4355-B1B7-DFF537DF2BE3}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AE602"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="4" width="11.453125" style="20"/>
     <col min="5" max="5" width="18.26953125" style="20" customWidth="1"/>
     <col min="6" max="16384" width="11.453125" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A2" s="20" t="s">
         <v>104</v>
       </c>
@@ -15242,7 +15242,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A3" s="20" t="s">
         <v>114</v>
       </c>
@@ -15275,7 +15275,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A4" s="20" t="s">
         <v>114</v>
       </c>
@@ -15308,7 +15308,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A5" s="20" t="s">
         <v>114</v>
       </c>
@@ -15341,7 +15341,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A6" s="20" t="s">
         <v>114</v>
       </c>
@@ -15374,7 +15374,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A7" s="20" t="s">
         <v>114</v>
       </c>
@@ -15403,7 +15403,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A8" s="20" t="s">
         <v>114</v>
       </c>
@@ -15432,7 +15432,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A9" s="20" t="s">
         <v>114</v>
       </c>
@@ -15461,7 +15461,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A10" s="20" t="s">
         <v>114</v>
       </c>
@@ -15490,7 +15490,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A11" s="20" t="s">
         <v>114</v>
       </c>
@@ -15523,7 +15523,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A12" s="20" t="s">
         <v>114</v>
       </c>
@@ -15556,7 +15556,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A13" s="20" t="s">
         <v>114</v>
       </c>
@@ -15589,7 +15589,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A14" s="20" t="s">
         <v>114</v>
       </c>
@@ -15622,7 +15622,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A15" s="20" t="s">
         <v>114</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A16" s="20" t="s">
         <v>114</v>
       </c>
@@ -15688,7 +15688,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A17" s="20" t="s">
         <v>114</v>
       </c>
@@ -15717,7 +15717,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A18" s="20" t="s">
         <v>114</v>
       </c>
@@ -15746,7 +15746,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A19" s="20" t="s">
         <v>114</v>
       </c>
@@ -15775,7 +15775,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A20" s="20" t="s">
         <v>114</v>
       </c>
@@ -15804,7 +15804,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A21" s="20" t="s">
         <v>114</v>
       </c>
@@ -15837,7 +15837,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A22" s="20" t="s">
         <v>114</v>
       </c>
@@ -15870,7 +15870,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A23" s="20" t="s">
         <v>114</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A24" s="20" t="s">
         <v>114</v>
       </c>
@@ -15936,7 +15936,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A25" s="20" t="s">
         <v>114</v>
       </c>
@@ -15969,7 +15969,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A26" s="20" t="s">
         <v>114</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A27" s="20" t="s">
         <v>114</v>
       </c>
@@ -16031,7 +16031,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A28" s="20" t="s">
         <v>114</v>
       </c>
@@ -16060,7 +16060,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A29" s="20" t="s">
         <v>114</v>
       </c>
@@ -16089,7 +16089,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A30" s="20" t="s">
         <v>114</v>
       </c>
@@ -16118,7 +16118,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A31" s="20" t="s">
         <v>114</v>
       </c>
@@ -16151,7 +16151,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A32" s="20" t="s">
         <v>114</v>
       </c>
@@ -16184,7 +16184,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A33" s="20" t="s">
         <v>114</v>
       </c>
@@ -16217,7 +16217,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A34" s="20" t="s">
         <v>114</v>
       </c>
@@ -16250,7 +16250,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A35" s="20" t="s">
         <v>114</v>
       </c>
@@ -16283,7 +16283,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A36" s="20" t="s">
         <v>114</v>
       </c>
@@ -16316,7 +16316,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="37" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A37" s="20" t="s">
         <v>114</v>
       </c>
@@ -16345,7 +16345,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A38" s="20" t="s">
         <v>114</v>
       </c>
@@ -16374,7 +16374,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A39" s="20" t="s">
         <v>114</v>
       </c>
@@ -16403,7 +16403,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A40" s="20" t="s">
         <v>114</v>
       </c>
@@ -16432,7 +16432,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A41" s="20" t="s">
         <v>114</v>
       </c>
@@ -16465,7 +16465,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A42" s="20" t="s">
         <v>114</v>
       </c>
@@ -16498,7 +16498,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A43" s="20" t="s">
         <v>114</v>
       </c>
@@ -16528,7 +16528,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A44" s="20" t="s">
         <v>114</v>
       </c>
@@ -16633,7 +16633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A45" s="20" t="s">
         <v>114</v>
       </c>
@@ -16666,7 +16666,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A46" s="20" t="s">
         <v>114</v>
       </c>
@@ -16699,7 +16699,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="47" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A47" s="20" t="s">
         <v>114</v>
       </c>
@@ -16725,7 +16725,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:31" hidden="1" x14ac:dyDescent="0.75">
       <c r="A48" s="20" t="s">
         <v>114</v>
       </c>
@@ -16754,7 +16754,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A49" s="20" t="s">
         <v>114</v>
       </c>
@@ -16783,7 +16783,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A50" s="20" t="s">
         <v>114</v>
       </c>
@@ -16812,7 +16812,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A51" s="20" t="s">
         <v>114</v>
       </c>
@@ -16842,7 +16842,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A52" s="20" t="s">
         <v>114</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A53" s="20" t="s">
         <v>114</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A54" s="20" t="s">
         <v>114</v>
       </c>
@@ -16941,7 +16941,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A55" s="20" t="s">
         <v>114</v>
       </c>
@@ -16974,7 +16974,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A56" s="20" t="s">
         <v>114</v>
       </c>
@@ -17007,7 +17007,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A57" s="20" t="s">
         <v>114</v>
       </c>
@@ -17036,7 +17036,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A58" s="20" t="s">
         <v>114</v>
       </c>
@@ -17065,7 +17065,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A59" s="20" t="s">
         <v>114</v>
       </c>
@@ -17094,7 +17094,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A60" s="20" t="s">
         <v>114</v>
       </c>
@@ -17123,7 +17123,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A61" s="20" t="s">
         <v>114</v>
       </c>
@@ -17156,7 +17156,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A62" s="20" t="s">
         <v>114</v>
       </c>
@@ -17189,7 +17189,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A63" s="20" t="s">
         <v>114</v>
       </c>
@@ -17222,7 +17222,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A64" s="20" t="s">
         <v>114</v>
       </c>
@@ -17255,7 +17255,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A65" s="20" t="s">
         <v>114</v>
       </c>
@@ -17288,7 +17288,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A66" s="20" t="s">
         <v>114</v>
       </c>
@@ -17321,7 +17321,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A67" s="20" t="s">
         <v>114</v>
       </c>
@@ -17350,7 +17350,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A68" s="20" t="s">
         <v>114</v>
       </c>
@@ -17379,7 +17379,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A69" s="20" t="s">
         <v>114</v>
       </c>
@@ -17408,7 +17408,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A70" s="20" t="s">
         <v>114</v>
       </c>
@@ -17437,7 +17437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A71" s="20" t="s">
         <v>114</v>
       </c>
@@ -17470,7 +17470,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A72" s="20" t="s">
         <v>114</v>
       </c>
@@ -17503,7 +17503,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A73" s="20" t="s">
         <v>114</v>
       </c>
@@ -17536,7 +17536,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A74" s="20" t="s">
         <v>114</v>
       </c>
@@ -17569,7 +17569,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A75" s="20" t="s">
         <v>114</v>
       </c>
@@ -17602,7 +17602,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A76" s="20" t="s">
         <v>114</v>
       </c>
@@ -17635,7 +17635,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A77" s="20" t="s">
         <v>114</v>
       </c>
@@ -17664,7 +17664,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A78" s="20" t="s">
         <v>114</v>
       </c>
@@ -17693,7 +17693,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A79" s="20" t="s">
         <v>114</v>
       </c>
@@ -17722,7 +17722,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A80" s="20" t="s">
         <v>114</v>
       </c>
@@ -17751,7 +17751,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A81" s="20" t="s">
         <v>114</v>
       </c>
@@ -17784,7 +17784,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A82" s="20" t="s">
         <v>114</v>
       </c>
@@ -17817,7 +17817,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A83" s="20" t="s">
         <v>114</v>
       </c>
@@ -17846,7 +17846,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A84" s="20" t="s">
         <v>114</v>
       </c>
@@ -17875,7 +17875,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A85" s="20" t="s">
         <v>114</v>
       </c>
@@ -17904,7 +17904,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A86" s="20" t="s">
         <v>114</v>
       </c>
@@ -17933,7 +17933,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A87" s="20" t="s">
         <v>114</v>
       </c>
@@ -17962,7 +17962,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A88" s="20" t="s">
         <v>114</v>
       </c>
@@ -17995,7 +17995,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A89" s="20" t="s">
         <v>114</v>
       </c>
@@ -18028,7 +18028,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A90" s="20" t="s">
         <v>114</v>
       </c>
@@ -18061,7 +18061,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A91" s="20" t="s">
         <v>114</v>
       </c>
@@ -18094,7 +18094,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A92" s="20" t="s">
         <v>114</v>
       </c>
@@ -18127,7 +18127,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A93" s="20" t="s">
         <v>114</v>
       </c>
@@ -18156,7 +18156,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A94" s="20" t="s">
         <v>114</v>
       </c>
@@ -18185,7 +18185,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A95" s="20" t="s">
         <v>114</v>
       </c>
@@ -18214,7 +18214,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A96" s="20" t="s">
         <v>114</v>
       </c>
@@ -18243,7 +18243,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A97" s="20" t="s">
         <v>114</v>
       </c>
@@ -18272,7 +18272,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A98" s="20" t="s">
         <v>114</v>
       </c>
@@ -18301,7 +18301,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A99" s="20" t="s">
         <v>114</v>
       </c>
@@ -18330,7 +18330,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A100" s="20" t="s">
         <v>114</v>
       </c>
@@ -18359,7 +18359,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A101" s="20" t="s">
         <v>114</v>
       </c>
@@ -18388,7 +18388,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A102" s="20" t="s">
         <v>114</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A103" s="20" t="s">
         <v>114</v>
       </c>
@@ -18446,7 +18446,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A104" s="20" t="s">
         <v>114</v>
       </c>
@@ -18475,7 +18475,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A105" s="20" t="s">
         <v>114</v>
       </c>
@@ -18504,7 +18504,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A106" s="20" t="s">
         <v>114</v>
       </c>
@@ -18533,7 +18533,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A107" s="20" t="s">
         <v>114</v>
       </c>
@@ -18562,7 +18562,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A108" s="20" t="s">
         <v>114</v>
       </c>
@@ -18591,7 +18591,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A109" s="20" t="s">
         <v>114</v>
       </c>
@@ -18620,7 +18620,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A110" s="20" t="s">
         <v>114</v>
       </c>
@@ -18649,7 +18649,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A111" s="20" t="s">
         <v>114</v>
       </c>
@@ -18678,7 +18678,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A112" s="20" t="s">
         <v>114</v>
       </c>
@@ -18707,7 +18707,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A113" s="20" t="s">
         <v>114</v>
       </c>
@@ -18736,7 +18736,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A114" s="20" t="s">
         <v>114</v>
       </c>
@@ -18765,7 +18765,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A115" s="20" t="s">
         <v>114</v>
       </c>
@@ -18794,7 +18794,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A116" s="20" t="s">
         <v>114</v>
       </c>
@@ -18823,7 +18823,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A117" s="20" t="s">
         <v>114</v>
       </c>
@@ -18852,7 +18852,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A118" s="20" t="s">
         <v>114</v>
       </c>
@@ -18881,7 +18881,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A119" s="20" t="s">
         <v>114</v>
       </c>
@@ -18910,7 +18910,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A120" s="20" t="s">
         <v>114</v>
       </c>
@@ -18939,7 +18939,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A121" s="20" t="s">
         <v>114</v>
       </c>
@@ -18968,7 +18968,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A122" s="20" t="s">
         <v>114</v>
       </c>
@@ -18997,7 +18997,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A123" s="20" t="s">
         <v>114</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A124" s="20" t="s">
         <v>114</v>
       </c>
@@ -19055,7 +19055,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A125" s="20" t="s">
         <v>114</v>
       </c>
@@ -19084,7 +19084,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A126" s="20" t="s">
         <v>114</v>
       </c>
@@ -19113,7 +19113,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A127" s="20" t="s">
         <v>114</v>
       </c>
@@ -19142,7 +19142,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A128" s="20" t="s">
         <v>114</v>
       </c>
@@ -19171,7 +19171,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A129" s="20" t="s">
         <v>114</v>
       </c>
@@ -19200,7 +19200,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A130" s="20" t="s">
         <v>114</v>
       </c>
@@ -19229,7 +19229,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A131" s="20" t="s">
         <v>114</v>
       </c>
@@ -19258,7 +19258,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A132" s="20" t="s">
         <v>114</v>
       </c>
@@ -19287,7 +19287,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A133" s="20" t="s">
         <v>114</v>
       </c>
@@ -19316,7 +19316,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A134" s="20" t="s">
         <v>114</v>
       </c>
@@ -19345,7 +19345,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A135" s="20" t="s">
         <v>114</v>
       </c>
@@ -19374,7 +19374,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A136" s="20" t="s">
         <v>114</v>
       </c>
@@ -19403,7 +19403,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A137" s="20" t="s">
         <v>114</v>
       </c>
@@ -19432,7 +19432,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A138" s="20" t="s">
         <v>114</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A139" s="20" t="s">
         <v>114</v>
       </c>
@@ -19490,7 +19490,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A140" s="20" t="s">
         <v>114</v>
       </c>
@@ -19519,7 +19519,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A141" s="20" t="s">
         <v>114</v>
       </c>
@@ -19548,7 +19548,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A142" s="20" t="s">
         <v>114</v>
       </c>
@@ -19577,7 +19577,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A143" s="20" t="s">
         <v>114</v>
       </c>
@@ -19606,7 +19606,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A144" s="20" t="s">
         <v>114</v>
       </c>
@@ -19635,7 +19635,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A145" s="20" t="s">
         <v>114</v>
       </c>
@@ -19664,7 +19664,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A146" s="20" t="s">
         <v>114</v>
       </c>
@@ -19693,7 +19693,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A147" s="20" t="s">
         <v>114</v>
       </c>
@@ -19722,7 +19722,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A148" s="20" t="s">
         <v>114</v>
       </c>
@@ -19751,7 +19751,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A149" s="20" t="s">
         <v>114</v>
       </c>
@@ -19780,7 +19780,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A150" s="20" t="s">
         <v>114</v>
       </c>
@@ -19809,7 +19809,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A151" s="20" t="s">
         <v>114</v>
       </c>
@@ -19838,7 +19838,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A152" s="20" t="s">
         <v>114</v>
       </c>
@@ -19867,7 +19867,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A153" s="20" t="s">
         <v>114</v>
       </c>
@@ -19900,7 +19900,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A154" s="20" t="s">
         <v>114</v>
       </c>
@@ -19933,7 +19933,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A155" s="20" t="s">
         <v>114</v>
       </c>
@@ -19962,7 +19962,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A156" s="20" t="s">
         <v>114</v>
       </c>
@@ -19991,7 +19991,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A157" s="20" t="s">
         <v>114</v>
       </c>
@@ -20020,7 +20020,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A158" s="20" t="s">
         <v>114</v>
       </c>
@@ -20049,7 +20049,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A159" s="20" t="s">
         <v>114</v>
       </c>
@@ -20082,7 +20082,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A160" s="20" t="s">
         <v>114</v>
       </c>
@@ -20115,7 +20115,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A161" s="20" t="s">
         <v>114</v>
       </c>
@@ -20148,7 +20148,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A162" s="20" t="s">
         <v>114</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A163" s="20" t="s">
         <v>114</v>
       </c>
@@ -20214,7 +20214,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A164" s="20" t="s">
         <v>114</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A165" s="20" t="s">
         <v>114</v>
       </c>
@@ -20276,7 +20276,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A166" s="20" t="s">
         <v>114</v>
       </c>
@@ -20305,7 +20305,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A167" s="20" t="s">
         <v>114</v>
       </c>
@@ -20334,7 +20334,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A168" s="20" t="s">
         <v>114</v>
       </c>
@@ -20363,7 +20363,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A169" s="20" t="s">
         <v>114</v>
       </c>
@@ -20396,7 +20396,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A170" s="20" t="s">
         <v>114</v>
       </c>
@@ -20429,7 +20429,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A171" s="20" t="s">
         <v>114</v>
       </c>
@@ -20462,7 +20462,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A172" s="20" t="s">
         <v>114</v>
       </c>
@@ -20495,7 +20495,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A173" s="20" t="s">
         <v>114</v>
       </c>
@@ -20528,7 +20528,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A174" s="20" t="s">
         <v>114</v>
       </c>
@@ -20561,7 +20561,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A175" s="20" t="s">
         <v>114</v>
       </c>
@@ -20590,7 +20590,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A176" s="20" t="s">
         <v>114</v>
       </c>
@@ -20619,7 +20619,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A177" s="20" t="s">
         <v>114</v>
       </c>
@@ -20648,7 +20648,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A178" s="20" t="s">
         <v>114</v>
       </c>
@@ -20677,7 +20677,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A179" s="20" t="s">
         <v>114</v>
       </c>
@@ -20710,7 +20710,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A180" s="20" t="s">
         <v>114</v>
       </c>
@@ -20743,7 +20743,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A181" s="20" t="s">
         <v>114</v>
       </c>
@@ -20776,7 +20776,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A182" s="20" t="s">
         <v>114</v>
       </c>
@@ -20809,7 +20809,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A183" s="20" t="s">
         <v>114</v>
       </c>
@@ -20842,7 +20842,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A184" s="20" t="s">
         <v>114</v>
       </c>
@@ -20875,7 +20875,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A185" s="20" t="s">
         <v>114</v>
       </c>
@@ -20904,7 +20904,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A186" s="20" t="s">
         <v>114</v>
       </c>
@@ -20933,7 +20933,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A187" s="20" t="s">
         <v>114</v>
       </c>
@@ -20962,7 +20962,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A188" s="20" t="s">
         <v>114</v>
       </c>
@@ -20991,7 +20991,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A189" s="20" t="s">
         <v>114</v>
       </c>
@@ -21024,7 +21024,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A190" s="20" t="s">
         <v>114</v>
       </c>
@@ -21057,7 +21057,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A191" s="20" t="s">
         <v>114</v>
       </c>
@@ -21090,7 +21090,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A192" s="20" t="s">
         <v>114</v>
       </c>
@@ -21123,7 +21123,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A193" s="20" t="s">
         <v>114</v>
       </c>
@@ -21156,7 +21156,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A194" s="20" t="s">
         <v>114</v>
       </c>
@@ -21189,7 +21189,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A195" s="20" t="s">
         <v>114</v>
       </c>
@@ -21215,7 +21215,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A196" s="20" t="s">
         <v>114</v>
       </c>
@@ -21244,7 +21244,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A197" s="20" t="s">
         <v>114</v>
       </c>
@@ -21273,7 +21273,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A198" s="20" t="s">
         <v>114</v>
       </c>
@@ -21302,7 +21302,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A199" s="20" t="s">
         <v>114</v>
       </c>
@@ -21332,7 +21332,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A200" s="20" t="s">
         <v>114</v>
       </c>
@@ -21365,7 +21365,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A201" s="20" t="s">
         <v>114</v>
       </c>
@@ -21398,7 +21398,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A202" s="20" t="s">
         <v>114</v>
       </c>
@@ -21431,7 +21431,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A203" s="20" t="s">
         <v>114</v>
       </c>
@@ -21464,7 +21464,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A204" s="20" t="s">
         <v>114</v>
       </c>
@@ -21497,7 +21497,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A205" s="20" t="s">
         <v>114</v>
       </c>
@@ -21526,7 +21526,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A206" s="20" t="s">
         <v>114</v>
       </c>
@@ -21555,7 +21555,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A207" s="20" t="s">
         <v>114</v>
       </c>
@@ -21584,7 +21584,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A208" s="20" t="s">
         <v>114</v>
       </c>
@@ -21613,7 +21613,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A209" s="20" t="s">
         <v>114</v>
       </c>
@@ -21646,7 +21646,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A210" s="20" t="s">
         <v>114</v>
       </c>
@@ -21679,7 +21679,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A211" s="20" t="s">
         <v>114</v>
       </c>
@@ -21712,7 +21712,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A212" s="20" t="s">
         <v>114</v>
       </c>
@@ -21745,7 +21745,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A213" s="20" t="s">
         <v>114</v>
       </c>
@@ -21778,7 +21778,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A214" s="20" t="s">
         <v>114</v>
       </c>
@@ -21811,7 +21811,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A215" s="20" t="s">
         <v>114</v>
       </c>
@@ -21840,7 +21840,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A216" s="20" t="s">
         <v>114</v>
       </c>
@@ -21869,7 +21869,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A217" s="20" t="s">
         <v>114</v>
       </c>
@@ -21898,7 +21898,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A218" s="20" t="s">
         <v>114</v>
       </c>
@@ -21927,7 +21927,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A219" s="20" t="s">
         <v>114</v>
       </c>
@@ -21960,7 +21960,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A220" s="20" t="s">
         <v>114</v>
       </c>
@@ -21993,7 +21993,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A221" s="20" t="s">
         <v>114</v>
       </c>
@@ -22026,7 +22026,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A222" s="20" t="s">
         <v>114</v>
       </c>
@@ -22059,7 +22059,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A223" s="20" t="s">
         <v>114</v>
       </c>
@@ -22092,7 +22092,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A224" s="20" t="s">
         <v>114</v>
       </c>
@@ -22125,7 +22125,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A225" s="20" t="s">
         <v>114</v>
       </c>
@@ -22154,7 +22154,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A226" s="20" t="s">
         <v>114</v>
       </c>
@@ -22183,7 +22183,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A227" s="20" t="s">
         <v>114</v>
       </c>
@@ -22212,7 +22212,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A228" s="20" t="s">
         <v>114</v>
       </c>
@@ -22241,7 +22241,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A229" s="20" t="s">
         <v>114</v>
       </c>
@@ -22274,7 +22274,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A230" s="20" t="s">
         <v>114</v>
       </c>
@@ -22307,7 +22307,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A231" s="20" t="s">
         <v>114</v>
       </c>
@@ -22340,7 +22340,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A232" s="20" t="s">
         <v>114</v>
       </c>
@@ -22373,7 +22373,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A233" s="20" t="s">
         <v>114</v>
       </c>
@@ -22402,7 +22402,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A234" s="20" t="s">
         <v>114</v>
       </c>
@@ -22431,7 +22431,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A235" s="20" t="s">
         <v>114</v>
       </c>
@@ -22460,7 +22460,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A236" s="20" t="s">
         <v>114</v>
       </c>
@@ -22489,7 +22489,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A237" s="20" t="s">
         <v>114</v>
       </c>
@@ -22518,7 +22518,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A238" s="20" t="s">
         <v>114</v>
       </c>
@@ -22551,7 +22551,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A239" s="20" t="s">
         <v>114</v>
       </c>
@@ -22584,7 +22584,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A240" s="20" t="s">
         <v>114</v>
       </c>
@@ -22617,7 +22617,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A241" s="20" t="s">
         <v>114</v>
       </c>
@@ -22650,7 +22650,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A242" s="20" t="s">
         <v>114</v>
       </c>
@@ -22683,7 +22683,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A243" s="20" t="s">
         <v>114</v>
       </c>
@@ -22712,7 +22712,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A244" s="20" t="s">
         <v>114</v>
       </c>
@@ -22741,7 +22741,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A245" s="20" t="s">
         <v>114</v>
       </c>
@@ -22770,7 +22770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A246" s="20" t="s">
         <v>114</v>
       </c>
@@ -22799,7 +22799,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A247" s="20" t="s">
         <v>114</v>
       </c>
@@ -22828,7 +22828,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A248" s="20" t="s">
         <v>114</v>
       </c>
@@ -22857,7 +22857,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A249" s="20" t="s">
         <v>114</v>
       </c>
@@ -22886,7 +22886,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A250" s="20" t="s">
         <v>114</v>
       </c>
@@ -22915,7 +22915,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A251" s="20" t="s">
         <v>114</v>
       </c>
@@ -22944,7 +22944,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A252" s="20" t="s">
         <v>114</v>
       </c>
@@ -22973,7 +22973,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A253" s="20" t="s">
         <v>114</v>
       </c>
@@ -23002,7 +23002,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A254" s="20" t="s">
         <v>114</v>
       </c>
@@ -23031,7 +23031,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A255" s="20" t="s">
         <v>114</v>
       </c>
@@ -23060,7 +23060,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A256" s="20" t="s">
         <v>114</v>
       </c>
@@ -23089,7 +23089,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A257" s="20" t="s">
         <v>114</v>
       </c>
@@ -23118,7 +23118,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A258" s="20" t="s">
         <v>114</v>
       </c>
@@ -23147,7 +23147,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A259" s="20" t="s">
         <v>114</v>
       </c>
@@ -23176,7 +23176,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A260" s="20" t="s">
         <v>114</v>
       </c>
@@ -23205,7 +23205,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A261" s="20" t="s">
         <v>114</v>
       </c>
@@ -23234,7 +23234,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A262" s="20" t="s">
         <v>114</v>
       </c>
@@ -23263,7 +23263,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A263" s="20" t="s">
         <v>114</v>
       </c>
@@ -23292,7 +23292,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A264" s="20" t="s">
         <v>114</v>
       </c>
@@ -23321,7 +23321,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A265" s="20" t="s">
         <v>114</v>
       </c>
@@ -23350,7 +23350,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A266" s="20" t="s">
         <v>114</v>
       </c>
@@ -23379,7 +23379,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A267" s="20" t="s">
         <v>114</v>
       </c>
@@ -23408,7 +23408,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A268" s="20" t="s">
         <v>114</v>
       </c>
@@ -23437,7 +23437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A269" s="20" t="s">
         <v>114</v>
       </c>
@@ -23466,7 +23466,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A270" s="20" t="s">
         <v>114</v>
       </c>
@@ -23495,7 +23495,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A271" s="20" t="s">
         <v>114</v>
       </c>
@@ -23524,7 +23524,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A272" s="20" t="s">
         <v>114</v>
       </c>
@@ -23553,7 +23553,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A273" s="20" t="s">
         <v>114</v>
       </c>
@@ -23582,7 +23582,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A274" s="20" t="s">
         <v>114</v>
       </c>
@@ -23611,7 +23611,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A275" s="20" t="s">
         <v>114</v>
       </c>
@@ -23640,7 +23640,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A276" s="20" t="s">
         <v>114</v>
       </c>
@@ -23669,7 +23669,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A277" s="20" t="s">
         <v>114</v>
       </c>
@@ -23698,7 +23698,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A278" s="20" t="s">
         <v>114</v>
       </c>
@@ -23727,7 +23727,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A279" s="20" t="s">
         <v>114</v>
       </c>
@@ -23756,7 +23756,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A280" s="20" t="s">
         <v>114</v>
       </c>
@@ -23785,7 +23785,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A281" s="20" t="s">
         <v>114</v>
       </c>
@@ -23814,7 +23814,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A282" s="20" t="s">
         <v>114</v>
       </c>
@@ -23843,7 +23843,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A283" s="20" t="s">
         <v>114</v>
       </c>
@@ -23872,7 +23872,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A284" s="20" t="s">
         <v>114</v>
       </c>
@@ -23901,7 +23901,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A285" s="20" t="s">
         <v>114</v>
       </c>
@@ -23930,7 +23930,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A286" s="20" t="s">
         <v>114</v>
       </c>
@@ -23959,7 +23959,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A287" s="20" t="s">
         <v>114</v>
       </c>
@@ -23988,7 +23988,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A288" s="20" t="s">
         <v>114</v>
       </c>
@@ -24017,7 +24017,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A289" s="20" t="s">
         <v>114</v>
       </c>
@@ -24046,7 +24046,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A290" s="20" t="s">
         <v>114</v>
       </c>
@@ -24075,7 +24075,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A291" s="20" t="s">
         <v>114</v>
       </c>
@@ -24104,7 +24104,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A292" s="20" t="s">
         <v>114</v>
       </c>
@@ -24133,7 +24133,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A293" s="20" t="s">
         <v>114</v>
       </c>
@@ -24162,7 +24162,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A294" s="20" t="s">
         <v>114</v>
       </c>
@@ -24191,7 +24191,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A295" s="20" t="s">
         <v>114</v>
       </c>
@@ -24220,7 +24220,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A296" s="20" t="s">
         <v>114</v>
       </c>
@@ -24249,7 +24249,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A297" s="20" t="s">
         <v>114</v>
       </c>
@@ -24278,7 +24278,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A298" s="20" t="s">
         <v>114</v>
       </c>
@@ -24307,7 +24307,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A299" s="20" t="s">
         <v>114</v>
       </c>
@@ -24336,7 +24336,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A300" s="20" t="s">
         <v>114</v>
       </c>
@@ -24365,7 +24365,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A301" s="20" t="s">
         <v>114</v>
       </c>
@@ -24394,7 +24394,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A302" s="20" t="s">
         <v>114</v>
       </c>
@@ -24423,7 +24423,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A303" s="20" t="s">
         <v>114</v>
       </c>
@@ -24452,7 +24452,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A304" s="20" t="s">
         <v>114</v>
       </c>
@@ -24481,7 +24481,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A305" s="20" t="s">
         <v>114</v>
       </c>
@@ -24510,7 +24510,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A306" s="20" t="s">
         <v>114</v>
       </c>
@@ -24539,7 +24539,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A307" s="20" t="s">
         <v>114</v>
       </c>
@@ -24572,7 +24572,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A308" s="20" t="s">
         <v>114</v>
       </c>
@@ -24605,7 +24605,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A309" s="20" t="s">
         <v>114</v>
       </c>
@@ -24638,7 +24638,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A310" s="20" t="s">
         <v>114</v>
       </c>
@@ -24671,7 +24671,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A311" s="20" t="s">
         <v>114</v>
       </c>
@@ -24700,7 +24700,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A312" s="20" t="s">
         <v>114</v>
       </c>
@@ -24729,7 +24729,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A313" s="20" t="s">
         <v>114</v>
       </c>
@@ -24758,7 +24758,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A314" s="20" t="s">
         <v>114</v>
       </c>
@@ -24787,7 +24787,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A315" s="20" t="s">
         <v>114</v>
       </c>
@@ -24816,7 +24816,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A316" s="20" t="s">
         <v>114</v>
       </c>
@@ -24845,7 +24845,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A317" s="20" t="s">
         <v>114</v>
       </c>
@@ -24878,7 +24878,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A318" s="20" t="s">
         <v>114</v>
       </c>
@@ -24911,7 +24911,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A319" s="20" t="s">
         <v>114</v>
       </c>
@@ -24944,7 +24944,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A320" s="20" t="s">
         <v>114</v>
       </c>
@@ -24977,7 +24977,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A321" s="20" t="s">
         <v>114</v>
       </c>
@@ -25006,7 +25006,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A322" s="20" t="s">
         <v>114</v>
       </c>
@@ -25035,7 +25035,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A323" s="20" t="s">
         <v>114</v>
       </c>
@@ -25064,7 +25064,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A324" s="20" t="s">
         <v>114</v>
       </c>
@@ -25093,7 +25093,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A325" s="20" t="s">
         <v>114</v>
       </c>
@@ -25122,7 +25122,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A326" s="20" t="s">
         <v>114</v>
       </c>
@@ -25151,7 +25151,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A327" s="20" t="s">
         <v>114</v>
       </c>
@@ -25184,7 +25184,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A328" s="20" t="s">
         <v>114</v>
       </c>
@@ -25217,7 +25217,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A329" s="20" t="s">
         <v>114</v>
       </c>
@@ -25250,7 +25250,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A330" s="20" t="s">
         <v>114</v>
       </c>
@@ -25283,7 +25283,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A331" s="20" t="s">
         <v>114</v>
       </c>
@@ -25312,7 +25312,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A332" s="20" t="s">
         <v>114</v>
       </c>
@@ -25341,7 +25341,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A333" s="20" t="s">
         <v>114</v>
       </c>
@@ -25370,7 +25370,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A334" s="20" t="s">
         <v>114</v>
       </c>
@@ -25399,7 +25399,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A335" s="20" t="s">
         <v>114</v>
       </c>
@@ -25428,7 +25428,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A336" s="20" t="s">
         <v>114</v>
       </c>
@@ -25457,7 +25457,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A337" s="20" t="s">
         <v>114</v>
       </c>
@@ -25490,7 +25490,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A338" s="20" t="s">
         <v>114</v>
       </c>
@@ -25523,7 +25523,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A339" s="20" t="s">
         <v>114</v>
       </c>
@@ -25556,7 +25556,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A340" s="20" t="s">
         <v>114</v>
       </c>
@@ -25589,7 +25589,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A341" s="20" t="s">
         <v>114</v>
       </c>
@@ -25618,7 +25618,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A342" s="20" t="s">
         <v>114</v>
       </c>
@@ -25647,7 +25647,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A343" s="20" t="s">
         <v>114</v>
       </c>
@@ -25673,7 +25673,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A344" s="20" t="s">
         <v>114</v>
       </c>
@@ -25702,7 +25702,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A345" s="20" t="s">
         <v>114</v>
       </c>
@@ -25731,7 +25731,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A346" s="20" t="s">
         <v>114</v>
       </c>
@@ -25760,7 +25760,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A347" s="20" t="s">
         <v>114</v>
       </c>
@@ -25790,7 +25790,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A348" s="20" t="s">
         <v>114</v>
       </c>
@@ -25823,7 +25823,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A349" s="20" t="s">
         <v>114</v>
       </c>
@@ -25856,7 +25856,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A350" s="20" t="s">
         <v>114</v>
       </c>
@@ -25889,7 +25889,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A351" s="20" t="s">
         <v>114</v>
       </c>
@@ -25915,7 +25915,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A352" s="20" t="s">
         <v>114</v>
       </c>
@@ -25944,7 +25944,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A353" s="20" t="s">
         <v>114</v>
       </c>
@@ -25973,7 +25973,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A354" s="20" t="s">
         <v>114</v>
       </c>
@@ -26002,7 +26002,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A355" s="20" t="s">
         <v>114</v>
       </c>
@@ -26031,7 +26031,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A356" s="20" t="s">
         <v>114</v>
       </c>
@@ -26060,7 +26060,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A357" s="20" t="s">
         <v>114</v>
       </c>
@@ -26093,7 +26093,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A358" s="20" t="s">
         <v>114</v>
       </c>
@@ -26126,7 +26126,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A359" s="20" t="s">
         <v>114</v>
       </c>
@@ -26159,7 +26159,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A360" s="20" t="s">
         <v>114</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A361" s="20" t="s">
         <v>114</v>
       </c>
@@ -26221,7 +26221,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A362" s="20" t="s">
         <v>114</v>
       </c>
@@ -26250,7 +26250,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A363" s="20" t="s">
         <v>114</v>
       </c>
@@ -26279,7 +26279,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A364" s="20" t="s">
         <v>114</v>
       </c>
@@ -26308,7 +26308,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A365" s="20" t="s">
         <v>114</v>
       </c>
@@ -26337,7 +26337,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A366" s="20" t="s">
         <v>114</v>
       </c>
@@ -26366,7 +26366,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A367" s="20" t="s">
         <v>114</v>
       </c>
@@ -26399,7 +26399,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A368" s="20" t="s">
         <v>114</v>
       </c>
@@ -26432,7 +26432,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A369" s="20" t="s">
         <v>114</v>
       </c>
@@ -26465,7 +26465,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A370" s="20" t="s">
         <v>114</v>
       </c>
@@ -26498,7 +26498,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A371" s="20" t="s">
         <v>114</v>
       </c>
@@ -26527,7 +26527,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A372" s="20" t="s">
         <v>114</v>
       </c>
@@ -26556,7 +26556,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A373" s="20" t="s">
         <v>114</v>
       </c>
@@ -26585,7 +26585,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A374" s="20" t="s">
         <v>114</v>
       </c>
@@ -26614,7 +26614,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A375" s="20" t="s">
         <v>114</v>
       </c>
@@ -26643,7 +26643,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A376" s="20" t="s">
         <v>114</v>
       </c>
@@ -26672,7 +26672,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A377" s="20" t="s">
         <v>114</v>
       </c>
@@ -26705,7 +26705,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A378" s="20" t="s">
         <v>114</v>
       </c>
@@ -26738,7 +26738,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A379" s="20" t="s">
         <v>114</v>
       </c>
@@ -26771,7 +26771,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A380" s="20" t="s">
         <v>114</v>
       </c>
@@ -26804,7 +26804,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A381" s="20" t="s">
         <v>114</v>
       </c>
@@ -26833,7 +26833,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A382" s="20" t="s">
         <v>114</v>
       </c>
@@ -26862,7 +26862,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A383" s="20" t="s">
         <v>114</v>
       </c>
@@ -26891,7 +26891,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A384" s="20" t="s">
         <v>114</v>
       </c>
@@ -26920,7 +26920,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A385" s="20" t="s">
         <v>114</v>
       </c>
@@ -26949,7 +26949,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A386" s="20" t="s">
         <v>114</v>
       </c>
@@ -26978,7 +26978,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A387" s="20" t="s">
         <v>114</v>
       </c>
@@ -27007,7 +27007,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A388" s="20" t="s">
         <v>114</v>
       </c>
@@ -27040,7 +27040,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A389" s="20" t="s">
         <v>114</v>
       </c>
@@ -27073,7 +27073,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A390" s="20" t="s">
         <v>114</v>
       </c>
@@ -27106,7 +27106,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A391" s="20" t="s">
         <v>114</v>
       </c>
@@ -27139,7 +27139,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A392" s="20" t="s">
         <v>114</v>
       </c>
@@ -27172,7 +27172,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A393" s="20" t="s">
         <v>114</v>
       </c>
@@ -27201,7 +27201,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A394" s="20" t="s">
         <v>114</v>
       </c>
@@ -27230,7 +27230,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A395" s="20" t="s">
         <v>114</v>
       </c>
@@ -27259,7 +27259,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A396" s="20" t="s">
         <v>114</v>
       </c>
@@ -27288,7 +27288,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A397" s="20" t="s">
         <v>114</v>
       </c>
@@ -27317,7 +27317,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A398" s="20" t="s">
         <v>114</v>
       </c>
@@ -27346,7 +27346,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A399" s="20" t="s">
         <v>114</v>
       </c>
@@ -27375,7 +27375,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A400" s="20" t="s">
         <v>114</v>
       </c>
@@ -27404,7 +27404,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A401" s="20" t="s">
         <v>114</v>
       </c>
@@ -27433,7 +27433,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A402" s="20" t="s">
         <v>114</v>
       </c>
@@ -27462,7 +27462,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A403" s="20" t="s">
         <v>114</v>
       </c>
@@ -27491,7 +27491,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A404" s="20" t="s">
         <v>114</v>
       </c>
@@ -27520,7 +27520,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A405" s="20" t="s">
         <v>114</v>
       </c>
@@ -27549,7 +27549,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A406" s="20" t="s">
         <v>114</v>
       </c>
@@ -27578,7 +27578,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A407" s="20" t="s">
         <v>114</v>
       </c>
@@ -27607,7 +27607,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A408" s="20" t="s">
         <v>114</v>
       </c>
@@ -27636,7 +27636,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A409" s="20" t="s">
         <v>114</v>
       </c>
@@ -27665,7 +27665,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A410" s="20" t="s">
         <v>114</v>
       </c>
@@ -27694,7 +27694,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A411" s="20" t="s">
         <v>114</v>
       </c>
@@ -27723,7 +27723,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A412" s="20" t="s">
         <v>114</v>
       </c>
@@ -27752,7 +27752,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A413" s="20" t="s">
         <v>114</v>
       </c>
@@ -27781,7 +27781,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A414" s="20" t="s">
         <v>114</v>
       </c>
@@ -27810,7 +27810,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A415" s="20" t="s">
         <v>114</v>
       </c>
@@ -27839,7 +27839,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A416" s="20" t="s">
         <v>114</v>
       </c>
@@ -27868,7 +27868,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A417" s="20" t="s">
         <v>114</v>
       </c>
@@ -27897,7 +27897,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A418" s="20" t="s">
         <v>114</v>
       </c>
@@ -27926,7 +27926,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A419" s="20" t="s">
         <v>114</v>
       </c>
@@ -27955,7 +27955,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A420" s="20" t="s">
         <v>114</v>
       </c>
@@ -27984,7 +27984,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A421" s="20" t="s">
         <v>114</v>
       </c>
@@ -28013,7 +28013,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A422" s="20" t="s">
         <v>114</v>
       </c>
@@ -28042,7 +28042,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A423" s="20" t="s">
         <v>114</v>
       </c>
@@ -28071,7 +28071,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A424" s="20" t="s">
         <v>114</v>
       </c>
@@ -28100,7 +28100,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A425" s="20" t="s">
         <v>114</v>
       </c>
@@ -28129,7 +28129,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A426" s="20" t="s">
         <v>114</v>
       </c>
@@ -28158,7 +28158,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A427" s="20" t="s">
         <v>114</v>
       </c>
@@ -28187,7 +28187,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A428" s="20" t="s">
         <v>114</v>
       </c>
@@ -28216,7 +28216,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A429" s="20" t="s">
         <v>114</v>
       </c>
@@ -28245,7 +28245,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A430" s="20" t="s">
         <v>114</v>
       </c>
@@ -28274,7 +28274,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A431" s="20" t="s">
         <v>114</v>
       </c>
@@ -28303,7 +28303,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A432" s="20" t="s">
         <v>114</v>
       </c>
@@ -28332,7 +28332,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A433" s="20" t="s">
         <v>114</v>
       </c>
@@ -28361,7 +28361,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A434" s="20" t="s">
         <v>114</v>
       </c>
@@ -28390,7 +28390,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A435" s="20" t="s">
         <v>114</v>
       </c>
@@ -28419,7 +28419,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A436" s="20" t="s">
         <v>114</v>
       </c>
@@ -28448,7 +28448,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A437" s="20" t="s">
         <v>114</v>
       </c>
@@ -28477,7 +28477,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A438" s="20" t="s">
         <v>114</v>
       </c>
@@ -28506,7 +28506,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A439" s="20" t="s">
         <v>114</v>
       </c>
@@ -28535,7 +28535,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A440" s="20" t="s">
         <v>114</v>
       </c>
@@ -28564,7 +28564,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A441" s="20" t="s">
         <v>114</v>
       </c>
@@ -28593,7 +28593,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A442" s="20" t="s">
         <v>114</v>
       </c>
@@ -28622,7 +28622,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A443" s="20" t="s">
         <v>114</v>
       </c>
@@ -28651,7 +28651,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A444" s="20" t="s">
         <v>114</v>
       </c>
@@ -28680,7 +28680,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A445" s="20" t="s">
         <v>114</v>
       </c>
@@ -28709,7 +28709,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A446" s="20" t="s">
         <v>114</v>
       </c>
@@ -28738,7 +28738,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A447" s="20" t="s">
         <v>114</v>
       </c>
@@ -28767,7 +28767,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A448" s="20" t="s">
         <v>114</v>
       </c>
@@ -28796,7 +28796,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A449" s="20" t="s">
         <v>114</v>
       </c>
@@ -28825,7 +28825,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A450" s="20" t="s">
         <v>114</v>
       </c>
@@ -28854,7 +28854,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A451" s="20" t="s">
         <v>114</v>
       </c>
@@ -28883,7 +28883,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A452" s="20" t="s">
         <v>114</v>
       </c>
@@ -28912,7 +28912,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A453" s="20" t="s">
         <v>114</v>
       </c>
@@ -28941,7 +28941,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A454" s="20" t="s">
         <v>114</v>
       </c>
@@ -28970,7 +28970,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A455" s="20" t="s">
         <v>114</v>
       </c>
@@ -29003,7 +29003,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A456" s="20" t="s">
         <v>114</v>
       </c>
@@ -29036,7 +29036,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A457" s="20" t="s">
         <v>114</v>
       </c>
@@ -29069,7 +29069,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A458" s="20" t="s">
         <v>114</v>
       </c>
@@ -29102,7 +29102,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A459" s="20" t="s">
         <v>114</v>
       </c>
@@ -29131,7 +29131,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A460" s="20" t="s">
         <v>114</v>
       </c>
@@ -29160,7 +29160,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A461" s="20" t="s">
         <v>114</v>
       </c>
@@ -29189,7 +29189,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A462" s="20" t="s">
         <v>114</v>
       </c>
@@ -29218,7 +29218,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A463" s="20" t="s">
         <v>114</v>
       </c>
@@ -29247,7 +29247,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A464" s="20" t="s">
         <v>114</v>
       </c>
@@ -29276,7 +29276,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A465" s="20" t="s">
         <v>114</v>
       </c>
@@ -29309,7 +29309,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A466" s="20" t="s">
         <v>114</v>
       </c>
@@ -29342,7 +29342,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A467" s="20" t="s">
         <v>114</v>
       </c>
@@ -29375,7 +29375,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A468" s="20" t="s">
         <v>114</v>
       </c>
@@ -29408,7 +29408,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A469" s="20" t="s">
         <v>114</v>
       </c>
@@ -29437,7 +29437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A470" s="20" t="s">
         <v>114</v>
       </c>
@@ -29466,7 +29466,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A471" s="20" t="s">
         <v>114</v>
       </c>
@@ -29495,7 +29495,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A472" s="20" t="s">
         <v>114</v>
       </c>
@@ -29524,7 +29524,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A473" s="20" t="s">
         <v>114</v>
       </c>
@@ -29553,7 +29553,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A474" s="20" t="s">
         <v>114</v>
       </c>
@@ -29582,7 +29582,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A475" s="20" t="s">
         <v>114</v>
       </c>
@@ -29615,7 +29615,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A476" s="20" t="s">
         <v>114</v>
       </c>
@@ -29648,7 +29648,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A477" s="20" t="s">
         <v>114</v>
       </c>
@@ -29681,7 +29681,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A478" s="20" t="s">
         <v>114</v>
       </c>
@@ -29714,7 +29714,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A479" s="20" t="s">
         <v>114</v>
       </c>
@@ -29743,7 +29743,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A480" s="20" t="s">
         <v>114</v>
       </c>
@@ -29772,7 +29772,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A481" s="20" t="s">
         <v>114</v>
       </c>
@@ -29801,7 +29801,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A482" s="20" t="s">
         <v>114</v>
       </c>
@@ -29830,7 +29830,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A483" s="20" t="s">
         <v>114</v>
       </c>
@@ -29859,7 +29859,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A484" s="20" t="s">
         <v>114</v>
       </c>
@@ -29888,7 +29888,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A485" s="20" t="s">
         <v>114</v>
       </c>
@@ -29921,7 +29921,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A486" s="20" t="s">
         <v>114</v>
       </c>
@@ -29954,7 +29954,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A487" s="20" t="s">
         <v>114</v>
       </c>
@@ -29987,7 +29987,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A488" s="20" t="s">
         <v>114</v>
       </c>
@@ -30020,7 +30020,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A489" s="20" t="s">
         <v>114</v>
       </c>
@@ -30049,7 +30049,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A490" s="20" t="s">
         <v>114</v>
       </c>
@@ -30078,7 +30078,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A491" s="20" t="s">
         <v>114</v>
       </c>
@@ -30107,7 +30107,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A492" s="20" t="s">
         <v>114</v>
       </c>
@@ -30136,7 +30136,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A493" s="20" t="s">
         <v>114</v>
       </c>
@@ -30165,7 +30165,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A494" s="20" t="s">
         <v>114</v>
       </c>
@@ -30194,7 +30194,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A495" s="20" t="s">
         <v>114</v>
       </c>
@@ -30224,7 +30224,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A496" s="20" t="s">
         <v>114</v>
       </c>
@@ -30257,7 +30257,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A497" s="20" t="s">
         <v>114</v>
       </c>
@@ -30290,7 +30290,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A498" s="20" t="s">
         <v>114</v>
       </c>
@@ -30323,7 +30323,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A499" s="20" t="s">
         <v>114</v>
       </c>
@@ -30349,7 +30349,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A500" s="20" t="s">
         <v>114</v>
       </c>
@@ -30378,7 +30378,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A501" s="20" t="s">
         <v>114</v>
       </c>
@@ -30407,7 +30407,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A502" s="20" t="s">
         <v>114</v>
       </c>
@@ -30436,7 +30436,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A503" s="20" t="s">
         <v>114</v>
       </c>
@@ -30465,7 +30465,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A504" s="20" t="s">
         <v>114</v>
       </c>
@@ -30494,7 +30494,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A505" s="20" t="s">
         <v>114</v>
       </c>
@@ -30527,7 +30527,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A506" s="20" t="s">
         <v>114</v>
       </c>
@@ -30560,7 +30560,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A507" s="20" t="s">
         <v>114</v>
       </c>
@@ -30593,7 +30593,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A508" s="20" t="s">
         <v>114</v>
       </c>
@@ -30626,7 +30626,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A509" s="20" t="s">
         <v>114</v>
       </c>
@@ -30655,7 +30655,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A510" s="20" t="s">
         <v>114</v>
       </c>
@@ -30684,7 +30684,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A511" s="20" t="s">
         <v>114</v>
       </c>
@@ -30713,7 +30713,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A512" s="20" t="s">
         <v>114</v>
       </c>
@@ -30742,7 +30742,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A513" s="20" t="s">
         <v>114</v>
       </c>
@@ -30771,7 +30771,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A514" s="20" t="s">
         <v>114</v>
       </c>
@@ -30800,7 +30800,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A515" s="20" t="s">
         <v>114</v>
       </c>
@@ -30833,7 +30833,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A516" s="20" t="s">
         <v>114</v>
       </c>
@@ -30866,7 +30866,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A517" s="20" t="s">
         <v>114</v>
       </c>
@@ -30899,7 +30899,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A518" s="20" t="s">
         <v>114</v>
       </c>
@@ -30932,7 +30932,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A519" s="20" t="s">
         <v>114</v>
       </c>
@@ -30961,7 +30961,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A520" s="20" t="s">
         <v>114</v>
       </c>
@@ -30990,7 +30990,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A521" s="20" t="s">
         <v>114</v>
       </c>
@@ -31019,7 +31019,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A522" s="20" t="s">
         <v>114</v>
       </c>
@@ -31048,7 +31048,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A523" s="20" t="s">
         <v>114</v>
       </c>
@@ -31077,7 +31077,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A524" s="20" t="s">
         <v>114</v>
       </c>
@@ -31106,7 +31106,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A525" s="20" t="s">
         <v>114</v>
       </c>
@@ -31139,7 +31139,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A526" s="20" t="s">
         <v>114</v>
       </c>
@@ -31172,7 +31172,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A527" s="20" t="s">
         <v>114</v>
       </c>
@@ -31205,7 +31205,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A528" s="20" t="s">
         <v>114</v>
       </c>
@@ -31238,7 +31238,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A529" s="20" t="s">
         <v>114</v>
       </c>
@@ -31267,7 +31267,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A530" s="20" t="s">
         <v>114</v>
       </c>
@@ -31296,7 +31296,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A531" s="20" t="s">
         <v>114</v>
       </c>
@@ -31325,7 +31325,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A532" s="20" t="s">
         <v>114</v>
       </c>
@@ -31354,7 +31354,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A533" s="20" t="s">
         <v>114</v>
       </c>
@@ -31383,7 +31383,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A534" s="20" t="s">
         <v>114</v>
       </c>
@@ -31412,7 +31412,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A535" s="20" t="s">
         <v>114</v>
       </c>
@@ -31441,7 +31441,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A536" s="20" t="s">
         <v>114</v>
       </c>
@@ -31470,7 +31470,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A537" s="20" t="s">
         <v>114</v>
       </c>
@@ -31499,7 +31499,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A538" s="20" t="s">
         <v>114</v>
       </c>
@@ -31532,7 +31532,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A539" s="20" t="s">
         <v>114</v>
       </c>
@@ -31565,7 +31565,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A540" s="20" t="s">
         <v>114</v>
       </c>
@@ -31598,7 +31598,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A541" s="20" t="s">
         <v>114</v>
       </c>
@@ -31631,7 +31631,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A542" s="20" t="s">
         <v>114</v>
       </c>
@@ -31664,7 +31664,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A543" s="20" t="s">
         <v>114</v>
       </c>
@@ -31693,7 +31693,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A544" s="20" t="s">
         <v>114</v>
       </c>
@@ -31722,7 +31722,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A545" s="20" t="s">
         <v>114</v>
       </c>
@@ -31751,7 +31751,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A546" s="20" t="s">
         <v>114</v>
       </c>
@@ -31780,7 +31780,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A547" s="20" t="s">
         <v>114</v>
       </c>
@@ -31809,7 +31809,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A548" s="20" t="s">
         <v>114</v>
       </c>
@@ -31838,7 +31838,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A549" s="20" t="s">
         <v>114</v>
       </c>
@@ -31867,7 +31867,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A550" s="20" t="s">
         <v>114</v>
       </c>
@@ -31896,7 +31896,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A551" s="20" t="s">
         <v>114</v>
       </c>
@@ -31925,7 +31925,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A552" s="20" t="s">
         <v>114</v>
       </c>
@@ -31954,7 +31954,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A553" s="20" t="s">
         <v>114</v>
       </c>
@@ -31983,7 +31983,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A554" s="20" t="s">
         <v>114</v>
       </c>
@@ -32012,7 +32012,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A555" s="20" t="s">
         <v>114</v>
       </c>
@@ -32041,7 +32041,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A556" s="20" t="s">
         <v>114</v>
       </c>
@@ -32070,7 +32070,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A557" s="20" t="s">
         <v>114</v>
       </c>
@@ -32099,7 +32099,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A558" s="20" t="s">
         <v>114</v>
       </c>
@@ -32128,7 +32128,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A559" s="20" t="s">
         <v>114</v>
       </c>
@@ -32157,7 +32157,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A560" s="20" t="s">
         <v>114</v>
       </c>
@@ -32186,7 +32186,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A561" s="20" t="s">
         <v>114</v>
       </c>
@@ -32215,7 +32215,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A562" s="20" t="s">
         <v>114</v>
       </c>
@@ -32244,7 +32244,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A563" s="20" t="s">
         <v>114</v>
       </c>
@@ -32273,7 +32273,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A564" s="20" t="s">
         <v>114</v>
       </c>
@@ -32302,7 +32302,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A565" s="20" t="s">
         <v>114</v>
       </c>
@@ -32331,7 +32331,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A566" s="20" t="s">
         <v>114</v>
       </c>
@@ -32360,7 +32360,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A567" s="20" t="s">
         <v>114</v>
       </c>
@@ -32389,7 +32389,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A568" s="20" t="s">
         <v>114</v>
       </c>
@@ -32418,7 +32418,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A569" s="20" t="s">
         <v>114</v>
       </c>
@@ -32447,7 +32447,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A570" s="20" t="s">
         <v>114</v>
       </c>
@@ -32476,7 +32476,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A571" s="20" t="s">
         <v>114</v>
       </c>
@@ -32505,7 +32505,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A572" s="20" t="s">
         <v>114</v>
       </c>
@@ -32534,7 +32534,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A573" s="20" t="s">
         <v>114</v>
       </c>
@@ -32563,7 +32563,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A574" s="20" t="s">
         <v>114</v>
       </c>
@@ -32592,7 +32592,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A575" s="20" t="s">
         <v>114</v>
       </c>
@@ -32621,7 +32621,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A576" s="20" t="s">
         <v>114</v>
       </c>
@@ -32650,7 +32650,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A577" s="20" t="s">
         <v>114</v>
       </c>
@@ -32679,7 +32679,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A578" s="20" t="s">
         <v>114</v>
       </c>
@@ -32708,7 +32708,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A579" s="20" t="s">
         <v>114</v>
       </c>
@@ -32737,7 +32737,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A580" s="20" t="s">
         <v>114</v>
       </c>
@@ -32766,7 +32766,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A581" s="20" t="s">
         <v>114</v>
       </c>
@@ -32795,7 +32795,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A582" s="20" t="s">
         <v>114</v>
       </c>
@@ -32824,7 +32824,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A583" s="20" t="s">
         <v>114</v>
       </c>
@@ -32853,7 +32853,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A584" s="20" t="s">
         <v>114</v>
       </c>
@@ -32882,7 +32882,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A585" s="20" t="s">
         <v>114</v>
       </c>
@@ -32911,7 +32911,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A586" s="20" t="s">
         <v>114</v>
       </c>
@@ -32940,7 +32940,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A587" s="20" t="s">
         <v>114</v>
       </c>
@@ -32969,7 +32969,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A588" s="20" t="s">
         <v>114</v>
       </c>
@@ -32998,7 +32998,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A589" s="20" t="s">
         <v>114</v>
       </c>
@@ -33027,7 +33027,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A590" s="20" t="s">
         <v>114</v>
       </c>
@@ -33056,7 +33056,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A591" s="20" t="s">
         <v>114</v>
       </c>
@@ -33085,7 +33085,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A592" s="20" t="s">
         <v>114</v>
       </c>
@@ -33114,7 +33114,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A593" s="20" t="s">
         <v>114</v>
       </c>
@@ -33143,7 +33143,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A594" s="20" t="s">
         <v>114</v>
       </c>
@@ -33172,7 +33172,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A595" s="20" t="s">
         <v>114</v>
       </c>
@@ -33201,7 +33201,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A596" s="20" t="s">
         <v>114</v>
       </c>
@@ -33230,7 +33230,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A597" s="20" t="s">
         <v>114</v>
       </c>
@@ -33259,7 +33259,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A598" s="20" t="s">
         <v>114</v>
       </c>
@@ -33288,7 +33288,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A599" s="20" t="s">
         <v>114</v>
       </c>
@@ -33317,7 +33317,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A600" s="20" t="s">
         <v>114</v>
       </c>
@@ -33346,7 +33346,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A601" s="20" t="s">
         <v>114</v>
       </c>
@@ -33375,7 +33375,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A602" s="20" t="s">
         <v>114</v>
       </c>
@@ -33428,7 +33428,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D039B65-B517-48F3-ABEF-F6AA7FDFDF8B}">
   <dimension ref="A1:AE60"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="37.26953125" style="20" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" style="20" bestFit="1" customWidth="1"/>
@@ -33453,7 +33453,7 @@
     <col min="35" max="16384" width="8.7265625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A1" s="20" t="s">
         <v>107</v>
       </c>
@@ -33461,7 +33461,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A2" s="20" t="s">
         <v>109</v>
       </c>
@@ -33469,7 +33469,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A3" s="20" t="s">
         <v>110</v>
       </c>
@@ -33477,7 +33477,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A5" s="20" t="s">
         <v>136</v>
       </c>
@@ -33485,7 +33485,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A6" s="20" t="s">
         <v>138</v>
       </c>
@@ -33505,7 +33505,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A7" s="21" t="s">
         <v>117</v>
       </c>
@@ -33528,7 +33528,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A8" s="21" t="s">
         <v>124</v>
       </c>
@@ -33551,7 +33551,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A9" s="21" t="s">
         <v>123</v>
       </c>
@@ -33574,7 +33574,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A10" s="21" t="s">
         <v>125</v>
       </c>
@@ -33597,7 +33597,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A11" s="21" t="s">
         <v>126</v>
       </c>
@@ -33617,7 +33617,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" s="21" t="s">
         <v>127</v>
       </c>
@@ -33640,7 +33640,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A13" s="21" t="s">
         <v>128</v>
       </c>
@@ -33663,7 +33663,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A14" s="21" t="s">
         <v>129</v>
       </c>
@@ -33686,7 +33686,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A15" s="21" t="s">
         <v>131</v>
       </c>
@@ -33706,7 +33706,7 @@
         <v>-1020.6999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A16" s="21" t="s">
         <v>139</v>
       </c>
@@ -33726,7 +33726,7 @@
         <v>-2041.4</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A18" s="21" t="s">
         <v>140</v>
       </c>
@@ -33747,12 +33747,12 @@
         <v>-368.4</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A20" s="22" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A21" s="22"/>
       <c r="B21" s="20" t="s">
         <v>141</v>
@@ -33763,7 +33763,7 @@
       </c>
       <c r="Z21" s="23"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.75">
       <c r="B22" s="20">
         <v>2025</v>
       </c>
@@ -33789,7 +33789,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A23" s="20">
         <v>5</v>
       </c>
@@ -33831,7 +33831,7 @@
       <c r="AB23" s="24"/>
       <c r="AC23" s="24"/>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A24" s="20">
         <v>20</v>
       </c>
@@ -33873,7 +33873,7 @@
       <c r="AB24" s="24"/>
       <c r="AC24" s="24"/>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A25" s="20">
         <v>35</v>
       </c>
@@ -33915,7 +33915,7 @@
       <c r="AB25" s="24"/>
       <c r="AC25" s="24"/>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A26" s="20">
         <v>50</v>
       </c>
@@ -33957,7 +33957,7 @@
       <c r="AB26" s="24"/>
       <c r="AC26" s="24"/>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A27" s="20">
         <v>100</v>
       </c>
@@ -33999,12 +33999,12 @@
       <c r="AB27" s="24"/>
       <c r="AC27" s="24"/>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A29" s="22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A30" s="22"/>
       <c r="B30" s="20" t="s">
         <v>141</v>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="Z30" s="23"/>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.75">
       <c r="B31" s="20">
         <v>2025</v>
       </c>
@@ -34041,7 +34041,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A32" s="20">
         <v>5</v>
       </c>
@@ -34083,7 +34083,7 @@
       <c r="AB32" s="24"/>
       <c r="AC32" s="24"/>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A33" s="20">
         <v>20</v>
       </c>
@@ -34125,7 +34125,7 @@
       <c r="AB33" s="24"/>
       <c r="AC33" s="24"/>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A34" s="20">
         <v>35</v>
       </c>
@@ -34167,7 +34167,7 @@
       <c r="AB34" s="24"/>
       <c r="AC34" s="24"/>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A35" s="20">
         <v>50</v>
       </c>
@@ -34209,7 +34209,7 @@
       <c r="AB35" s="25"/>
       <c r="AC35" s="24"/>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A36" s="20">
         <v>100</v>
       </c>
@@ -34251,15 +34251,15 @@
       <c r="AB36" s="24"/>
       <c r="AC36" s="24"/>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A37" s="22"/>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A38" s="22" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A39" s="34" t="s">
         <v>159</v>
       </c>
@@ -34354,7 +34354,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A40" s="20">
         <v>5</v>
       </c>
@@ -34479,7 +34479,7 @@
         <v>24900000000000.09</v>
       </c>
     </row>
-    <row r="41" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A41" s="20">
         <v>20</v>
       </c>
@@ -34604,7 +34604,7 @@
         <v>28299999999999.953</v>
       </c>
     </row>
-    <row r="42" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A42" s="20">
         <v>35</v>
       </c>
@@ -34729,7 +34729,7 @@
         <v>12750000000000</v>
       </c>
     </row>
-    <row r="43" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A43" s="20">
         <v>50</v>
       </c>
@@ -34854,7 +34854,7 @@
         <v>4450000000000.0029</v>
       </c>
     </row>
-    <row r="44" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A44" s="20">
         <v>100</v>
       </c>
@@ -34979,12 +34979,12 @@
         <v>11949999999999.988</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A46" s="22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A47" s="34" t="s">
         <v>159</v>
       </c>
@@ -35079,7 +35079,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="48" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A48" s="20">
         <v>5</v>
       </c>
@@ -35204,7 +35204,7 @@
         <v>1050000000000.0114</v>
       </c>
     </row>
-    <row r="49" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A49" s="20">
         <v>20</v>
       </c>
@@ -35329,7 +35329,7 @@
         <v>50250000000000</v>
       </c>
     </row>
-    <row r="50" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A50" s="20">
         <v>35</v>
       </c>
@@ -35454,7 +35454,7 @@
         <v>60350000000000.023</v>
       </c>
     </row>
-    <row r="51" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A51" s="20">
         <v>50</v>
       </c>
@@ -35579,7 +35579,7 @@
         <v>43500000000000</v>
       </c>
     </row>
-    <row r="52" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A52" s="20">
         <v>100</v>
       </c>
@@ -35704,12 +35704,12 @@
         <v>19899999999999.863</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A54" s="22" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A55" s="34" t="s">
         <v>159</v>
       </c>
@@ -35804,7 +35804,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="56" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A56" s="20">
         <v>5</v>
       </c>
@@ -35929,7 +35929,7 @@
         <v>1050000000000.0114</v>
       </c>
     </row>
-    <row r="57" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A57" s="20">
         <v>20</v>
       </c>
@@ -36054,7 +36054,7 @@
         <v>50250000000000</v>
       </c>
     </row>
-    <row r="58" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A58" s="20">
         <v>35</v>
       </c>
@@ -36179,7 +36179,7 @@
         <v>60350000000000.023</v>
       </c>
     </row>
-    <row r="59" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A59" s="20">
         <v>50</v>
       </c>
@@ -36304,7 +36304,7 @@
         <v>43500000000000</v>
       </c>
     </row>
-    <row r="60" spans="1:31" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:31" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A60" s="20">
         <v>100</v>
       </c>
@@ -36440,7 +36440,7 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:BM272"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="73.81640625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -36453,7 +36453,7 @@
     <col min="16" max="16" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A1" s="8" t="s">
         <v>77</v>
       </c>
@@ -36521,17 +36521,17 @@
       <c r="BK1" s="10"/>
       <c r="BL1" s="10"/>
     </row>
-    <row r="2" spans="1:64" ht="145.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:64" ht="145.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A2" s="11" t="s">
         <v>91</v>
       </c>
       <c r="B2" s="12"/>
     </row>
-    <row r="3" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
     </row>
-    <row r="4" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A4" s="8" t="s">
         <v>78</v>
       </c>
@@ -36599,7 +36599,7 @@
       <c r="BK4" s="10"/>
       <c r="BL4" s="10"/>
     </row>
-    <row r="5" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -36607,12 +36607,12 @@
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -36623,7 +36623,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -36634,7 +36634,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>83</v>
       </c>
@@ -36645,7 +36645,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>84</v>
       </c>
@@ -36656,7 +36656,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -36667,7 +36667,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>86</v>
       </c>
@@ -36678,7 +36678,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>86</v>
       </c>
@@ -36689,7 +36689,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -36700,7 +36700,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -36711,7 +36711,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -36722,7 +36722,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -36733,7 +36733,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -36744,12 +36744,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>85</v>
       </c>
@@ -36758,7 +36758,7 @@
         <v>1299999999.9999998</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>89</v>
       </c>
@@ -36767,12 +36767,12 @@
         <v>1500000000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.75">
       <c r="B42">
         <v>2023</v>
       </c>
@@ -36801,7 +36801,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>156</v>
       </c>
@@ -36833,7 +36833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>157</v>
       </c>
@@ -36865,7 +36865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>158</v>
       </c>
@@ -36897,7 +36897,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>154</v>
       </c>
@@ -36938,7 +36938,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>155</v>
       </c>
@@ -36979,7 +36979,7 @@
         <v>5.1172707889125799E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.75">
       <c r="B48" s="36"/>
       <c r="C48" s="36"/>
       <c r="D48" s="36"/>
@@ -36990,7 +36990,7 @@
       <c r="I48" s="36"/>
       <c r="J48" s="36"/>
     </row>
-    <row r="49" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A49" s="27"/>
       <c r="B49" s="28"/>
       <c r="C49" s="27"/>
@@ -37063,7 +37063,7 @@
       <c r="BL49" s="16"/>
       <c r="BM49" s="16"/>
     </row>
-    <row r="50" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A50" s="27"/>
       <c r="B50" s="12">
         <v>2023</v>
@@ -37155,7 +37155,7 @@
       <c r="BL50" s="16"/>
       <c r="BM50" s="16"/>
     </row>
-    <row r="51" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A51" s="27" t="s">
         <v>160</v>
       </c>
@@ -37262,7 +37262,7 @@
       <c r="BL51" s="16"/>
       <c r="BM51" s="16"/>
     </row>
-    <row r="52" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A52" s="27" t="s">
         <v>161</v>
       </c>
@@ -37369,7 +37369,7 @@
       <c r="BL52" s="16"/>
       <c r="BM52" s="16"/>
     </row>
-    <row r="53" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A53" s="27"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -37435,7 +37435,7 @@
       <c r="BL53" s="16"/>
       <c r="BM53" s="16"/>
     </row>
-    <row r="54" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A54" s="27"/>
       <c r="B54" s="30"/>
       <c r="C54" s="27"/>
@@ -37501,7 +37501,7 @@
       <c r="BL54" s="16"/>
       <c r="BM54" s="16"/>
     </row>
-    <row r="55" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A55" s="31" t="s">
         <v>162</v>
       </c>
@@ -37545,7 +37545,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="56" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A56" s="32">
         <v>5</v>
       </c>
@@ -37602,7 +37602,7 @@
         <v>78500000.000000224</v>
       </c>
     </row>
-    <row r="57" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A57" s="32">
         <v>20</v>
       </c>
@@ -37659,7 +37659,7 @@
         <v>468000000.00000179</v>
       </c>
     </row>
-    <row r="58" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A58" s="32">
         <v>35</v>
       </c>
@@ -37716,7 +37716,7 @@
         <v>364000000.00000316</v>
       </c>
     </row>
-    <row r="59" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A59" s="32">
         <v>50</v>
       </c>
@@ -37773,7 +37773,7 @@
         <v>189999999.99999917</v>
       </c>
     </row>
-    <row r="60" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A60" s="32">
         <v>100</v>
       </c>
@@ -37830,7 +37830,7 @@
         <v>1080000000.0000012</v>
       </c>
     </row>
-    <row r="61" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A61" s="32"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -37843,7 +37843,7 @@
       <c r="J61" s="12"/>
       <c r="L61" s="12"/>
     </row>
-    <row r="62" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A62" s="31" t="s">
         <v>163</v>
       </c>
@@ -37887,7 +37887,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="63" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A63" s="32">
         <v>5</v>
       </c>
@@ -37944,7 +37944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.75">
       <c r="A64" s="32">
         <v>20</v>
       </c>
@@ -38001,7 +38001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A65" s="32">
         <v>35</v>
       </c>
@@ -38058,7 +38058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A66" s="32">
         <v>50</v>
       </c>
@@ -38115,7 +38115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A67" s="32">
         <v>100</v>
       </c>
@@ -38172,7 +38172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A68" s="27"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -38188,7 +38188,7 @@
       <c r="M68" s="12"/>
       <c r="N68" s="12"/>
     </row>
-    <row r="69" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A69" s="31" t="s">
         <v>165</v>
       </c>
@@ -38245,7 +38245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A70" s="31" t="s">
         <v>164</v>
       </c>
@@ -38352,7 +38352,7 @@
       <c r="BK70" s="12"/>
       <c r="BL70" s="12"/>
     </row>
-    <row r="71" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
@@ -38418,7 +38418,7 @@
       <c r="BK71" s="12"/>
       <c r="BL71" s="12"/>
     </row>
-    <row r="72" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A72" s="31" t="s">
         <v>169</v>
       </c>
@@ -38462,7 +38462,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="73" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A73" s="32">
         <v>5</v>
       </c>
@@ -38519,7 +38519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A74" s="32">
         <v>20</v>
       </c>
@@ -38576,7 +38576,7 @@
         <v>437200000.00001162</v>
       </c>
     </row>
-    <row r="75" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A75" s="32">
         <v>35</v>
       </c>
@@ -38633,7 +38633,7 @@
         <v>908600000.00000119</v>
       </c>
     </row>
-    <row r="76" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A76" s="32">
         <v>50</v>
       </c>
@@ -38690,7 +38690,7 @@
         <v>2238000000.0000048</v>
       </c>
     </row>
-    <row r="77" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A77" s="32">
         <v>100</v>
       </c>
@@ -38747,7 +38747,7 @@
         <v>1595999999.9999583</v>
       </c>
     </row>
-    <row r="78" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A78" s="32"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
@@ -38760,7 +38760,7 @@
       <c r="J78" s="12"/>
       <c r="L78" s="12"/>
     </row>
-    <row r="79" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A79" s="31" t="s">
         <v>166</v>
       </c>
@@ -38804,7 +38804,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="80" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A80" s="32">
         <v>5</v>
       </c>
@@ -38861,7 +38861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A81" s="32">
         <v>20</v>
       </c>
@@ -38918,7 +38918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A82" s="32">
         <v>35</v>
       </c>
@@ -38975,7 +38975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A83" s="32">
         <v>50</v>
       </c>
@@ -39032,7 +39032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A84" s="32">
         <v>100</v>
       </c>
@@ -39089,7 +39089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A85" s="27"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
@@ -39105,7 +39105,7 @@
       <c r="M85" s="12"/>
       <c r="N85" s="12"/>
     </row>
-    <row r="86" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A86" s="31" t="s">
         <v>167</v>
       </c>
@@ -39162,7 +39162,7 @@
         <v>10179858186482.16</v>
       </c>
     </row>
-    <row r="87" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A87" s="13"/>
       <c r="B87" s="12">
         <f>B86/10^12</f>
@@ -39267,10 +39267,10 @@
       <c r="BK87" s="12"/>
       <c r="BL87" s="12"/>
     </row>
-    <row r="88" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A88" s="13"/>
     </row>
-    <row r="89" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A89" s="13"/>
       <c r="B89" s="12">
         <v>2021</v>
@@ -39363,7 +39363,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="90" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A90" s="1" t="s">
         <v>170</v>
       </c>
@@ -39489,7 +39489,7 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
     </row>
-    <row r="91" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A91" s="1" t="s">
         <v>171</v>
       </c>
@@ -39615,7 +39615,7 @@
       <c r="AG91" s="18"/>
       <c r="AH91" s="18"/>
     </row>
-    <row r="92" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:64" x14ac:dyDescent="0.75">
       <c r="D92" s="18"/>
       <c r="E92" s="18"/>
       <c r="F92" s="18"/>
@@ -39646,7 +39646,7 @@
       <c r="AE92" s="18"/>
       <c r="AF92" s="18"/>
     </row>
-    <row r="93" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
         <v>172</v>
       </c>
@@ -39680,7 +39680,7 @@
       <c r="AE93" s="18"/>
       <c r="AF93" s="18"/>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A252" s="13" t="s">
         <v>92</v>
       </c>
@@ -39688,15 +39688,15 @@
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A253" s="13"/>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A254" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A255" s="16" t="s">
         <v>80</v>
       </c>
@@ -39708,7 +39708,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A256" s="16" t="s">
         <v>82</v>
       </c>
@@ -39720,7 +39720,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A257" s="16" t="s">
         <v>83</v>
       </c>
@@ -39732,7 +39732,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A258" s="16" t="s">
         <v>84</v>
       </c>
@@ -39744,7 +39744,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A259" s="16" t="s">
         <v>86</v>
       </c>
@@ -39756,7 +39756,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A260" s="16" t="s">
         <v>86</v>
       </c>
@@ -39768,7 +39768,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A261" s="16" t="s">
         <v>86</v>
       </c>
@@ -39780,7 +39780,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A262" s="16" t="s">
         <v>86</v>
       </c>
@@ -39792,7 +39792,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A263" s="16" t="s">
         <v>87</v>
       </c>
@@ -39804,7 +39804,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A264" s="16" t="s">
         <v>86</v>
       </c>
@@ -39816,7 +39816,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A265" s="16" t="s">
         <v>88</v>
       </c>
@@ -39828,7 +39828,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A266" s="16" t="s">
         <v>90</v>
       </c>
@@ -39840,13 +39840,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A268" s="15" t="s">
         <v>144</v>
       </c>
       <c r="B268" s="14"/>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A269" s="16" t="s">
         <v>85</v>
       </c>
@@ -39855,7 +39855,7 @@
         <v>102049999.99999999</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A270" s="16" t="s">
         <v>89</v>
       </c>
@@ -39864,7 +39864,7 @@
         <v>117750000</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A272" s="1" t="s">
         <v>146</v>
       </c>
@@ -39882,14 +39882,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="16.7265625" customWidth="1"/>
     <col min="2" max="17" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="18" max="32" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>102</v>
       </c>
@@ -39987,136 +39987,136 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="40">
+      <c r="B2" s="39">
         <f>Calcs!B4*10^12</f>
         <v>-972800000000000</v>
       </c>
-      <c r="C2" s="40">
-        <f>Calcs!C4*10^12-'Inflation Reduction Act'!B90</f>
+      <c r="C2" s="39">
+        <f>Calcs!C4*10^12</f>
         <v>-983400000000000</v>
       </c>
-      <c r="D2" s="40">
-        <f>Calcs!D4*10^12-'Inflation Reduction Act'!C90</f>
+      <c r="D2" s="39">
+        <f>Calcs!D4*10^12</f>
         <v>-921800000000000</v>
       </c>
-      <c r="E2" s="40">
-        <f>Calcs!E4*10^12-'Inflation Reduction Act'!D90</f>
+      <c r="E2" s="39">
+        <f>Calcs!E4*10^12</f>
         <v>-956473333333333.38</v>
       </c>
-      <c r="F2" s="40">
-        <f>Calcs!F4*10^12-'Inflation Reduction Act'!E90</f>
+      <c r="F2" s="39">
+        <f>Calcs!F4*10^12</f>
         <v>-956384848484848.5</v>
       </c>
-      <c r="G2" s="40">
-        <f>Calcs!G4*10^12-'Inflation Reduction Act'!F90</f>
+      <c r="G2" s="39">
+        <f>Calcs!G4*10^12</f>
         <v>-956296363636363.63</v>
       </c>
-      <c r="H2" s="40">
-        <f>Calcs!H4*10^12-'Inflation Reduction Act'!G90</f>
-        <v>-963781270634201.13</v>
-      </c>
-      <c r="I2" s="40">
-        <f>Calcs!I4*10^12-'Inflation Reduction Act'!H90</f>
-        <v>-974205885478659.13</v>
-      </c>
-      <c r="J2" s="40">
-        <f>Calcs!J4*10^12-'Inflation Reduction Act'!I90</f>
-        <v>-980543585639673.13</v>
-      </c>
-      <c r="K2" s="40">
-        <f>Calcs!K4*10^12-'Inflation Reduction Act'!J90</f>
-        <v>-981937847460889.38</v>
-      </c>
-      <c r="L2" s="40">
-        <f>Calcs!L4*10^12-'Inflation Reduction Act'!K90</f>
-        <v>-980829453230741.38</v>
-      </c>
-      <c r="M2" s="40">
-        <f>Calcs!M4*10^12-'Inflation Reduction Act'!L90</f>
-        <v>-978196538744729.75</v>
-      </c>
-      <c r="N2" s="40">
-        <f>Calcs!N4*10^12-'Inflation Reduction Act'!M90</f>
-        <v>-975835505921831.25</v>
-      </c>
-      <c r="O2" s="40">
-        <f>Calcs!O4*10^12-'Inflation Reduction Act'!N90</f>
-        <v>-972420795060553.25</v>
-      </c>
-      <c r="P2" s="40">
-        <f>Calcs!P4*10^12-'Inflation Reduction Act'!O90</f>
-        <v>-969006084199275.38</v>
-      </c>
-      <c r="Q2" s="40">
-        <f>Calcs!Q4*10^12-'Inflation Reduction Act'!P90</f>
-        <v>-965591373337997.25</v>
-      </c>
-      <c r="R2" s="40">
-        <f>Calcs!R4*10^12-'Inflation Reduction Act'!Q90</f>
-        <v>-965502888489512.38</v>
-      </c>
-      <c r="S2" s="40">
-        <f>Calcs!S4*10^12-'Inflation Reduction Act'!R90</f>
-        <v>-965414403641027.63</v>
-      </c>
-      <c r="T2" s="40">
-        <f>Calcs!T4*10^12-'Inflation Reduction Act'!S90</f>
-        <v>-965325918792542.75</v>
-      </c>
-      <c r="U2" s="40">
-        <f>Calcs!U4*10^12-'Inflation Reduction Act'!T90</f>
-        <v>-965237433944057.88</v>
-      </c>
-      <c r="V2" s="40">
-        <f>Calcs!V4*10^12-'Inflation Reduction Act'!U90</f>
-        <v>-965148949095573</v>
-      </c>
-      <c r="W2" s="40">
-        <f>Calcs!W4*10^12-'Inflation Reduction Act'!V90</f>
-        <v>-965060464247088.13</v>
-      </c>
-      <c r="X2" s="40">
-        <f>Calcs!X4*10^12-'Inflation Reduction Act'!W90</f>
-        <v>-964971979398603.25</v>
-      </c>
-      <c r="Y2" s="40">
-        <f>Calcs!Y4*10^12-'Inflation Reduction Act'!X90</f>
-        <v>-964883494550118.38</v>
-      </c>
-      <c r="Z2" s="40">
-        <f>Calcs!Z4*10^12-'Inflation Reduction Act'!Y90</f>
-        <v>-964795009701633.5</v>
-      </c>
-      <c r="AA2" s="40">
-        <f>Calcs!AA4*10^12-'Inflation Reduction Act'!Z90</f>
-        <v>-964706524853148.75</v>
-      </c>
-      <c r="AB2" s="40">
-        <f>Calcs!AB4*10^12-'Inflation Reduction Act'!AA90</f>
-        <v>-964618040004663.88</v>
-      </c>
-      <c r="AC2" s="40">
-        <f>Calcs!AC4*10^12-'Inflation Reduction Act'!AB90</f>
-        <v>-964529555156179</v>
-      </c>
-      <c r="AD2" s="40">
-        <f>Calcs!AD4*10^12-'Inflation Reduction Act'!AC90</f>
-        <v>-964441070307694.25</v>
-      </c>
-      <c r="AE2" s="40">
-        <f>Calcs!AE4*10^12-'Inflation Reduction Act'!AD90</f>
-        <v>-964352585459209.38</v>
-      </c>
-      <c r="AF2" s="40">
-        <f>Calcs!AF4*10^12-'Inflation Reduction Act'!AE90</f>
-        <v>-964264100610724.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="H2" s="39">
+        <f>Calcs!H4*10^12</f>
+        <v>-956207878787878.88</v>
+      </c>
+      <c r="I2" s="39">
+        <f>Calcs!I4*10^12</f>
+        <v>-956119393939394</v>
+      </c>
+      <c r="J2" s="39">
+        <f>Calcs!J4*10^12</f>
+        <v>-956030909090909.13</v>
+      </c>
+      <c r="K2" s="39">
+        <f>Calcs!K4*10^12</f>
+        <v>-955942424242424.25</v>
+      </c>
+      <c r="L2" s="39">
+        <f>Calcs!L4*10^12</f>
+        <v>-955853939393939.38</v>
+      </c>
+      <c r="M2" s="39">
+        <f>Calcs!M4*10^12</f>
+        <v>-955765454545454.5</v>
+      </c>
+      <c r="N2" s="39">
+        <f>Calcs!N4*10^12</f>
+        <v>-955676969696969.63</v>
+      </c>
+      <c r="O2" s="39">
+        <f>Calcs!O4*10^12</f>
+        <v>-955588484848484.75</v>
+      </c>
+      <c r="P2" s="39">
+        <f>Calcs!P4*10^12</f>
+        <v>-955500000000000</v>
+      </c>
+      <c r="Q2" s="39">
+        <f>Calcs!Q4*10^12</f>
+        <v>-955411515151515.13</v>
+      </c>
+      <c r="R2" s="39">
+        <f>Calcs!R4*10^12</f>
+        <v>-955323030303030.25</v>
+      </c>
+      <c r="S2" s="39">
+        <f>Calcs!S4*10^12</f>
+        <v>-955234545454545.5</v>
+      </c>
+      <c r="T2" s="39">
+        <f>Calcs!T4*10^12</f>
+        <v>-955146060606060.63</v>
+      </c>
+      <c r="U2" s="39">
+        <f>Calcs!U4*10^12</f>
+        <v>-955057575757575.75</v>
+      </c>
+      <c r="V2" s="39">
+        <f>Calcs!V4*10^12</f>
+        <v>-954969090909090.88</v>
+      </c>
+      <c r="W2" s="39">
+        <f>Calcs!W4*10^12</f>
+        <v>-954880606060606</v>
+      </c>
+      <c r="X2" s="39">
+        <f>Calcs!X4*10^12</f>
+        <v>-954792121212121.13</v>
+      </c>
+      <c r="Y2" s="39">
+        <f>Calcs!Y4*10^12</f>
+        <v>-954703636363636.25</v>
+      </c>
+      <c r="Z2" s="39">
+        <f>Calcs!Z4*10^12</f>
+        <v>-954615151515151.38</v>
+      </c>
+      <c r="AA2" s="39">
+        <f>Calcs!AA4*10^12</f>
+        <v>-954526666666666.63</v>
+      </c>
+      <c r="AB2" s="39">
+        <f>Calcs!AB4*10^12</f>
+        <v>-954438181818181.75</v>
+      </c>
+      <c r="AC2" s="39">
+        <f>Calcs!AC4*10^12</f>
+        <v>-954349696969696.88</v>
+      </c>
+      <c r="AD2" s="39">
+        <f>Calcs!AD4*10^12</f>
+        <v>-954261212121212.13</v>
+      </c>
+      <c r="AE2" s="39">
+        <f>Calcs!AE4*10^12</f>
+        <v>-954172727272727.25</v>
+      </c>
+      <c r="AF2" s="39">
+        <f>Calcs!AF4*10^12</f>
+        <v>-954084242424242.38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -40214,7 +40214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -40312,7 +40312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -40410,7 +40410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -40508,7 +40508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -40606,7 +40606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -40704,7 +40704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -40802,7 +40802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -40900,265 +40900,265 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="39">
         <f>Calcs!B5*10^12/About!$B$17</f>
         <v>2117857142857.1428</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="39">
         <f>Calcs!C5*10^12/About!$B$17</f>
         <v>2217857142857.1431</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="39">
         <f>Calcs!D5*10^12/About!$B$17</f>
         <v>2085714285714.2856</v>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="39">
         <f>Calcs!E5*10^12/About!$B$17</f>
         <v>2121060606060.6055</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="39">
         <f>Calcs!F5*10^12/About!$B$17</f>
         <v>2136883116883.1184</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="39">
         <f>Calcs!G5*10^12/About!$B$17</f>
         <v>2152705627705.6309</v>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="39">
         <f>Calcs!H5*10^12/About!$B$17</f>
         <v>2168528138528.1394</v>
       </c>
-      <c r="I11" s="40">
+      <c r="I11" s="39">
         <f>Calcs!I5*10^12/About!$B$17</f>
         <v>2184350649350.6523</v>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="39">
         <f>Calcs!J5*10^12/About!$B$17</f>
         <v>2200173160173.1606</v>
       </c>
-      <c r="K11" s="40">
+      <c r="K11" s="39">
         <f>Calcs!K5*10^12/About!$B$17</f>
         <v>2215995670995.6733</v>
       </c>
-      <c r="L11" s="40">
+      <c r="L11" s="39">
         <f>Calcs!L5*10^12/About!$B$17</f>
         <v>2231818181818.1821</v>
       </c>
-      <c r="M11" s="40">
+      <c r="M11" s="39">
         <f>Calcs!M5*10^12/About!$B$17</f>
         <v>2247640692640.6948</v>
       </c>
-      <c r="N11" s="40">
+      <c r="N11" s="39">
         <f>Calcs!N5*10^12/About!$B$17</f>
         <v>2263463203463.2036</v>
       </c>
-      <c r="O11" s="40">
+      <c r="O11" s="39">
         <f>Calcs!O5*10^12/About!$B$17</f>
         <v>2279285714285.7158</v>
       </c>
-      <c r="P11" s="40">
+      <c r="P11" s="39">
         <f>Calcs!P5*10^12/About!$B$17</f>
         <v>2295108225108.2246</v>
       </c>
-      <c r="Q11" s="40">
+      <c r="Q11" s="39">
         <f>Calcs!Q5*10^12/About!$B$17</f>
         <v>2310930735930.7373</v>
       </c>
-      <c r="R11" s="40">
+      <c r="R11" s="39">
         <f>Calcs!R5*10^12/About!$B$17</f>
         <v>2326753246753.25</v>
       </c>
-      <c r="S11" s="40">
+      <c r="S11" s="39">
         <f>Calcs!S5*10^12/About!$B$17</f>
         <v>2342575757575.7588</v>
       </c>
-      <c r="T11" s="40">
+      <c r="T11" s="39">
         <f>Calcs!T5*10^12/About!$B$17</f>
         <v>2358398268398.271</v>
       </c>
-      <c r="U11" s="40">
+      <c r="U11" s="39">
         <f>Calcs!U5*10^12/About!$B$17</f>
         <v>2374220779220.7798</v>
       </c>
-      <c r="V11" s="40">
+      <c r="V11" s="39">
         <f>Calcs!V5*10^12/About!$B$17</f>
         <v>2390043290043.2925</v>
       </c>
-      <c r="W11" s="40">
+      <c r="W11" s="39">
         <f>Calcs!W5*10^12/About!$B$17</f>
         <v>2405865800865.8013</v>
       </c>
-      <c r="X11" s="40">
+      <c r="X11" s="39">
         <f>Calcs!X5*10^12/About!$B$17</f>
         <v>2421688311688.314</v>
       </c>
-      <c r="Y11" s="40">
+      <c r="Y11" s="39">
         <f>Calcs!Y5*10^12/About!$B$17</f>
         <v>2437510822510.8228</v>
       </c>
-      <c r="Z11" s="40">
+      <c r="Z11" s="39">
         <f>Calcs!Z5*10^12/About!$B$17</f>
         <v>2453333333333.335</v>
       </c>
-      <c r="AA11" s="40">
+      <c r="AA11" s="39">
         <f>Calcs!AA5*10^12/About!$B$17</f>
         <v>2469155844155.8438</v>
       </c>
-      <c r="AB11" s="40">
+      <c r="AB11" s="39">
         <f>Calcs!AB5*10^12/About!$B$17</f>
         <v>2484978354978.3564</v>
       </c>
-      <c r="AC11" s="40">
+      <c r="AC11" s="39">
         <f>Calcs!AC5*10^12/About!$B$17</f>
         <v>2500800865800.8647</v>
       </c>
-      <c r="AD11" s="40">
+      <c r="AD11" s="39">
         <f>Calcs!AD5*10^12/About!$B$17</f>
         <v>2516623376623.3779</v>
       </c>
-      <c r="AE11" s="40">
+      <c r="AE11" s="39">
         <f>Calcs!AE5*10^12/About!$B$17</f>
         <v>2532445887445.8906</v>
       </c>
-      <c r="AF11" s="40">
+      <c r="AF11" s="39">
         <f>Calcs!AF5*10^12/About!$B$17</f>
         <v>2548268398268.3989</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="39">
         <f>Calcs!B6*10^12/About!$B$18</f>
         <v>34339622641.509434</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="39">
         <f>Calcs!C6*10^12/About!$B$18</f>
         <v>40377358490.56604</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <f>Calcs!D6*10^12/About!$B$18</f>
         <v>34339622641.509434</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="39">
         <f>Calcs!E6*10^12/About!$B$18</f>
         <v>34810748999.428329</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="39">
         <f>Calcs!F6*10^12/About!$B$18</f>
         <v>35684391080.617645</v>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="39">
         <f>Calcs!G6*10^12/About!$B$18</f>
         <v>36558033161.806961</v>
       </c>
-      <c r="H12" s="40">
+      <c r="H12" s="39">
         <f>Calcs!H6*10^12/About!$B$18</f>
         <v>37431675242.996277</v>
       </c>
-      <c r="I12" s="40">
+      <c r="I12" s="39">
         <f>Calcs!I6*10^12/About!$B$18</f>
         <v>38305317324.185379</v>
       </c>
-      <c r="J12" s="40">
+      <c r="J12" s="39">
         <f>Calcs!J6*10^12/About!$B$18</f>
         <v>39178959405.374687</v>
       </c>
-      <c r="K12" s="40">
+      <c r="K12" s="39">
         <f>Calcs!K6*10^12/About!$B$18</f>
         <v>40052601486.564003</v>
       </c>
-      <c r="L12" s="40">
+      <c r="L12" s="39">
         <f>Calcs!L6*10^12/About!$B$18</f>
         <v>40926243567.753105</v>
       </c>
-      <c r="M12" s="40">
+      <c r="M12" s="39">
         <f>Calcs!M6*10^12/About!$B$18</f>
         <v>41799885648.942413</v>
       </c>
-      <c r="N12" s="40">
+      <c r="N12" s="39">
         <f>Calcs!N6*10^12/About!$B$18</f>
         <v>42673527730.131729</v>
       </c>
-      <c r="O12" s="40">
+      <c r="O12" s="39">
         <f>Calcs!O6*10^12/About!$B$18</f>
         <v>43547169811.320831</v>
       </c>
-      <c r="P12" s="40">
+      <c r="P12" s="39">
         <f>Calcs!P6*10^12/About!$B$18</f>
         <v>44420811892.510147</v>
       </c>
-      <c r="Q12" s="40">
+      <c r="Q12" s="39">
         <f>Calcs!Q6*10^12/About!$B$18</f>
         <v>45294453973.699463</v>
       </c>
-      <c r="R12" s="40">
+      <c r="R12" s="39">
         <f>Calcs!R6*10^12/About!$B$18</f>
         <v>46168096054.888779</v>
       </c>
-      <c r="S12" s="40">
+      <c r="S12" s="39">
         <f>Calcs!S6*10^12/About!$B$18</f>
         <v>47041738136.077873</v>
       </c>
-      <c r="T12" s="40">
+      <c r="T12" s="39">
         <f>Calcs!T6*10^12/About!$B$18</f>
         <v>47915380217.267189</v>
       </c>
-      <c r="U12" s="40">
+      <c r="U12" s="39">
         <f>Calcs!U6*10^12/About!$B$18</f>
         <v>48789022298.456497</v>
       </c>
-      <c r="V12" s="40">
+      <c r="V12" s="39">
         <f>Calcs!V6*10^12/About!$B$18</f>
         <v>49662664379.645607</v>
       </c>
-      <c r="W12" s="40">
+      <c r="W12" s="39">
         <f>Calcs!W6*10^12/About!$B$18</f>
         <v>50536306460.834923</v>
       </c>
-      <c r="X12" s="40">
+      <c r="X12" s="39">
         <f>Calcs!X6*10^12/About!$B$18</f>
         <v>51409948542.024231</v>
       </c>
-      <c r="Y12" s="40">
+      <c r="Y12" s="39">
         <f>Calcs!Y6*10^12/About!$B$18</f>
         <v>52283590623.213333</v>
       </c>
-      <c r="Z12" s="40">
+      <c r="Z12" s="39">
         <f>Calcs!Z6*10^12/About!$B$18</f>
         <v>53157232704.402649</v>
       </c>
-      <c r="AA12" s="40">
+      <c r="AA12" s="39">
         <f>Calcs!AA6*10^12/About!$B$18</f>
         <v>54030874785.591957</v>
       </c>
-      <c r="AB12" s="40">
+      <c r="AB12" s="39">
         <f>Calcs!AB6*10^12/About!$B$18</f>
         <v>54904516866.781281</v>
       </c>
-      <c r="AC12" s="40">
+      <c r="AC12" s="39">
         <f>Calcs!AC6*10^12/About!$B$18</f>
         <v>55778158947.970375</v>
       </c>
-      <c r="AD12" s="40">
+      <c r="AD12" s="39">
         <f>Calcs!AD6*10^12/About!$B$18</f>
         <v>56651801029.159691</v>
       </c>
-      <c r="AE12" s="40">
+      <c r="AE12" s="39">
         <f>Calcs!AE6*10^12/About!$B$18</f>
         <v>57525443110.349007</v>
       </c>
-      <c r="AF12" s="40">
+      <c r="AF12" s="39">
         <f>Calcs!AF6*10^12/About!$B$18</f>
         <v>58399085191.538101</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>7</v>
       </c>
